--- a/Result/checksun_type/配電系統.xlsx
+++ b/Result/checksun_type/配電系統.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1116.653</t>
+          <t>617.266</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-80.90</t>
+          <t>-75.86</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-17 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>-8.03</t>
+          <t>-5.99</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,77 +1009,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1117</t>
+          <t>617</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>23.47</t>
+          <t>8.47</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-3.99</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>9.29</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>10.09</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>752.0</t>
+          <t>745.6</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>688.05</t>
+          <t>695.2</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>628.72</t>
+          <t>631.48</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>632.04</t>
+          <t>633.66</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>42.23</t>
+          <t>39.85</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>40.46</t>
+          <t>40.34</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-49.89</t>
+          <t>-50.05</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,27 +1099,27 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>4935698093.450796</t>
+          <t>4929548641.36344</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>811169006.0</t>
+          <t>453518166.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>779349653.2</t>
+          <t>696124492.8</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>4079717323.9</t>
+          <t>2883970531.7</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>2168937186.34</t>
+          <t>2126707687.18</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
@@ -1129,15 +1129,15 @@
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>149460129.7576182</t>
+          <t>29518563.01117429</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-567096178.3200001</v>
+        <v>-630160054.09</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-6.48</t>
+          <t>-4.40</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1182,22 +1182,22 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>-23.80928100874268</t>
+          <t>17.93840330060069</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>7.31764784445801</t>
+          <t>13.37012123856452</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>28.02509919012324</t>
+          <t>23.64886415022257</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1207,12 +1207,12 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>26.03</t>
+          <t>26.60</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>52.97</t>
+          <t>54.15</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>228065</t>
+          <t>233119</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>725.0</t>
+          <t>737.0</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>736.0</t>
+          <t>739.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>730.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1008.586</t>
+          <t>1116.653</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>745.0</t>
+          <t>722.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-3.19</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-82.40</t>
+          <t>-80.90</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-17 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -1404,12 +1404,12 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>-5.10</t>
+          <t>-8.03</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,12 +1440,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1117</t>
+          <t>617</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1455,62 +1455,62 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>49.94</t>
+          <t>23.47</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-3.99</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>11.02</t>
+          <t>9.29</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>8.78</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>756.8</t>
+          <t>752.0</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>681.7</t>
+          <t>688.05</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>626.7</t>
+          <t>628.72</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>630.91</t>
+          <t>632.04</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>15.69</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>46.30</t>
+          <t>42.23</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>40.02</t>
+          <t>40.46</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-50.44</t>
+          <t>-49.89</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,27 +1530,27 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>4935698093.450796</t>
+          <t>4929548641.36344</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>757270421.0</t>
+          <t>811169006.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>855936440.6</t>
+          <t>779349653.2</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>4864530439.2</t>
+          <t>4079717323.9</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>2227082877.5</t>
+          <t>2168937186.34</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
@@ -1560,15 +1560,15 @@
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>279743094.8631054</t>
+          <t>149460129.7576182</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-495071225.14</v>
+        <v>-567096178.3200001</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-3.50</t>
+          <t>-6.48</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1613,17 +1613,17 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>-23.80928100874268</t>
+          <t>17.93840330060069</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>7.31764784445801</t>
+          <t>13.37012123856452</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>28.02509919012324</t>
+          <t>23.64886415022257</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
@@ -1633,17 +1633,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>26.86</t>
+          <t>26.03</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>52.97</t>
+          <t>54.15</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>228065</t>
+          <t>233119</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>769.0</t>
+          <t>725.0</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>769.0</t>
+          <t>736.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>737.0</t>
+          <t>722.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>745.0</t>
+          <t>722.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>711.087</t>
+          <t>1008.586</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>765.0</t>
+          <t>745.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-5.96</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-81.30</t>
+          <t>-82.40</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-17 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-5.10</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,77 +1871,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1117</t>
+          <t>617</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>70.42</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>80.35</t>
+          <t>49.94</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>13.05</t>
+          <t>11.02</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>8.78</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>760.8</t>
+          <t>756.8</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>673.0</t>
+          <t>681.7</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>624.74</t>
+          <t>626.7</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>629.5</t>
+          <t>630.91</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>26.07</t>
+          <t>15.69</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>48.47</t>
+          <t>46.30</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>38.45</t>
+          <t>40.02</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-52.39</t>
+          <t>-50.44</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,27 +1961,27 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>4935698093.450796</t>
+          <t>4929548641.36344</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>543477829.0</t>
+          <t>757270421.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>1032473983.6</t>
+          <t>855936440.6</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>5522062366.6</t>
+          <t>4864530439.2</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>2292721646.52</t>
+          <t>2227082877.5</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -1991,15 +1991,15 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>420618425.772247</t>
+          <t>279743094.8631054</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-368722471.3</v>
+        <v>-495071225.14</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-3.50</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2044,37 +2044,37 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>-23.80928100874268</t>
+          <t>17.93840330060069</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>7.31764784445801</t>
+          <t>13.37012123856452</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>28.02509919012324</t>
+          <t>23.64886415022257</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>27.58</t>
+          <t>26.86</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>52.97</t>
+          <t>54.15</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>228065</t>
+          <t>233119</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>765.0</t>
+          <t>769.0</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>770.0</t>
+          <t>769.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>759.0</t>
+          <t>737.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>765.0</t>
+          <t>745.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1193.09</t>
+          <t>711.087</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>758.0</t>
+          <t>765.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-4.99</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-57.71</t>
+          <t>-81.30</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-17 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.90</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,77 +2302,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1117</t>
+          <t>617</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>79.41</t>
+          <t>70.42</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>82.88</t>
+          <t>80.35</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>15.48</t>
+          <t>13.05</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>6.51</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>764.8</t>
+          <t>760.8</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>662.3</t>
+          <t>673.0</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>621.8</t>
+          <t>624.74</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>627.64</t>
+          <t>629.5</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>34.94</t>
+          <t>26.07</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>48.50</t>
+          <t>48.47</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>35.94</t>
+          <t>38.45</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-55.49</t>
+          <t>-52.39</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,27 +2392,27 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>4935698093.450796</t>
+          <t>4929548641.36344</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>915187042.0</t>
+          <t>543477829.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>2404829140.4</t>
+          <t>1032473983.6</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>5686609711.2</t>
+          <t>5522062366.6</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>2312774767.92</t>
+          <t>2292721646.52</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -2422,15 +2422,15 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>564134952.5119295</t>
+          <t>420618425.772247</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-152149242.69</v>
+        <v>-368722471.3</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2475,22 +2475,22 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>-23.80928100874268</t>
+          <t>17.93840330060069</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>7.31764784445801</t>
+          <t>13.37012123856452</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>28.02509919012324</t>
+          <t>23.64886415022257</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2500,12 +2500,12 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>27.33</t>
+          <t>27.58</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>52.97</t>
+          <t>54.15</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>228065</t>
+          <t>233119</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>775.0</t>
+          <t>765.0</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>780.0</t>
+          <t>770.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>758.0</t>
+          <t>759.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>758.0</t>
+          <t>765.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1144.535</t>
+          <t>1193.09</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>770.0</t>
+          <t>758.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-6.65</t>
+          <t>-2.71</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-15.19</t>
+          <t>-57.71</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-17 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -2697,12 +2697,12 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>-2.90</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,77 +2733,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1117</t>
+          <t>617</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>91.21</t>
+          <t>79.41</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>86.14</t>
+          <t>82.88</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>17.70</t>
+          <t>15.48</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>5.32</t>
+          <t>6.51</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>767.6</t>
+          <t>764.8</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>652.15</t>
+          <t>662.3</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>619.2</t>
+          <t>621.8</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>625.75</t>
+          <t>627.64</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>48.00</t>
+          <t>34.94</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>48.55</t>
+          <t>48.50</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>32.80</t>
+          <t>35.94</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-59.38</t>
+          <t>-55.49</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,45 +2823,45 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>4935698093.450796</t>
+          <t>4929548641.36344</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>869643968.0</t>
+          <t>915187042.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>5071816570.6</t>
+          <t>2404829140.4</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>5980378748.8</t>
+          <t>5686609711.2</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>2324099002.48</t>
+          <t>2312774767.92</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-908562178</t>
+          <t>-2147483648</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>694368442.54881</t>
+          <t>564134952.5119295</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>122848998.31</v>
+        <v>-152149242.69</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2906,37 +2906,37 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>-23.80928100874268</t>
+          <t>17.93840330060069</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>7.31764784445801</t>
+          <t>13.37012123856452</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>28.02509919012324</t>
+          <t>23.64886415022257</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>27.76</t>
+          <t>27.33</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>52.97</t>
+          <t>54.15</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>228065</t>
+          <t>233119</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>765.0</t>
+          <t>775.0</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>770.0</t>
+          <t>780.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>758.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>770.0</t>
+          <t>758.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1587.408</t>
+          <t>1144.535</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>746.0</t>
+          <t>770.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-3.32</t>
+          <t>-4.34</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>23.64</t>
+          <t>-15.19</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-17 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -3128,12 +3128,12 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>-4.97</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3164,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1117</t>
+          <t>617</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>78.02</t>
+          <t>91.21</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>88.9</t>
+          <t>86.14</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>20.18</t>
+          <t>17.70</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>770.8</t>
+          <t>767.6</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>641.35</t>
+          <t>652.15</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>616.0</t>
+          <t>619.2</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>624.02</t>
+          <t>625.75</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>61.71</t>
+          <t>48.00</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>46.68</t>
+          <t>48.55</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>28.87</t>
+          <t>32.80</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-64.25</t>
+          <t>-59.38</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,45 +3254,45 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>4935698093.450796</t>
+          <t>4929548641.36344</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1194102943.0</t>
+          <t>869643968.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>7380084994.6</t>
+          <t>5071816570.6</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>5968914067.6</t>
+          <t>5980378748.8</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>2329253341.64</t>
+          <t>2324099002.48</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>1411170927</t>
+          <t>-908562178</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>798281068.7748979</t>
+          <t>694368442.54881</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>516195779.15</v>
+        <v>122848998.31</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3337,22 +3337,22 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>-23.80928100874268</t>
+          <t>17.93840330060069</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>7.31764784445801</t>
+          <t>13.37012123856452</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>28.02509919012324</t>
+          <t>23.64886415022257</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>26.89</t>
+          <t>27.76</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>52.97</t>
+          <t>54.15</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>228065</t>
+          <t>233119</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>755.0</t>
+          <t>765.0</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>774.0</t>
+          <t>770.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>743.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>746.0</t>
+          <t>770.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2119.821</t>
+          <t>1587.408</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>765.0</t>
+          <t>746.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-5.96</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>49.26</t>
+          <t>23.64</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3519,7 +3519,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-17 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3539,7 +3539,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-4.97</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,98 +3574,98 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1117</t>
+          <t>617</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>89.18</t>
+          <t>78.02</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>93.92</t>
+          <t>88.9</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>20.88</t>
+          <t>20.18</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>764.6</t>
+          <t>770.8</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>632.55</t>
+          <t>641.35</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>613.28</t>
+          <t>616.0</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>622.34</t>
+          <t>624.02</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>88.66</t>
+          <t>61.71</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>46.06</t>
+          <t>46.68</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>24.41</t>
+          <t>28.87</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-69.77</t>
+          <t>-64.25</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,45 +3685,45 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>4935698093.450796</t>
+          <t>4929548641.36344</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1639958136.0</t>
+          <t>1194102943.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>8873124437.8</t>
+          <t>7380084994.6</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>5944629753.8</t>
+          <t>5968914067.6</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>2333052998.56</t>
+          <t>2329253341.64</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-2147483648</t>
+          <t>1411170927</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>849569303.2528446</t>
+          <t>798281068.7748979</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>1024920726.63</v>
+        <v>516195779.15</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3768,17 +3768,17 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>-23.80928100874268</t>
+          <t>17.93840330060069</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>7.31764784445801</t>
+          <t>13.37012123856452</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>28.02509919012324</t>
+          <t>23.64886415022257</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
@@ -3788,17 +3788,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>27.58</t>
+          <t>26.89</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>52.97</t>
+          <t>54.15</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>228065</t>
+          <t>233119</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>785.0</t>
+          <t>755.0</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>785.0</t>
+          <t>774.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>765.0</t>
+          <t>743.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>765.0</t>
+          <t>746.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>9688.689</t>
+          <t>2119.821</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,74 +3910,74 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>765.0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-3.66</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>-1.95</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>49.26</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2025-11-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2025-09-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>785.0</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>-8.73</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>-0.77</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>70.54</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>2025-11-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2025-11-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2025-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2025-09-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>738.0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>785.0</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>785.0</t>
-        </is>
-      </c>
       <c r="T9" t="inlineStr">
         <is>
           <t>624.0</t>
@@ -3990,12 +3990,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>34.55</t>
+          <t>7.56</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>5.41</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1117</t>
+          <t>617</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>99.5</t>
+          <t>89.18</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>97.52</t>
+          <t>93.92</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>5.85</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>20.88</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>741.6</t>
+          <t>764.6</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>623.0</t>
+          <t>632.55</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>609.92</t>
+          <t>613.28</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>620.01</t>
+          <t>622.34</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>124.51</t>
+          <t>88.66</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>42.66</t>
+          <t>46.06</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>24.41</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-76.47</t>
+          <t>-69.77</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,27 +4116,27 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>4935698093.450796</t>
+          <t>4929548641.36344</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>7405253613.0</t>
+          <t>1639958136.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>10011650749.6</t>
+          <t>8873124437.8</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>5870589709.3</t>
+          <t>5944629753.8</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>2337679186.88</t>
+          <t>2333052998.56</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -4146,15 +4146,15 @@
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>817687226.2755579</t>
+          <t>849569303.2528446</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>1667296140.69</v>
+        <v>1024920726.63</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4199,37 +4199,37 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>-23.80928100874268</t>
+          <t>17.93840330060069</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>7.31764784445801</t>
+          <t>13.37012123856452</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>28.02509919012324</t>
+          <t>23.64886415022257</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>28.30</t>
+          <t>27.58</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>52.97</t>
+          <t>54.15</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>228065</t>
+          <t>233119</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>748.0</t>
+          <t>785.0</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>788.0</t>
+          <t>785.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>742.0</t>
+          <t>765.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>785.0</t>
+          <t>765.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>18118.77</t>
+          <t>9688.689</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>772.0</t>
+          <t>785.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,22 +4351,22 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-6.93</t>
+          <t>-6.37</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>69.40</t>
+          <t>70.54</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-17 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>785.0</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -4421,12 +4421,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6.37</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>64.61</t>
+          <t>34.55</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>5.41</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1117</t>
+          <t>617</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>93.07</t>
+          <t>99.5</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>97.69</t>
+          <t>97.52</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>5.85</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>15.20</t>
+          <t>19.04</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>705.4</t>
+          <t>741.6</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>612.35</t>
+          <t>623.0</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>606.42</t>
+          <t>609.92</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>617.41</t>
+          <t>620.01</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>172.56</t>
+          <t>124.51</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>35.67</t>
+          <t>42.66</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>13.09</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-83.79</t>
+          <t>-76.47</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,27 +4547,27 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>4935698093.450796</t>
+          <t>4929548641.36344</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>14250124193.0</t>
+          <t>7405253613.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>8968390282.0</t>
+          <t>10011650749.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>5294074253.1</t>
+          <t>5870589709.3</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>2221550552.1</t>
+          <t>2337679186.88</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
@@ -4577,15 +4577,15 @@
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>663212878.2008342</t>
+          <t>817687226.2755579</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>1907718783.21</v>
+        <v>1667296140.69</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4630,22 +4630,22 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>-23.80928100874268</t>
+          <t>17.93840330060069</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>7.31764784445801</t>
+          <t>13.37012123856452</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>28.02509919012324</t>
+          <t>23.64886415022257</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>27.83</t>
+          <t>28.30</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>52.97</t>
+          <t>54.15</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>228065</t>
+          <t>233119</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>800.0</t>
+          <t>748.0</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>816.0</t>
+          <t>788.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>763.0</t>
+          <t>742.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>772.0</t>
+          <t>785.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>9.45</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>16158.888</t>
+          <t>18118.77</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>786.0</t>
+          <t>772.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-8.86</t>
+          <t>-4.61</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>70.78</t>
+          <t>69.40</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-17 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,98 +4867,98 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>57.62</t>
+          <t>64.61</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1117</t>
+          <t>617</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>93.07</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>97.69</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>16.51</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>12.08</t>
+          <t>15.20</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>674.6</t>
+          <t>705.4</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>601.9</t>
+          <t>612.35</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>603.2</t>
+          <t>606.42</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>614.95</t>
+          <t>617.41</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>270.23</t>
+          <t>172.56</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>27.55</t>
+          <t>35.67</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>7.44</t>
+          <t>13.09</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-90.78</t>
+          <t>-83.79</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,27 +4978,27 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>4935698093.450796</t>
+          <t>4929548641.36344</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>12410986088.0</t>
+          <t>14250124193.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>6888940927.0</t>
+          <t>8968390282.0</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>4033826236.5</t>
+          <t>5294074253.1</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>1975526023.72</t>
+          <t>2221550552.1</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
@@ -5008,11 +5008,11 @@
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>436939077.2900687</t>
+          <t>663212878.2008342</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>1449667896.7</v>
+        <v>1907718783.21</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5061,22 +5061,22 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>-23.80928100874268</t>
+          <t>17.93840330060069</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>7.31764784445801</t>
+          <t>13.37012123856452</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>28.02509919012324</t>
+          <t>23.64886415022257</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>28.33</t>
+          <t>27.83</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>52.97</t>
+          <t>54.15</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>228065</t>
+          <t>233119</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>751.0</t>
+          <t>800.0</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>786.0</t>
+          <t>816.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>740.0</t>
+          <t>763.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>786.0</t>
+          <t>772.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>9.92</t>
+          <t>9.45</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>12447.108</t>
+          <t>16158.888</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>715.0</t>
+          <t>786.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>-6.5</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>54.83</t>
+          <t>70.78</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-17 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5263,7 +5263,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6.50</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>44.39</t>
+          <t>57.62</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>9.83</t>
+          <t>6.22</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,12 +5319,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1117</t>
+          <t>617</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5334,62 +5334,62 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>86.27</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>12.46</t>
+          <t>16.51</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>7.51</t>
+          <t>12.08</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>635.8</t>
+          <t>674.6</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>591.4</t>
+          <t>601.9</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>599.7</t>
+          <t>603.2</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>612.08</t>
+          <t>614.95</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>536.26</t>
+          <t>270.23</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>15.36</t>
+          <t>27.55</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>7.44</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-97.01</t>
+          <t>-90.78</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>4935698093.450796</t>
+          <t>4929548641.36344</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>8659300159.0</t>
+          <t>12410986088.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>4557743140.6</t>
+          <t>6888940927.0</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>2943700170.0</t>
+          <t>4033826236.5</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>1771180630.7</t>
+          <t>1975526023.72</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>1614042970</t>
+          <t>-2147483648</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>252806564.6700073</t>
+          <t>436939077.2900687</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>940586145.2</v>
+        <v>1449667896.7</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-7.38</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5492,22 +5492,22 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>-23.80928100874268</t>
+          <t>17.93840330060069</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>7.31764784445801</t>
+          <t>13.37012123856452</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>28.02509919012324</t>
+          <t>23.64886415022257</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>25.78</t>
+          <t>28.33</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>52.97</t>
+          <t>54.15</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>228065</t>
+          <t>233119</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>655.0</t>
+          <t>751.0</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>715.0</t>
+          <t>786.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>651.0</t>
+          <t>740.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>715.0</t>
+          <t>786.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-2.9</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3626.375</t>
+          <t>2248.507</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-75.12</t>
+          <t>-53.51</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-11.57</t>
+          <t>-12.56</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,33 +5729,33 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>5.98</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>67</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>3626</t>
+          <t>2249</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5770,57 +5770,57 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>101.72</t>
+          <t>100.42</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>103.96</t>
+          <t>103.72</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>103.6</t>
+          <t>103.4</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>104.44</t>
+          <t>104.41</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-109.91</t>
+          <t>-215.80</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-94.89</t>
+          <t>-96.68</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,41 +5840,41 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>1686949275.130246</t>
+          <t>1684989303.348988</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>360108082.0</t>
+          <t>220432535.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>286154072.8</t>
+          <t>268507044.2</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>1150276311.8</t>
+          <t>577618774.1</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>408529389.62</t>
+          <t>409190484.56</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-864122239</t>
+          <t>-309111729</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>66575220.08572514</t>
+          <t>41195103.42357187</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>-80684181.05</v>
+        <v>-98395538.22</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-2.86</t>
+          <t>-3.94</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5923,22 +5923,22 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>25.2953630939842</t>
+          <t>-3.87807238678311</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>75.04202393244248</t>
+          <t>19.31984554517413</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>18.11389392834446</t>
+          <t>19.19310202755954</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
@@ -5948,12 +5948,12 @@
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>4.40</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>32.65</t>
+          <t>32.28</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>26928</t>
+          <t>26628</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>99.2</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>99.6</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>97.2</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2607.704</t>
+          <t>3626.375</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-77.08</t>
+          <t>-75.12</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-8.97</t>
+          <t>-11.57</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6160,33 +6160,33 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>5.98</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>67</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>3626</t>
+          <t>2249</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6196,62 +6196,62 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>5.21</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>103.1</t>
+          <t>101.72</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>104.18</t>
+          <t>103.96</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>103.79</t>
+          <t>103.6</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>104.52</t>
+          <t>104.44</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-53.80</t>
+          <t>-109.91</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-93.49</t>
+          <t>-94.89</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,41 +6271,41 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>1686949275.130246</t>
+          <t>1684989303.348988</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>264455621.0</t>
+          <t>360108082.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>299044660.2</t>
+          <t>286154072.8</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>1304605197.0</t>
+          <t>1150276311.8</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>411510598.5</t>
+          <t>408529389.62</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-1005560536</t>
+          <t>-864122239</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>93349656.65584514</t>
+          <t>66575220.08572514</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>-67465901.52</v>
+        <v>-80684181.05</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.86</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6354,22 +6354,22 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>25.2953630939842</t>
+          <t>-3.87807238678311</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>75.04202393244248</t>
+          <t>19.31984554517413</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>18.11389392834446</t>
+          <t>19.19310202755954</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
@@ -6379,12 +6379,12 @@
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>32.65</t>
+          <t>32.28</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>26928</t>
+          <t>26628</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2354.931</t>
+          <t>2607.704</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6506,17 +6506,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-4.1</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-67.98</t>
+          <t>-77.08</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>3.89</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,12 +6612,12 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>67</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>3626</t>
+          <t>2249</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6627,32 +6627,32 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>16.14</t>
+          <t>5.21</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>104.9</t>
+          <t>103.1</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -6662,27 +6662,27 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>104.03</t>
+          <t>103.79</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>104.57</t>
+          <t>104.52</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-25.93</t>
+          <t>-53.80</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-92.62</t>
+          <t>-93.49</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,41 +6702,41 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>1686949275.130246</t>
+          <t>1684989303.348988</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>240787568.0</t>
+          <t>264455621.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>420099846.8</t>
+          <t>299044660.2</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>1311901908.4</t>
+          <t>1304605197.0</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>422014478.54</t>
+          <t>411510598.5</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-891802061</t>
+          <t>-1005560536</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>122588849.0518091</t>
+          <t>93349656.65584514</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>-35924670.61</v>
+        <v>-67465901.52</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
@@ -6785,27 +6785,27 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>25.2953630939842</t>
+          <t>-3.87807238678311</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>75.04202393244248</t>
+          <t>19.31984554517413</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>18.11389392834446</t>
+          <t>19.19310202755954</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6815,7 +6815,7 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>32.65</t>
+          <t>32.28</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>26928</t>
+          <t>26628</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2468.394</t>
+          <t>2354.931</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-4.46</t>
+          <t>-4.1</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-52.97</t>
+          <t>-67.98</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-7.62</t>
+          <t>-8.97</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,77 +7043,77 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>67</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>3626</t>
+          <t>2249</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>15.62</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>30.28</t>
+          <t>16.14</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-4.45</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>107.8</t>
+          <t>104.9</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>104.1</t>
+          <t>104.18</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>104.21</t>
+          <t>104.03</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>104.62</t>
+          <t>104.57</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>8.52</t>
+          <t>-25.93</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-92.14</t>
+          <t>-92.62</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,41 +7133,41 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>1686949275.130246</t>
+          <t>1684989303.348988</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>256751415.0</t>
+          <t>240787568.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>610105241.8</t>
+          <t>420099846.8</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>1297204898.4</t>
+          <t>1311901908.4</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>427732003.84</t>
+          <t>422014478.54</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-687099656</t>
+          <t>-891802061</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>151409488.9896297</t>
+          <t>122588849.0518091</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>12953117.47</v>
+        <v>-35924670.61</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7216,22 +7216,22 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>25.2953630939842</t>
+          <t>-3.87807238678311</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>75.04202393244248</t>
+          <t>19.31984554517413</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>18.11389392834446</t>
+          <t>19.19310202755954</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>32.65</t>
+          <t>32.28</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>26928</t>
+          <t>26628</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2959.424</t>
+          <t>2468.394</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-5.48</t>
+          <t>-5.64</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-30.99</t>
+          <t>-52.97</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-6.73</t>
+          <t>-7.62</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,77 +7474,77 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>67</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>3626</t>
+          <t>2249</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>32.8</t>
+          <t>15.62</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>47.93</t>
+          <t>30.28</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>-4.45</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>5.35</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>109.6</t>
+          <t>107.8</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>104.03</t>
+          <t>104.1</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>104.32</t>
+          <t>104.21</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>104.64</t>
+          <t>104.62</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>46.78</t>
+          <t>8.52</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-92.31</t>
+          <t>-92.14</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,41 +7564,41 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>1686949275.130246</t>
+          <t>1684989303.348988</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>308667678.0</t>
+          <t>256751415.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>886730504.0</t>
+          <t>610105241.8</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>1285022286.6</t>
+          <t>1297204898.4</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>427982006.44</t>
+          <t>427732003.84</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-398291782</t>
+          <t>-687099656</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>176583374.7198053</t>
+          <t>151409488.9896297</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>80605505.5</v>
+        <v>12953117.47</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7647,37 +7647,37 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>25.2953630939842</t>
+          <t>-3.87807238678311</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>75.04202393244248</t>
+          <t>19.31984554517413</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>18.11389392834446</t>
+          <t>19.19310202755954</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>32.65</t>
+          <t>32.28</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>26928</t>
+          <t>26628</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>106.5</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-4.57</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>3956.697</t>
+          <t>2959.424</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-7.0</t>
+          <t>-6.67</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>58.05</t>
+          <t>-30.99</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-5.38</t>
+          <t>-6.73</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>6.53</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,77 +7905,77 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>67</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>3626</t>
+          <t>2249</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>42.41</t>
+          <t>32.8</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>69.46</t>
+          <t>47.93</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-5.89</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>7.99</t>
+          <t>5.35</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>112.1</t>
+          <t>109.6</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>103.8</t>
+          <t>104.03</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>104.4</t>
+          <t>104.32</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>104.67</t>
+          <t>104.64</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>105.65</t>
+          <t>46.78</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-93.21</t>
+          <t>-92.31</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,41 +7995,41 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1686949275.130246</t>
+          <t>1684989303.348988</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>424561019.0</t>
+          <t>308667678.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>2014398550.8</t>
+          <t>886730504.0</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>1274536171.3</t>
+          <t>1285022286.6</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>424494347.48</t>
+          <t>427982006.44</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>739862379</t>
+          <t>-398291782</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>194033896.3962396</t>
+          <t>176583374.7198053</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>168810549.3</v>
+        <v>80605505.5</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8078,37 +8078,37 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>25.2953630939842</t>
+          <t>-3.87807238678311</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>75.04202393244248</t>
+          <t>19.31984554517413</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>18.11389392834446</t>
+          <t>19.19310202755954</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>32.65</t>
+          <t>32.28</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>26928</t>
+          <t>26628</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,22 +8158,22 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>109.5</t>
+          <t>106.5</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-4.74</t>
+          <t>-4.57</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>7756.599</t>
+          <t>3956.697</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-12.07</t>
+          <t>-8.21</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>84.41</t>
+          <t>58.05</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-5.38</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12.80</t>
+          <t>6.53</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,77 +8336,77 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>67</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>3626</t>
+          <t>2249</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>68.59</t>
+          <t>42.41</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>69.46</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-2.30</t>
+          <t>-5.89</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>9.16</t>
+          <t>7.99</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>113.1</t>
+          <t>112.1</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>103.6</t>
+          <t>103.8</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>104.44</t>
+          <t>104.4</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>104.68</t>
+          <t>104.67</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>223.35</t>
+          <t>105.65</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-95.00</t>
+          <t>-93.21</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,41 +8426,41 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>1686949275.130246</t>
+          <t>1684989303.348988</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>869731554.0</t>
+          <t>424561019.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>2310165733.8</t>
+          <t>2014398550.8</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>1252715915.0</t>
+          <t>1274536171.3</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>420881183.08</t>
+          <t>424494347.48</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>1057449818</t>
+          <t>739862379</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>198619959.5039042</t>
+          <t>194033896.3962396</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>276371662.87</v>
+        <v>168810549.3</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>8.87</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8509,37 +8509,37 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>25.2953630939842</t>
+          <t>-3.87807238678311</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>75.04202393244248</t>
+          <t>19.31984554517413</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>18.11389392834446</t>
+          <t>19.19310202755954</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>32.65</t>
+          <t>32.28</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>26928</t>
+          <t>26628</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,22 +8589,22 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>109.5</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>-4.74</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>10560.098</t>
+          <t>7756.599</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>110.5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-17.65</t>
+          <t>-13.33</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>87.89</t>
+          <t>84.41</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17.42</t>
+          <t>12.80</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>5.94</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,77 +8767,77 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>67</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>3626</t>
+          <t>2249</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>97.38</t>
+          <t>68.59</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>91.27</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>4.41</t>
+          <t>-2.30</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>7.73</t>
+          <t>9.16</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>111.1</t>
+          <t>113.1</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>103.13</t>
+          <t>103.6</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>104.35</t>
+          <t>104.44</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>104.64</t>
+          <t>104.68</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>593.93</t>
+          <t>223.35</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-97.79</t>
+          <t>-95.00</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,41 +8857,41 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>1686949275.130246</t>
+          <t>1684989303.348988</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>1190814543.0</t>
+          <t>869731554.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>2203703970.0</t>
+          <t>2310165733.8</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>1172861138.6</t>
+          <t>1252715915.0</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>406500816.74</t>
+          <t>420881183.08</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>1030842831</t>
+          <t>1057449818</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>184483286.1643741</t>
+          <t>198619959.5039042</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>372463136.97</v>
+        <v>276371662.87</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>14.29</t>
+          <t>8.87</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8940,22 +8940,22 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>25.2953630939842</t>
+          <t>-3.87807238678311</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
         <is>
-          <t>75.04202393244248</t>
+          <t>19.31984554517413</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>18.11389392834446</t>
+          <t>19.19310202755954</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
@@ -8965,12 +8965,12 @@
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>5.23</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>32.65</t>
+          <t>32.28</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>26928</t>
+          <t>26628</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,7 +9020,7 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>111.0</t>
+          <t>116.0</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
@@ -9030,12 +9030,12 @@
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>109.5</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>110.5</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>14306.024</t>
+          <t>10560.098</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>116.0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-13.59</t>
+          <t>-18.97</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>86.24</t>
+          <t>87.89</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>23.60</t>
+          <t>17.42</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>5.94</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,77 +9198,77 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>67</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>3626</t>
+          <t>2249</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>76.44</t>
+          <t>97.38</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>92.15</t>
+          <t>91.27</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>4.21</t>
+          <t>4.41</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>5.10</t>
+          <t>7.73</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>107.48</t>
+          <t>111.1</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>102.26</t>
+          <t>103.13</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>104.14</t>
+          <t>104.35</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>104.47</t>
+          <t>104.64</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>1059.40</t>
+          <t>593.93</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-101.07</t>
+          <t>-97.79</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,41 +9288,41 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>1686949275.130246</t>
+          <t>1684989303.348988</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>1639877726.0</t>
+          <t>1190814543.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>1984304555.0</t>
+          <t>2203703970.0</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>1065462599.4</t>
+          <t>1172861138.6</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>385852322.28</t>
+          <t>406500816.74</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>918841955</t>
+          <t>1030842831</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>150305131.4720843</t>
+          <t>184483286.1643741</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>462032667.69</v>
+        <v>372463136.97</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>14.29</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9371,22 +9371,22 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>25.2953630939842</t>
+          <t>-3.87807238678311</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>75.04202393244248</t>
+          <t>19.31984554517413</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>18.11389392834446</t>
+          <t>19.19310202755954</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>5.23</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>32.65</t>
+          <t>32.28</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>26928</t>
+          <t>26628</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,22 +9451,22 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>116.5</t>
+          <t>111.0</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>118.0</t>
+          <t>116.0</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>111.5</t>
+          <t>109.5</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>116.0</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>5.22</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>51029.92</t>
+          <t>14306.024</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>116.5</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-18.15</t>
+          <t>-14.87</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>84.57</t>
+          <t>86.24</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>4.48</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>84.20</t>
+          <t>23.60</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,77 +9629,77 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>67</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>3626</t>
+          <t>2249</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>76.44</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>86.93</t>
+          <t>92.15</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>4.21</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>5.10</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>104.56</t>
+          <t>107.48</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>101.57</t>
+          <t>102.26</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>103.94</t>
+          <t>104.14</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>104.37</t>
+          <t>104.47</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>263.89</t>
+          <t>1059.40</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-103.91</t>
+          <t>-101.07</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,41 +9719,41 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>1686949275.130246</t>
+          <t>1684989303.348988</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>5947007912.0</t>
+          <t>1639877726.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>1683314069.2</t>
+          <t>1984304555.0</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>912031635.6</t>
+          <t>1065462599.4</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>357502833.02</t>
+          <t>385852322.28</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>771282433</t>
+          <t>918841955</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>93627397.61461249</t>
+          <t>150305131.4720843</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>525374060.97</v>
+        <v>462032667.69</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>14.78</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9802,22 +9802,22 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>25.2953630939842</t>
+          <t>-3.87807238678311</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
         <is>
-          <t>75.04202393244248</t>
+          <t>19.31984554517413</t>
         </is>
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>18.11389392834446</t>
+          <t>19.19310202755954</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9827,12 +9827,12 @@
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.05</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>32.65</t>
+          <t>32.28</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>26928</t>
+          <t>26628</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,22 +9882,22 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>115.0</t>
+          <t>116.5</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>118.0</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>112.5</t>
+          <t>111.5</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>116.5</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>9.9</t>
+          <t>5.22</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>17569.74</t>
+          <t>51029.92</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>116.5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-12.07</t>
+          <t>-19.49</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>63.12</t>
+          <t>84.57</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>4.48</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>28.99</t>
+          <t>84.20</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>9.95</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,12 +10060,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>67</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>3626</t>
+          <t>2249</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10075,62 +10075,62 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>56.57</t>
+          <t>86.93</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>9.49</t>
+          <t>11.42</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>100.92</t>
+          <t>104.56</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>100.77</t>
+          <t>101.57</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>103.71</t>
+          <t>103.94</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>104.2</t>
+          <t>104.37</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>73.78</t>
+          <t>263.89</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-106.48</t>
+          <t>-103.91</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>1686949275.130246</t>
+          <t>1684989303.348988</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>1903396934.0</t>
+          <t>5947007912.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>534673791.8</t>
+          <t>1683314069.2</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>327782660.5</t>
+          <t>912031635.6</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>246250173.4</t>
+          <t>357502833.02</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>206891131</t>
+          <t>771282433</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>15128004.27681929</t>
+          <t>93627397.61461249</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>135620172.13</v>
+        <v>525374060.97</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>8.87</t>
+          <t>14.78</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10233,22 +10233,22 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>25.2953630939842</t>
+          <t>-3.87807238678311</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
         <is>
-          <t>75.04202393244248</t>
+          <t>19.31984554517413</t>
         </is>
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>18.11389392834446</t>
+          <t>19.19310202755954</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10258,12 +10258,12 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>32.65</t>
+          <t>32.28</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>26928</t>
+          <t>26628</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,22 +10313,22 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>115.0</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>112.5</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>116.5</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/配電系統.xlsx
+++ b/Result/checksun_type/配電系統.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>799.533</t>
+          <t>1152.161</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-58.59</t>
+          <t>-19.96</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-4.20</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-4.53</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,77 +1009,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>1152</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>68.25</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>8.47</t>
+          <t>31.22</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>10.66</t>
+          <t>11.42</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>735.4</t>
+          <t>732.4</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>701.1</t>
+          <t>708.6</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>633.54</t>
+          <t>635.96</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>634.25</t>
+          <t>635.39</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-10.78</t>
+          <t>-10.37</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>34.32</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>39.28</t>
+          <t>38.29</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-51.36</t>
+          <t>-52.59</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>4923677621.822511</t>
+          <t>4918417582.333573</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>573954733.0</t>
+          <t>848806811.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>627878031.0</t>
+          <t>688943827.4</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>1516353585.7</t>
+          <t>860708905.5</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>2106062606.14</t>
+          <t>2069337538.82</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-888475554</t>
+          <t>-171765078</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-74948604.10702263</t>
+          <t>-159759087.3581983</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-649518023.26</v>
+        <v>-626216745.24</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-8.42</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1197,22 +1197,22 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>25.49</t>
+          <t>27.04</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>51.87</t>
+          <t>55.03</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>223327</t>
+          <t>236910</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>740.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>740.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>617.266</t>
+          <t>799.533</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,72 +1324,72 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>707.0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>5.73</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>-1.42</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-58.59</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-11-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-09-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>785.0</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
           <t>738.0</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>-4.38</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>-3.09</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>-75.86</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-11-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-09-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>785.0</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>738.0</t>
-        </is>
-      </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>785.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1404,12 +1404,12 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>-5.99</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>-4.53</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,17 +1440,17 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>1152</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -1460,57 +1460,57 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>10.09</t>
+          <t>10.66</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>745.6</t>
+          <t>735.4</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>695.2</t>
+          <t>701.1</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>631.48</t>
+          <t>633.54</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>633.66</t>
+          <t>634.25</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-10.78</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>35.05</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>40.34</t>
+          <t>39.28</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-50.05</t>
+          <t>-51.36</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,45 +1530,45 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>4923677621.822511</t>
+          <t>4918417582.333573</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>453518166.0</t>
+          <t>573954733.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>696124492.8</t>
+          <t>627878031.0</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>2883970531.7</t>
+          <t>1516353585.7</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>2126707687.18</t>
+          <t>2106062606.14</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-2147483648</t>
+          <t>-888475554</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>29518563.01117429</t>
+          <t>-74948604.10702263</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-630160054.09</v>
+        <v>-649518023.26</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-4.40</t>
+          <t>-8.42</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1638,12 +1638,12 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>26.60</t>
+          <t>25.49</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>51.87</t>
+          <t>55.03</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>223327</t>
+          <t>236910</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>737.0</t>
+          <t>740.0</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>739.0</t>
+          <t>740.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>730.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>738.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1723,7 +1723,7 @@
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1116.653</t>
+          <t>617.266</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-80.90</t>
+          <t>-75.86</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>-8.03</t>
+          <t>-5.99</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,77 +1871,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>1152</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>23.47</t>
+          <t>8.47</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-3.99</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>9.29</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>10.09</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>752.0</t>
+          <t>745.6</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>688.05</t>
+          <t>695.2</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>628.72</t>
+          <t>631.48</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>632.04</t>
+          <t>633.66</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>42.23</t>
+          <t>39.85</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>40.46</t>
+          <t>40.34</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-49.89</t>
+          <t>-50.05</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,27 +1961,27 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>4923677621.822511</t>
+          <t>4918417582.333573</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>811169006.0</t>
+          <t>453518166.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>779349653.2</t>
+          <t>696124492.8</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>4079717323.9</t>
+          <t>2883970531.7</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>2168937186.34</t>
+          <t>2126707687.18</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -1991,11 +1991,11 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>149460129.7576182</t>
+          <t>29518563.01117429</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-567096178.3200001</v>
+        <v>-630160054.09</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-6.48</t>
+          <t>-4.40</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>26.03</t>
+          <t>26.60</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>51.87</t>
+          <t>55.03</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>223327</t>
+          <t>236910</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>725.0</t>
+          <t>737.0</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>736.0</t>
+          <t>739.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>730.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1008.586</t>
+          <t>1116.653</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>745.0</t>
+          <t>722.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-5.37</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-82.40</t>
+          <t>-80.90</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>-5.10</t>
+          <t>-8.03</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,12 +2302,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>1152</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2317,62 +2317,62 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>49.94</t>
+          <t>23.47</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-3.99</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>11.02</t>
+          <t>9.29</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>8.78</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>756.8</t>
+          <t>752.0</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>681.7</t>
+          <t>688.05</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>626.7</t>
+          <t>628.72</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>630.91</t>
+          <t>632.04</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>15.69</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>46.30</t>
+          <t>42.23</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>40.02</t>
+          <t>40.46</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-50.44</t>
+          <t>-49.89</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,27 +2392,27 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>4923677621.822511</t>
+          <t>4918417582.333573</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>757270421.0</t>
+          <t>811169006.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>855936440.6</t>
+          <t>779349653.2</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>4864530439.2</t>
+          <t>4079717323.9</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>2227082877.5</t>
+          <t>2168937186.34</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -2422,11 +2422,11 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>279743094.8631054</t>
+          <t>149460129.7576182</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-495071225.14</v>
+        <v>-567096178.3200001</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-3.50</t>
+          <t>-6.48</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2495,17 +2495,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>26.86</t>
+          <t>26.03</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>51.87</t>
+          <t>55.03</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>223327</t>
+          <t>236910</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>769.0</t>
+          <t>725.0</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>769.0</t>
+          <t>736.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>737.0</t>
+          <t>722.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>745.0</t>
+          <t>722.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2585,7 +2585,7 @@
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>711.087</t>
+          <t>1008.586</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>765.0</t>
+          <t>745.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-8.2</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-81.30</t>
+          <t>-82.40</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2697,12 +2697,12 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-5.10</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,77 +2733,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>1152</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>70.42</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>80.35</t>
+          <t>49.94</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>13.05</t>
+          <t>11.02</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>8.78</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>760.8</t>
+          <t>756.8</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>673.0</t>
+          <t>681.7</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>624.74</t>
+          <t>626.7</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>629.5</t>
+          <t>630.91</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>26.07</t>
+          <t>15.69</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>48.47</t>
+          <t>46.30</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>38.45</t>
+          <t>40.02</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-52.39</t>
+          <t>-50.44</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,27 +2823,27 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>4923677621.822511</t>
+          <t>4918417582.333573</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>543477829.0</t>
+          <t>757270421.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>1032473983.6</t>
+          <t>855936440.6</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>5522062366.6</t>
+          <t>4864530439.2</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>2292721646.52</t>
+          <t>2227082877.5</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -2853,11 +2853,11 @@
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>420618425.772247</t>
+          <t>279743094.8631054</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-368722471.3</v>
+        <v>-495071225.14</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-3.50</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>27.58</t>
+          <t>26.86</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>51.87</t>
+          <t>55.03</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>223327</t>
+          <t>236910</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>765.0</t>
+          <t>769.0</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>770.0</t>
+          <t>769.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>759.0</t>
+          <t>737.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>765.0</t>
+          <t>745.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1193.09</t>
+          <t>711.087</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>758.0</t>
+          <t>765.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-7.21</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-57.71</t>
+          <t>-81.30</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3128,12 +3128,12 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.90</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3164,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>1152</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>79.41</t>
+          <t>70.42</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>82.88</t>
+          <t>80.35</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>15.48</t>
+          <t>13.05</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>6.51</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>764.8</t>
+          <t>760.8</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>662.3</t>
+          <t>673.0</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>621.8</t>
+          <t>624.74</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>627.64</t>
+          <t>629.5</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>34.94</t>
+          <t>26.07</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>48.50</t>
+          <t>48.47</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>35.94</t>
+          <t>38.45</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-55.49</t>
+          <t>-52.39</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,27 +3254,27 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>4923677621.822511</t>
+          <t>4918417582.333573</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>915187042.0</t>
+          <t>543477829.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>2404829140.4</t>
+          <t>1032473983.6</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>5686609711.2</t>
+          <t>5522062366.6</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>2312774767.92</t>
+          <t>2292721646.52</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
@@ -3284,11 +3284,11 @@
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>564134952.5119295</t>
+          <t>420618425.772247</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-152149242.69</v>
+        <v>-368722471.3</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>27.33</t>
+          <t>27.58</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>51.87</t>
+          <t>55.03</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>223327</t>
+          <t>236910</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>775.0</t>
+          <t>765.0</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>780.0</t>
+          <t>770.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>758.0</t>
+          <t>759.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>758.0</t>
+          <t>765.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1144.535</t>
+          <t>1193.09</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>770.0</t>
+          <t>758.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-8.91</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-15.19</t>
+          <t>-57.71</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>-2.90</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3595,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>1152</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>91.21</t>
+          <t>79.41</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>86.14</t>
+          <t>82.88</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>17.70</t>
+          <t>15.48</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>5.32</t>
+          <t>6.51</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>767.6</t>
+          <t>764.8</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>652.15</t>
+          <t>662.3</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>619.2</t>
+          <t>621.8</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>625.75</t>
+          <t>627.64</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>48.00</t>
+          <t>34.94</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>48.55</t>
+          <t>48.50</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>32.80</t>
+          <t>35.94</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-59.38</t>
+          <t>-55.49</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>4923677621.822511</t>
+          <t>4918417582.333573</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>869643968.0</t>
+          <t>915187042.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>5071816570.6</t>
+          <t>2404829140.4</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>5980378748.8</t>
+          <t>5686609711.2</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>2324099002.48</t>
+          <t>2312774767.92</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-908562178</t>
+          <t>-2147483648</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>694368442.54881</t>
+          <t>564134952.5119295</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>122848998.31</v>
+        <v>-152149242.69</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3783,22 +3783,22 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>27.76</t>
+          <t>27.33</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>51.87</t>
+          <t>55.03</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>223327</t>
+          <t>236910</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>765.0</t>
+          <t>775.0</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>770.0</t>
+          <t>780.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>758.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>770.0</t>
+          <t>758.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3878,7 +3878,7 @@
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1587.408</t>
+          <t>1144.535</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>746.0</t>
+          <t>770.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-5.52</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>23.64</t>
+          <t>-15.19</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3990,12 +3990,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>-4.97</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>1152</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>78.02</t>
+          <t>91.21</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>88.9</t>
+          <t>86.14</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>20.18</t>
+          <t>17.70</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>770.8</t>
+          <t>767.6</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>641.35</t>
+          <t>652.15</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>616.0</t>
+          <t>619.2</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>624.02</t>
+          <t>625.75</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>61.71</t>
+          <t>48.00</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>46.68</t>
+          <t>48.55</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>28.87</t>
+          <t>32.80</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-64.25</t>
+          <t>-59.38</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>4923677621.822511</t>
+          <t>4918417582.333573</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>1194102943.0</t>
+          <t>869643968.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>7380084994.6</t>
+          <t>5071816570.6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>5968914067.6</t>
+          <t>5980378748.8</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>2329253341.64</t>
+          <t>2324099002.48</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>1411170927</t>
+          <t>-908562178</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>798281068.7748979</t>
+          <t>694368442.54881</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>516195779.15</v>
+        <v>122848998.31</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4224,12 +4224,12 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>26.89</t>
+          <t>27.76</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>51.87</t>
+          <t>55.03</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>223327</t>
+          <t>236910</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>755.0</t>
+          <t>765.0</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>774.0</t>
+          <t>770.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>743.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>746.0</t>
+          <t>770.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4309,7 +4309,7 @@
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2119.821</t>
+          <t>1587.408</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>765.0</t>
+          <t>746.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-8.2</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>49.26</t>
+          <t>23.64</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4421,12 +4421,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-4.97</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,98 +4436,98 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>1152</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>89.18</t>
+          <t>78.02</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>93.92</t>
+          <t>88.9</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>20.88</t>
+          <t>20.18</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>764.6</t>
+          <t>770.8</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>632.55</t>
+          <t>641.35</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>613.28</t>
+          <t>616.0</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>622.34</t>
+          <t>624.02</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>88.66</t>
+          <t>61.71</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>46.06</t>
+          <t>46.68</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>24.41</t>
+          <t>28.87</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-69.77</t>
+          <t>-64.25</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>4923677621.822511</t>
+          <t>4918417582.333573</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>1639958136.0</t>
+          <t>1194102943.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>8873124437.8</t>
+          <t>7380084994.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>5944629753.8</t>
+          <t>5968914067.6</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>2333052998.56</t>
+          <t>2329253341.64</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-2147483648</t>
+          <t>1411170927</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>849569303.2528446</t>
+          <t>798281068.7748979</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>1024920726.63</v>
+        <v>516195779.15</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>27.58</t>
+          <t>26.89</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>51.87</t>
+          <t>55.03</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>223327</t>
+          <t>236910</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>785.0</t>
+          <t>755.0</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>785.0</t>
+          <t>774.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>765.0</t>
+          <t>743.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>765.0</t>
+          <t>746.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4740,7 +4740,7 @@
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>9688.689</t>
+          <t>2119.821</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,74 +4772,74 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>765.0</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>-1.42</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>49.26</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2025-11-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-09-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>785.0</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>-11.03</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>-3.09</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>70.54</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2025-11-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-09-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>738.0</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
         <is>
           <t>785.0</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>738.0</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>785.0</t>
-        </is>
-      </c>
       <c r="T11" t="inlineStr">
         <is>
           <t>624.0</t>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>6.37</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>34.55</t>
+          <t>7.56</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>5.41</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4888,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>1152</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>99.5</t>
+          <t>89.18</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>97.52</t>
+          <t>93.92</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>5.85</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>20.88</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>741.6</t>
+          <t>764.6</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>623.0</t>
+          <t>632.55</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>609.92</t>
+          <t>613.28</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>620.01</t>
+          <t>622.34</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>124.51</t>
+          <t>88.66</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>42.66</t>
+          <t>46.06</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>24.41</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-76.47</t>
+          <t>-69.77</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,27 +4978,27 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>4923677621.822511</t>
+          <t>4918417582.333573</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>7405253613.0</t>
+          <t>1639958136.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>10011650749.6</t>
+          <t>8873124437.8</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>5870589709.3</t>
+          <t>5944629753.8</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>2337679186.88</t>
+          <t>2333052998.56</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
@@ -5008,11 +5008,11 @@
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>817687226.2755579</t>
+          <t>849569303.2528446</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>1667296140.69</v>
+        <v>1024920726.63</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>28.30</t>
+          <t>27.58</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>51.87</t>
+          <t>55.03</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>223327</t>
+          <t>236910</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>748.0</t>
+          <t>785.0</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>788.0</t>
+          <t>785.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>742.0</t>
+          <t>765.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>785.0</t>
+          <t>765.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>18118.77</t>
+          <t>9688.689</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>772.0</t>
+          <t>785.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,22 +5213,22 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-9.19</t>
+          <t>-4.67</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>69.40</t>
+          <t>70.54</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>785.0</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>6.37</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>64.61</t>
+          <t>34.55</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>5.41</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5319,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>1152</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>93.07</t>
+          <t>99.5</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>97.69</t>
+          <t>97.52</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>5.85</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>15.20</t>
+          <t>19.04</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>705.4</t>
+          <t>741.6</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>612.35</t>
+          <t>623.0</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>606.42</t>
+          <t>609.92</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>617.41</t>
+          <t>620.01</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>172.56</t>
+          <t>124.51</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>35.67</t>
+          <t>42.66</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>13.09</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-83.79</t>
+          <t>-76.47</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,27 +5409,27 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>4923677621.822511</t>
+          <t>4918417582.333573</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>14250124193.0</t>
+          <t>7405253613.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>8968390282.0</t>
+          <t>10011650749.6</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>5294074253.1</t>
+          <t>5870589709.3</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>2221550552.1</t>
+          <t>2337679186.88</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
@@ -5439,15 +5439,15 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>663212878.2008342</t>
+          <t>817687226.2755579</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>1907718783.21</v>
+        <v>1667296140.69</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>27.83</t>
+          <t>28.30</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>51.87</t>
+          <t>55.03</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>223327</t>
+          <t>236910</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>800.0</t>
+          <t>748.0</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>816.0</t>
+          <t>788.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>763.0</t>
+          <t>742.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>772.0</t>
+          <t>785.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5602,7 +5602,7 @@
       </c>
       <c r="CI12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3012.776</t>
+          <t>2950.547</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-37.86</t>
+          <t>-19.47</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-13.63</t>
+          <t>-14.62</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,12 +5750,12 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>73</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>3013</t>
+          <t>2951</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5770,57 +5770,57 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-5.20</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>99.08000000000001</t>
+          <t>97.82</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>103.19</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>103.2</t>
+          <t>102.95</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>104.3</t>
+          <t>104.19</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-667.15</t>
+          <t>-887.49</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-98.76</t>
+          <t>-101.02</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,41 +5840,41 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>1683183974.582251</t>
+          <t>1681366999.147694</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>289264312.0</t>
+          <t>281468682.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>275009623.6</t>
+          <t>283145846.4</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>442557432.7</t>
+          <t>351622846.6</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>412480726.12</t>
+          <t>414970230.06</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-167547809</t>
+          <t>-68477000</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>18984900.35753776</t>
+          <t>-15789.41195628047</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>-103171216.51</v>
+        <v>-104519583.14</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-5.12</t>
+          <t>-6.21</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5938,7 +5938,7 @@
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
@@ -5948,12 +5948,12 @@
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>31.89</t>
+          <t>31.52</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>26300</t>
+          <t>26000</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>97.2</t>
+          <t>97.9</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>94.1</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2248.507</t>
+          <t>3012.776</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>96.3</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-53.51</t>
+          <t>-37.86</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-12.56</t>
+          <t>-13.63</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,12 +6181,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>73</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>3013</t>
+          <t>2951</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -6216,42 +6216,42 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>100.42</t>
+          <t>99.08000000000001</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>103.72</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>103.4</t>
+          <t>103.2</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>104.41</t>
+          <t>104.3</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-215.80</t>
+          <t>-667.15</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-96.68</t>
+          <t>-98.76</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,41 +6271,41 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>1683183974.582251</t>
+          <t>1681366999.147694</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>220432535.0</t>
+          <t>289264312.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>268507044.2</t>
+          <t>275009623.6</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>577618774.1</t>
+          <t>442557432.7</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>409190484.56</t>
+          <t>412480726.12</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-309111729</t>
+          <t>-167547809</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>41195103.42357187</t>
+          <t>18984900.35753776</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>-98395538.22</v>
+        <v>-103171216.51</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-3.94</t>
+          <t>-5.12</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
@@ -6379,12 +6379,12 @@
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>4.40</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>31.89</t>
+          <t>31.52</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>26300</t>
+          <t>26000</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>99.2</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>97.2</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>97.2</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>96.3</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-2.9</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>3626.375</t>
+          <t>2248.507</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,17 +6506,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-75.12</t>
+          <t>-53.51</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-11.57</t>
+          <t>-12.56</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6591,33 +6591,33 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>5.98</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>73</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>3013</t>
+          <t>2951</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6632,57 +6632,57 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>101.72</t>
+          <t>100.42</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>103.96</t>
+          <t>103.72</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>103.6</t>
+          <t>103.4</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>104.44</t>
+          <t>104.41</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-109.91</t>
+          <t>-215.80</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-94.89</t>
+          <t>-96.68</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,41 +6702,41 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>1683183974.582251</t>
+          <t>1681366999.147694</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>360108082.0</t>
+          <t>220432535.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>286154072.8</t>
+          <t>268507044.2</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>1150276311.8</t>
+          <t>577618774.1</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>408529389.62</t>
+          <t>409190484.56</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-864122239</t>
+          <t>-309111729</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>66575220.08572514</t>
+          <t>41195103.42357187</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>-80684181.05</v>
+        <v>-98395538.22</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-2.86</t>
+          <t>-3.94</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6800,7 +6800,7 @@
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>4.40</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>31.89</t>
+          <t>31.52</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>26300</t>
+          <t>26000</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>99.2</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>99.6</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>97.2</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2607.704</t>
+          <t>3626.375</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-5.4</t>
+          <t>-3.57</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-77.08</t>
+          <t>-75.12</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-8.97</t>
+          <t>-11.57</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7022,33 +7022,33 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>5.98</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>73</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>3013</t>
+          <t>2951</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7058,62 +7058,62 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>5.21</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>103.1</t>
+          <t>101.72</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>104.18</t>
+          <t>103.96</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>103.79</t>
+          <t>103.6</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>104.52</t>
+          <t>104.44</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-53.80</t>
+          <t>-109.91</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-93.49</t>
+          <t>-94.89</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,41 +7133,41 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>1683183974.582251</t>
+          <t>1681366999.147694</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>264455621.0</t>
+          <t>360108082.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>299044660.2</t>
+          <t>286154072.8</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>1304605197.0</t>
+          <t>1150276311.8</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>411510598.5</t>
+          <t>408529389.62</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-1005560536</t>
+          <t>-864122239</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>93349656.65584514</t>
+          <t>66575220.08572514</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>-67465901.52</v>
+        <v>-80684181.05</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.86</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>31.89</t>
+          <t>31.52</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>26300</t>
+          <t>26000</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2354.931</t>
+          <t>2607.704</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-5.4</t>
+          <t>-6.62</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-67.98</t>
+          <t>-77.08</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>3.89</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,12 +7474,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>73</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>3013</t>
+          <t>2951</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7489,32 +7489,32 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>16.14</t>
+          <t>5.21</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>104.9</t>
+          <t>103.1</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -7524,27 +7524,27 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>104.03</t>
+          <t>103.79</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>104.57</t>
+          <t>104.52</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-25.93</t>
+          <t>-53.80</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-92.62</t>
+          <t>-93.49</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,41 +7564,41 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>1683183974.582251</t>
+          <t>1681366999.147694</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>240787568.0</t>
+          <t>264455621.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>420099846.8</t>
+          <t>299044660.2</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>1311901908.4</t>
+          <t>1304605197.0</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>422014478.54</t>
+          <t>411510598.5</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-891802061</t>
+          <t>-1005560536</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>122588849.0518091</t>
+          <t>93349656.65584514</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>-35924670.61</v>
+        <v>-67465901.52</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7662,12 +7662,12 @@
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7677,7 +7677,7 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>31.89</t>
+          <t>31.52</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>26300</t>
+          <t>26000</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,17 +7727,17 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2468.394</t>
+          <t>2354.931</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-6.96</t>
+          <t>-6.62</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-52.97</t>
+          <t>-67.98</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-7.62</t>
+          <t>-8.97</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,77 +7905,77 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>73</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>3013</t>
+          <t>2951</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>15.62</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>30.28</t>
+          <t>16.14</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-4.45</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>107.8</t>
+          <t>104.9</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>104.1</t>
+          <t>104.18</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>104.21</t>
+          <t>104.03</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>104.62</t>
+          <t>104.57</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>8.52</t>
+          <t>-25.93</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-92.14</t>
+          <t>-92.62</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,41 +7995,41 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1683183974.582251</t>
+          <t>1681366999.147694</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>256751415.0</t>
+          <t>240787568.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>610105241.8</t>
+          <t>420099846.8</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>1297204898.4</t>
+          <t>1311901908.4</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>427732003.84</t>
+          <t>422014478.54</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-687099656</t>
+          <t>-891802061</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>151409488.9896297</t>
+          <t>122588849.0518091</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>12953117.47</v>
+        <v>-35924670.61</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8093,7 +8093,7 @@
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
@@ -8103,12 +8103,12 @@
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>31.89</t>
+          <t>31.52</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>26300</t>
+          <t>26000</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,22 +8158,22 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2959.424</t>
+          <t>2468.394</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-8.0</t>
+          <t>-8.19</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-30.99</t>
+          <t>-52.97</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-6.73</t>
+          <t>-7.62</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,77 +8336,77 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>73</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>3013</t>
+          <t>2951</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>32.8</t>
+          <t>15.62</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>47.93</t>
+          <t>30.28</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>-4.45</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>5.35</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>109.6</t>
+          <t>107.8</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>104.03</t>
+          <t>104.1</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>104.32</t>
+          <t>104.21</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>104.64</t>
+          <t>104.62</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>46.78</t>
+          <t>8.52</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-92.31</t>
+          <t>-92.14</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,41 +8426,41 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>1683183974.582251</t>
+          <t>1681366999.147694</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>308667678.0</t>
+          <t>256751415.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>886730504.0</t>
+          <t>610105241.8</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>1285022286.6</t>
+          <t>1297204898.4</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>427982006.44</t>
+          <t>427732003.84</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-398291782</t>
+          <t>-687099656</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>176583374.7198053</t>
+          <t>151409488.9896297</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>80605505.5</v>
+        <v>12953117.47</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8524,22 +8524,22 @@
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>31.89</t>
+          <t>31.52</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>26300</t>
+          <t>26000</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,22 +8589,22 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>106.5</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-4.57</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3956.697</t>
+          <t>2959.424</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-9.55</t>
+          <t>-9.24</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>58.05</t>
+          <t>-30.99</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-5.38</t>
+          <t>-6.73</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>6.53</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,177 +8767,177 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>73</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>3013</t>
+          <t>2951</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>42.41</t>
+          <t>32.8</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>69.46</t>
+          <t>47.93</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-5.89</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>7.99</t>
+          <t>5.35</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>112.1</t>
+          <t>109.6</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>103.8</t>
+          <t>104.03</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>104.4</t>
+          <t>104.32</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>104.67</t>
+          <t>104.64</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>105.65</t>
+          <t>46.78</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
+          <t>1.15</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>14.93</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr">
+        <is>
+          <t>-92.31</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>2025/10/31</t>
+        </is>
+      </c>
+      <c r="AV20" t="inlineStr">
+        <is>
+          <t>1681366999.147694</t>
+        </is>
+      </c>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>308667678.0</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>886730504.0</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>1285022286.6</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>427982006.44</t>
+        </is>
+      </c>
+      <c r="BA20" t="inlineStr">
+        <is>
+          <t>-398291782</t>
+        </is>
+      </c>
+      <c r="BB20" t="inlineStr">
+        <is>
+          <t>176583374.7198053</t>
+        </is>
+      </c>
+      <c r="BC20" t="n">
+        <v>80605505.5</v>
+      </c>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE20" t="inlineStr">
+        <is>
+          <t>101.5</t>
+        </is>
+      </c>
+      <c r="BF20" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="BG20" t="inlineStr">
+        <is>
+          <t>2.46</t>
+        </is>
+      </c>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>亞力</t>
+        </is>
+      </c>
+      <c r="BI20" t="inlineStr">
+        <is>
+          <t>亞力</t>
+        </is>
+      </c>
+      <c r="BJ20" t="inlineStr">
+        <is>
+          <t>電機機械</t>
+        </is>
+      </c>
+      <c r="BK20" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL20" t="inlineStr">
+        <is>
           <t>1.01</t>
         </is>
       </c>
-      <c r="AS20" t="inlineStr">
-        <is>
-          <t>14.93</t>
-        </is>
-      </c>
-      <c r="AT20" t="inlineStr">
-        <is>
-          <t>-93.21</t>
-        </is>
-      </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>2025/10/31</t>
-        </is>
-      </c>
-      <c r="AV20" t="inlineStr">
-        <is>
-          <t>1683183974.582251</t>
-        </is>
-      </c>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t>424561019.0</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>2014398550.8</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>1274536171.3</t>
-        </is>
-      </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>424494347.48</t>
-        </is>
-      </c>
-      <c r="BA20" t="inlineStr">
-        <is>
-          <t>739862379</t>
-        </is>
-      </c>
-      <c r="BB20" t="inlineStr">
-        <is>
-          <t>194033896.3962396</t>
-        </is>
-      </c>
-      <c r="BC20" t="n">
-        <v>168810549.3</v>
-      </c>
-      <c r="BD20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE20" t="inlineStr">
-        <is>
-          <t>101.5</t>
-        </is>
-      </c>
-      <c r="BF20" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="BG20" t="inlineStr">
-        <is>
-          <t>3.94</t>
-        </is>
-      </c>
-      <c r="BH20" t="inlineStr">
-        <is>
-          <t>亞力</t>
-        </is>
-      </c>
-      <c r="BI20" t="inlineStr">
-        <is>
-          <t>亞力</t>
-        </is>
-      </c>
-      <c r="BJ20" t="inlineStr">
-        <is>
-          <t>電機機械</t>
-        </is>
-      </c>
-      <c r="BK20" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL20" t="inlineStr">
-        <is>
-          <t>1.01</t>
-        </is>
-      </c>
       <c r="BM20" t="inlineStr">
         <is>
           <t>-3.87807238678311</t>
@@ -8955,22 +8955,22 @@
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>31.89</t>
+          <t>31.52</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>26300</t>
+          <t>26000</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>109.5</t>
+          <t>106.5</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-4.74</t>
+          <t>-4.57</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>7756.599</t>
+          <t>3956.697</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-14.75</t>
+          <t>-10.82</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>84.41</t>
+          <t>58.05</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-5.38</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12.80</t>
+          <t>6.53</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,77 +9198,77 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>73</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>3013</t>
+          <t>2951</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>68.59</t>
+          <t>42.41</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>69.46</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-2.30</t>
+          <t>-5.89</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>9.16</t>
+          <t>7.99</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>113.1</t>
+          <t>112.1</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>103.6</t>
+          <t>103.8</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>104.44</t>
+          <t>104.4</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>104.68</t>
+          <t>104.67</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>223.35</t>
+          <t>105.65</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-95.00</t>
+          <t>-93.21</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,41 +9288,41 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>1683183974.582251</t>
+          <t>1681366999.147694</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>869731554.0</t>
+          <t>424561019.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>2310165733.8</t>
+          <t>2014398550.8</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>1252715915.0</t>
+          <t>1274536171.3</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>420881183.08</t>
+          <t>424494347.48</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>1057449818</t>
+          <t>739862379</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>198619959.5039042</t>
+          <t>194033896.3962396</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>276371662.87</v>
+        <v>168810549.3</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>8.87</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>31.89</t>
+          <t>31.52</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>26300</t>
+          <t>26000</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,22 +9451,22 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>109.5</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>-4.74</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>10560.098</t>
+          <t>7756.599</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>110.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-20.46</t>
+          <t>-16.07</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>87.89</t>
+          <t>84.41</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17.42</t>
+          <t>12.80</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>5.94</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,77 +9629,77 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>73</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>3013</t>
+          <t>2951</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>97.38</t>
+          <t>68.59</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>91.27</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>4.41</t>
+          <t>-2.30</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>7.73</t>
+          <t>9.16</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>111.1</t>
+          <t>113.1</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>103.13</t>
+          <t>103.6</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>104.35</t>
+          <t>104.44</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>104.64</t>
+          <t>104.68</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>593.93</t>
+          <t>223.35</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-97.79</t>
+          <t>-95.00</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,41 +9719,41 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>1683183974.582251</t>
+          <t>1681366999.147694</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>1190814543.0</t>
+          <t>869731554.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>2203703970.0</t>
+          <t>2310165733.8</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>1172861138.6</t>
+          <t>1252715915.0</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>406500816.74</t>
+          <t>420881183.08</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>1030842831</t>
+          <t>1057449818</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>184483286.1643741</t>
+          <t>198619959.5039042</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>372463136.97</v>
+        <v>276371662.87</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>14.29</t>
+          <t>8.87</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9827,12 +9827,12 @@
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>5.23</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>31.89</t>
+          <t>31.52</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>26300</t>
+          <t>26000</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,7 +9882,7 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>111.0</t>
+          <t>116.0</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
@@ -9892,12 +9892,12 @@
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>109.5</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>110.5</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>14306.024</t>
+          <t>10560.098</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>116.0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-16.3</t>
+          <t>-21.85</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>86.24</t>
+          <t>87.89</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>23.60</t>
+          <t>17.42</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>5.94</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,77 +10060,77 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>73</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>3013</t>
+          <t>2951</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>76.44</t>
+          <t>97.38</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>92.15</t>
+          <t>91.27</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>4.21</t>
+          <t>4.41</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>5.10</t>
+          <t>7.73</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>107.48</t>
+          <t>111.1</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>102.26</t>
+          <t>103.13</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>104.14</t>
+          <t>104.35</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>104.47</t>
+          <t>104.64</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>1059.40</t>
+          <t>593.93</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-101.07</t>
+          <t>-97.79</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>1683183974.582251</t>
+          <t>1681366999.147694</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>1639877726.0</t>
+          <t>1190814543.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>1984304555.0</t>
+          <t>2203703970.0</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>1065462599.4</t>
+          <t>1172861138.6</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>385852322.28</t>
+          <t>406500816.74</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>918841955</t>
+          <t>1030842831</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>150305131.4720843</t>
+          <t>184483286.1643741</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>462032667.69</v>
+        <v>372463136.97</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>14.29</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10258,12 +10258,12 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>5.23</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>31.89</t>
+          <t>31.52</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>26300</t>
+          <t>26000</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,22 +10313,22 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>116.5</t>
+          <t>111.0</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>118.0</t>
+          <t>116.0</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>111.5</t>
+          <t>109.5</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>116.0</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/配電系統.xlsx
+++ b/Result/checksun_type/配電系統.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1152.161</t>
+          <t>7500.722</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>739.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-4.37</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-19.96</t>
+          <t>32.75</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>26.75</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>-7.70</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,77 +1009,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>282</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1152</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>68.25</t>
+          <t>50.79</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>31.22</t>
+          <t>39.68</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>732.4</t>
+          <t>731.2</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>708.6</t>
+          <t>715.55</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>635.96</t>
+          <t>638.3</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>635.39</t>
+          <t>636.88</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-10.37</t>
+          <t>-12.52</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>34.32</t>
+          <t>32.48</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>38.29</t>
+          <t>37.13</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-52.59</t>
+          <t>-54.03</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>4918417582.333573</t>
+          <t>4923771953.88777</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>848806811.0</t>
+          <t>5759803875.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>688943827.4</t>
+          <t>1689450518.2</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>860708905.5</t>
+          <t>1272693479.4</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>2069337538.82</t>
+          <t>2149905312.46</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-171765078</t>
+          <t>416757038</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-159759087.3581983</t>
+          <t>-169938558.8717777</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-626216745.24</v>
+        <v>-225925652.2</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1197,22 +1197,22 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>27.04</t>
+          <t>26.64</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>55.03</t>
+          <t>54.22</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.81</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>236910</t>
+          <t>233435</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>789.0</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>803.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>732.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>739.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>799.533</t>
+          <t>1152.161</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-4.37</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-58.59</t>
+          <t>-19.96</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-4.20</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-4.53</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,77 +1440,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>282</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1152</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>68.25</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>8.47</t>
+          <t>31.22</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>10.66</t>
+          <t>11.42</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>735.4</t>
+          <t>732.4</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>701.1</t>
+          <t>708.6</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>633.54</t>
+          <t>635.96</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>634.25</t>
+          <t>635.39</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-10.78</t>
+          <t>-10.37</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>34.32</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>39.28</t>
+          <t>38.29</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-51.36</t>
+          <t>-52.59</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>4918417582.333573</t>
+          <t>4923771953.88777</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>573954733.0</t>
+          <t>848806811.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>627878031.0</t>
+          <t>688943827.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>1516353585.7</t>
+          <t>860708905.5</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>2106062606.14</t>
+          <t>2069337538.82</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-888475554</t>
+          <t>-171765078</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-74948604.10702263</t>
+          <t>-159759087.3581983</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-649518023.26</v>
+        <v>-626216745.24</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-8.42</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1628,22 +1628,22 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>25.49</t>
+          <t>27.04</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>55.03</t>
+          <t>54.22</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.81</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>236910</t>
+          <t>233435</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>740.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>740.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>617.266</t>
+          <t>799.533</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,72 +1755,72 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>707.0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>-4.37</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>-58.59</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-11-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-09-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>785.0</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
           <t>738.0</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>1.6</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>-1.42</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>-75.86</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2025-11-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-09-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>785.0</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>738.0</t>
-        </is>
-      </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>785.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>-5.99</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>-4.53</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,17 +1871,17 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>282</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1152</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1891,57 +1891,57 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>10.09</t>
+          <t>10.66</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>745.6</t>
+          <t>735.4</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>695.2</t>
+          <t>701.1</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>631.48</t>
+          <t>633.54</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>633.66</t>
+          <t>634.25</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-10.78</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>35.05</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>40.34</t>
+          <t>39.28</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-50.05</t>
+          <t>-51.36</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,45 +1961,45 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>4918417582.333573</t>
+          <t>4923771953.88777</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>453518166.0</t>
+          <t>573954733.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>696124492.8</t>
+          <t>627878031.0</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>2883970531.7</t>
+          <t>1516353585.7</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>2126707687.18</t>
+          <t>2106062606.14</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-2147483648</t>
+          <t>-888475554</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>29518563.01117429</t>
+          <t>-74948604.10702263</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-630160054.09</v>
+        <v>-649518023.26</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-4.40</t>
+          <t>-8.42</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>26.60</t>
+          <t>25.49</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>55.03</t>
+          <t>54.22</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.81</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>236910</t>
+          <t>233435</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>737.0</t>
+          <t>740.0</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>739.0</t>
+          <t>740.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>730.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>738.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1116.653</t>
+          <t>617.266</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-4.37</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-80.90</t>
+          <t>-75.86</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>-8.03</t>
+          <t>-5.99</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,77 +2302,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>282</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1152</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>23.47</t>
+          <t>8.47</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-3.99</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>9.29</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>10.09</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>752.0</t>
+          <t>745.6</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>688.05</t>
+          <t>695.2</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>628.72</t>
+          <t>631.48</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>632.04</t>
+          <t>633.66</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>42.23</t>
+          <t>39.85</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>40.46</t>
+          <t>40.34</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-49.89</t>
+          <t>-50.05</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,27 +2392,27 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>4918417582.333573</t>
+          <t>4923771953.88777</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>811169006.0</t>
+          <t>453518166.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>779349653.2</t>
+          <t>696124492.8</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>4079717323.9</t>
+          <t>2883970531.7</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>2168937186.34</t>
+          <t>2126707687.18</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -2422,11 +2422,11 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>149460129.7576182</t>
+          <t>29518563.01117429</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-567096178.3200001</v>
+        <v>-630160054.09</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-6.48</t>
+          <t>-4.40</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2500,12 +2500,12 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>26.03</t>
+          <t>26.60</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>55.03</t>
+          <t>54.22</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.81</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>236910</t>
+          <t>233435</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>725.0</t>
+          <t>737.0</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>736.0</t>
+          <t>739.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>730.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1008.586</t>
+          <t>1116.653</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>745.0</t>
+          <t>722.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-4.37</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-82.40</t>
+          <t>-80.90</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2697,12 +2697,12 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>-5.10</t>
+          <t>-8.03</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,12 +2733,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>282</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1152</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2748,62 +2748,62 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>49.94</t>
+          <t>23.47</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-3.99</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>11.02</t>
+          <t>9.29</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>8.78</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>756.8</t>
+          <t>752.0</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>681.7</t>
+          <t>688.05</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>626.7</t>
+          <t>628.72</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>630.91</t>
+          <t>632.04</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>15.69</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>46.30</t>
+          <t>42.23</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>40.02</t>
+          <t>40.46</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-50.44</t>
+          <t>-49.89</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,27 +2823,27 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>4918417582.333573</t>
+          <t>4923771953.88777</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>757270421.0</t>
+          <t>811169006.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>855936440.6</t>
+          <t>779349653.2</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>4864530439.2</t>
+          <t>4079717323.9</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>2227082877.5</t>
+          <t>2168937186.34</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -2853,11 +2853,11 @@
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>279743094.8631054</t>
+          <t>149460129.7576182</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-495071225.14</v>
+        <v>-567096178.3200001</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-3.50</t>
+          <t>-6.48</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -2926,17 +2926,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>26.86</t>
+          <t>26.03</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>55.03</t>
+          <t>54.22</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.81</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>236910</t>
+          <t>233435</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>769.0</t>
+          <t>725.0</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>769.0</t>
+          <t>736.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>737.0</t>
+          <t>722.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>745.0</t>
+          <t>722.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>711.087</t>
+          <t>1008.586</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>765.0</t>
+          <t>745.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-4.37</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-81.30</t>
+          <t>-82.40</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3128,12 +3128,12 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-5.10</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3164,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>282</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1152</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>70.42</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>80.35</t>
+          <t>49.94</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>13.05</t>
+          <t>11.02</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>8.78</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>760.8</t>
+          <t>756.8</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>673.0</t>
+          <t>681.7</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>624.74</t>
+          <t>626.7</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>629.5</t>
+          <t>630.91</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>26.07</t>
+          <t>15.69</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>48.47</t>
+          <t>46.30</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>38.45</t>
+          <t>40.02</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-52.39</t>
+          <t>-50.44</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,27 +3254,27 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>4918417582.333573</t>
+          <t>4923771953.88777</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>543477829.0</t>
+          <t>757270421.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>1032473983.6</t>
+          <t>855936440.6</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>5522062366.6</t>
+          <t>4864530439.2</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>2292721646.52</t>
+          <t>2227082877.5</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
@@ -3284,11 +3284,11 @@
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>420618425.772247</t>
+          <t>279743094.8631054</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-368722471.3</v>
+        <v>-495071225.14</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-3.50</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -3352,22 +3352,22 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>27.58</t>
+          <t>26.86</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>55.03</t>
+          <t>54.22</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.81</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>236910</t>
+          <t>233435</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>765.0</t>
+          <t>769.0</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>770.0</t>
+          <t>769.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>759.0</t>
+          <t>737.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>765.0</t>
+          <t>745.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1193.09</t>
+          <t>711.087</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>758.0</t>
+          <t>765.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-4.37</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-57.71</t>
+          <t>-81.30</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.90</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3595,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>282</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1152</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>79.41</t>
+          <t>70.42</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>82.88</t>
+          <t>80.35</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>15.48</t>
+          <t>13.05</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>6.51</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>764.8</t>
+          <t>760.8</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>662.3</t>
+          <t>673.0</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>621.8</t>
+          <t>624.74</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>627.64</t>
+          <t>629.5</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>34.94</t>
+          <t>26.07</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>48.50</t>
+          <t>48.47</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>35.94</t>
+          <t>38.45</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-55.49</t>
+          <t>-52.39</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,27 +3685,27 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>4918417582.333573</t>
+          <t>4923771953.88777</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>915187042.0</t>
+          <t>543477829.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>2404829140.4</t>
+          <t>1032473983.6</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>5686609711.2</t>
+          <t>5522062366.6</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>2312774767.92</t>
+          <t>2292721646.52</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -3715,11 +3715,11 @@
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>564134952.5119295</t>
+          <t>420618425.772247</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-152149242.69</v>
+        <v>-368722471.3</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>27.33</t>
+          <t>27.58</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>55.03</t>
+          <t>54.22</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.81</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>236910</t>
+          <t>233435</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>775.0</t>
+          <t>765.0</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>780.0</t>
+          <t>770.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>758.0</t>
+          <t>759.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>758.0</t>
+          <t>765.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1144.535</t>
+          <t>1193.09</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>770.0</t>
+          <t>758.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-4.37</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-15.19</t>
+          <t>-57.71</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3990,12 +3990,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>-2.90</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>282</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1152</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>91.21</t>
+          <t>79.41</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>86.14</t>
+          <t>82.88</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>17.70</t>
+          <t>15.48</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>5.32</t>
+          <t>6.51</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>767.6</t>
+          <t>764.8</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>652.15</t>
+          <t>662.3</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>619.2</t>
+          <t>621.8</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>625.75</t>
+          <t>627.64</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>48.00</t>
+          <t>34.94</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>48.55</t>
+          <t>48.50</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>32.80</t>
+          <t>35.94</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-59.38</t>
+          <t>-55.49</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>4918417582.333573</t>
+          <t>4923771953.88777</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>869643968.0</t>
+          <t>915187042.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>5071816570.6</t>
+          <t>2404829140.4</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>5980378748.8</t>
+          <t>5686609711.2</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>2324099002.48</t>
+          <t>2312774767.92</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-908562178</t>
+          <t>-2147483648</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>694368442.54881</t>
+          <t>564134952.5119295</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>122848998.31</v>
+        <v>-152149242.69</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -4214,22 +4214,22 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>27.76</t>
+          <t>27.33</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>55.03</t>
+          <t>54.22</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.81</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>236910</t>
+          <t>233435</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>765.0</t>
+          <t>775.0</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>770.0</t>
+          <t>780.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>758.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>770.0</t>
+          <t>758.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1587.408</t>
+          <t>1144.535</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>746.0</t>
+          <t>770.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-4.37</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>23.64</t>
+          <t>-15.19</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4421,12 +4421,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>-4.97</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>282</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1152</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>78.02</t>
+          <t>91.21</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>88.9</t>
+          <t>86.14</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>20.18</t>
+          <t>17.70</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>770.8</t>
+          <t>767.6</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>641.35</t>
+          <t>652.15</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>616.0</t>
+          <t>619.2</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>624.02</t>
+          <t>625.75</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>61.71</t>
+          <t>48.00</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>46.68</t>
+          <t>48.55</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>28.87</t>
+          <t>32.80</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-64.25</t>
+          <t>-59.38</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>4918417582.333573</t>
+          <t>4923771953.88777</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>1194102943.0</t>
+          <t>869643968.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>7380084994.6</t>
+          <t>5071816570.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>5968914067.6</t>
+          <t>5980378748.8</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>2329253341.64</t>
+          <t>2324099002.48</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>1411170927</t>
+          <t>-908562178</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>798281068.7748979</t>
+          <t>694368442.54881</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>516195779.15</v>
+        <v>122848998.31</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>26.89</t>
+          <t>27.76</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>55.03</t>
+          <t>54.22</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.81</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>236910</t>
+          <t>233435</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>755.0</t>
+          <t>765.0</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>774.0</t>
+          <t>770.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>743.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>746.0</t>
+          <t>770.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2119.821</t>
+          <t>1587.408</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>765.0</t>
+          <t>746.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-4.37</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>49.26</t>
+          <t>23.64</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4852,12 +4852,12 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-4.97</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,98 +4867,98 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>282</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1152</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>89.18</t>
+          <t>78.02</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>93.92</t>
+          <t>88.9</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>20.88</t>
+          <t>20.18</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>764.6</t>
+          <t>770.8</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>632.55</t>
+          <t>641.35</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>613.28</t>
+          <t>616.0</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>622.34</t>
+          <t>624.02</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>88.66</t>
+          <t>61.71</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>46.06</t>
+          <t>46.68</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>24.41</t>
+          <t>28.87</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-69.77</t>
+          <t>-64.25</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>4918417582.333573</t>
+          <t>4923771953.88777</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>1639958136.0</t>
+          <t>1194102943.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>8873124437.8</t>
+          <t>7380084994.6</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>5944629753.8</t>
+          <t>5968914067.6</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>2333052998.56</t>
+          <t>2329253341.64</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-2147483648</t>
+          <t>1411170927</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>849569303.2528446</t>
+          <t>798281068.7748979</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>1024920726.63</v>
+        <v>516195779.15</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>27.58</t>
+          <t>26.89</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>55.03</t>
+          <t>54.22</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.81</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>236910</t>
+          <t>233435</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>785.0</t>
+          <t>755.0</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>785.0</t>
+          <t>774.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>765.0</t>
+          <t>743.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>765.0</t>
+          <t>746.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>9688.689</t>
+          <t>2119.821</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,74 +5203,74 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>765.0</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-3.52</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>-4.37</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>49.26</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2025-11-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2025-09-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>785.0</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>-4.67</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>-1.42</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>70.54</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2025-11-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2025-09-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>738.0</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
         <is>
           <t>785.0</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>738.0</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>785.0</t>
-        </is>
-      </c>
       <c r="T12" t="inlineStr">
         <is>
           <t>624.0</t>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>6.37</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>34.55</t>
+          <t>7.56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>5.41</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5319,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>282</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1152</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>99.5</t>
+          <t>89.18</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>97.52</t>
+          <t>93.92</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>5.85</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>20.88</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>741.6</t>
+          <t>764.6</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>623.0</t>
+          <t>632.55</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>609.92</t>
+          <t>613.28</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>620.01</t>
+          <t>622.34</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>124.51</t>
+          <t>88.66</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>42.66</t>
+          <t>46.06</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>24.41</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-76.47</t>
+          <t>-69.77</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,27 +5409,27 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>4918417582.333573</t>
+          <t>4923771953.88777</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>7405253613.0</t>
+          <t>1639958136.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>10011650749.6</t>
+          <t>8873124437.8</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>5870589709.3</t>
+          <t>5944629753.8</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>2337679186.88</t>
+          <t>2333052998.56</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
@@ -5439,11 +5439,11 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>817687226.2755579</t>
+          <t>849569303.2528446</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>1667296140.69</v>
+        <v>1024920726.63</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>28.30</t>
+          <t>27.58</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>55.03</t>
+          <t>54.22</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.81</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>236910</t>
+          <t>233435</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>748.0</t>
+          <t>785.0</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>788.0</t>
+          <t>785.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>742.0</t>
+          <t>765.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>785.0</t>
+          <t>765.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2950.547</t>
+          <t>4255.671</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-19.47</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-14.62</t>
+          <t>-11.57</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>7.02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,77 +5750,77 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>2951</t>
+          <t>4256</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>38.64</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.88</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-5.20</t>
+          <t>-5.63</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>97.82</t>
+          <t>97.24000000000001</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>103.19</t>
+          <t>103.04</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>102.95</t>
+          <t>102.79</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>104.19</t>
+          <t>104.13</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-887.49</t>
+          <t>-260.17</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-101.02</t>
+          <t>-102.92</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,41 +5840,41 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>1681366999.147694</t>
+          <t>1679848857.064748</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>281468682.0</t>
+          <t>417505501.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>283145846.4</t>
+          <t>313755822.4</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>351622846.6</t>
+          <t>306400241.3</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>414970230.06</t>
+          <t>420660383.62</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-68477000</t>
+          <t>7355581</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-15789.41195628047</t>
+          <t>-14266850.85435314</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>-104519583.14</v>
+        <v>-92647688.79000001</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-6.21</t>
+          <t>-2.86</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5938,22 +5938,22 @@
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>31.52</t>
+          <t>32.65</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.81</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>26000</t>
+          <t>26928</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>98.4</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>97.9</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>94.1</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>3012.776</t>
+          <t>2950.547</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-37.86</t>
+          <t>-19.47</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-13.63</t>
+          <t>-14.62</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,12 +6181,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>2951</t>
+          <t>4256</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6201,57 +6201,57 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-5.20</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>99.08000000000001</t>
+          <t>97.82</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>103.19</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>103.2</t>
+          <t>102.95</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>104.3</t>
+          <t>104.19</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-667.15</t>
+          <t>-887.49</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-98.76</t>
+          <t>-101.02</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,41 +6271,41 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>1681366999.147694</t>
+          <t>1679848857.064748</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>289264312.0</t>
+          <t>281468682.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>275009623.6</t>
+          <t>283145846.4</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>442557432.7</t>
+          <t>351622846.6</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>412480726.12</t>
+          <t>414970230.06</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-167547809</t>
+          <t>-68477000</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>18984900.35753776</t>
+          <t>-15789.41195628047</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>-103171216.51</v>
+        <v>-104519583.14</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-5.12</t>
+          <t>-6.21</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
@@ -6379,12 +6379,12 @@
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>31.52</t>
+          <t>32.65</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.81</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>26000</t>
+          <t>26928</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>97.2</t>
+          <t>97.9</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>94.1</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2248.507</t>
+          <t>3012.776</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>96.3</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,17 +6506,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-53.51</t>
+          <t>-37.86</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-12.56</t>
+          <t>-13.63</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,12 +6612,12 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>2951</t>
+          <t>4256</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6632,12 +6632,12 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -6647,42 +6647,42 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>100.42</t>
+          <t>99.08000000000001</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>103.72</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>103.4</t>
+          <t>103.2</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>104.41</t>
+          <t>104.3</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-215.80</t>
+          <t>-667.15</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-96.68</t>
+          <t>-98.76</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,41 +6702,41 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>1681366999.147694</t>
+          <t>1679848857.064748</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>220432535.0</t>
+          <t>289264312.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>268507044.2</t>
+          <t>275009623.6</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>577618774.1</t>
+          <t>442557432.7</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>409190484.56</t>
+          <t>412480726.12</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-309111729</t>
+          <t>-167547809</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>41195103.42357187</t>
+          <t>18984900.35753776</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>-98395538.22</v>
+        <v>-103171216.51</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-3.94</t>
+          <t>-5.12</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6800,7 +6800,7 @@
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>4.40</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>31.52</t>
+          <t>32.65</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.81</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>26000</t>
+          <t>26928</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>99.2</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>97.2</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>97.2</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>96.3</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-2.9</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>3626.375</t>
+          <t>2248.507</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-3.57</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-75.12</t>
+          <t>-53.51</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-11.57</t>
+          <t>-12.56</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7022,33 +7022,33 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>5.98</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>2951</t>
+          <t>4256</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7063,57 +7063,57 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>101.72</t>
+          <t>100.42</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>103.96</t>
+          <t>103.72</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>103.6</t>
+          <t>103.4</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>104.44</t>
+          <t>104.41</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-109.91</t>
+          <t>-215.80</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-94.89</t>
+          <t>-96.68</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,41 +7133,41 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>1681366999.147694</t>
+          <t>1679848857.064748</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>360108082.0</t>
+          <t>220432535.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>286154072.8</t>
+          <t>268507044.2</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>1150276311.8</t>
+          <t>577618774.1</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>408529389.62</t>
+          <t>409190484.56</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-864122239</t>
+          <t>-309111729</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>66575220.08572514</t>
+          <t>41195103.42357187</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>-80684181.05</v>
+        <v>-98395538.22</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-2.86</t>
+          <t>-3.94</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>4.40</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>31.52</t>
+          <t>32.65</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.81</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>26000</t>
+          <t>26928</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>99.2</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>99.6</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>97.2</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,42 +7343,42 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>-2.9</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>3626.375</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>98.6</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2607.704</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>101.5</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>-6.62</t>
-        </is>
-      </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-77.08</t>
+          <t>-75.12</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-8.97</t>
+          <t>-11.57</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7453,33 +7453,33 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>5.98</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>2951</t>
+          <t>4256</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7489,62 +7489,62 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>5.21</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>103.1</t>
+          <t>101.72</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>104.18</t>
+          <t>103.96</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>103.79</t>
+          <t>103.6</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>104.52</t>
+          <t>104.44</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-53.80</t>
+          <t>-109.91</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-93.49</t>
+          <t>-94.89</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,41 +7564,41 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>1681366999.147694</t>
+          <t>1679848857.064748</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>264455621.0</t>
+          <t>360108082.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>299044660.2</t>
+          <t>286154072.8</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>1304605197.0</t>
+          <t>1150276311.8</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>411510598.5</t>
+          <t>408529389.62</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-1005560536</t>
+          <t>-864122239</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>93349656.65584514</t>
+          <t>66575220.08572514</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>-67465901.52</v>
+        <v>-80684181.05</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.86</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7662,7 +7662,7 @@
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
@@ -7672,12 +7672,12 @@
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>31.52</t>
+          <t>32.65</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.81</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>26000</t>
+          <t>26928</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2354.931</t>
+          <t>2607.704</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-6.62</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-67.98</t>
+          <t>-77.08</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>3.89</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,12 +7905,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>2951</t>
+          <t>4256</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -7920,32 +7920,32 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>16.14</t>
+          <t>5.21</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>104.9</t>
+          <t>103.1</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -7955,27 +7955,27 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>104.03</t>
+          <t>103.79</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>104.57</t>
+          <t>104.52</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-25.93</t>
+          <t>-53.80</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-92.62</t>
+          <t>-93.49</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,41 +7995,41 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1681366999.147694</t>
+          <t>1679848857.064748</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>240787568.0</t>
+          <t>264455621.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>420099846.8</t>
+          <t>299044660.2</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>1311901908.4</t>
+          <t>1304605197.0</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>422014478.54</t>
+          <t>411510598.5</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-891802061</t>
+          <t>-1005560536</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>122588849.0518091</t>
+          <t>93349656.65584514</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>-35924670.61</v>
+        <v>-67465901.52</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8093,12 +8093,12 @@
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8108,7 +8108,7 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>31.52</t>
+          <t>32.65</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.81</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>26000</t>
+          <t>26928</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,17 +8158,17 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2468.394</t>
+          <t>2354.931</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-8.19</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-52.97</t>
+          <t>-67.98</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-7.62</t>
+          <t>-8.97</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,77 +8336,77 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>2951</t>
+          <t>4256</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>15.62</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>30.28</t>
+          <t>16.14</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-4.45</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>107.8</t>
+          <t>104.9</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>104.1</t>
+          <t>104.18</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>104.21</t>
+          <t>104.03</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>104.62</t>
+          <t>104.57</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>8.52</t>
+          <t>-25.93</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-92.14</t>
+          <t>-92.62</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,41 +8426,41 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>1681366999.147694</t>
+          <t>1679848857.064748</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>256751415.0</t>
+          <t>240787568.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>610105241.8</t>
+          <t>420099846.8</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>1297204898.4</t>
+          <t>1311901908.4</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>427732003.84</t>
+          <t>422014478.54</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-687099656</t>
+          <t>-891802061</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>151409488.9896297</t>
+          <t>122588849.0518091</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>12953117.47</v>
+        <v>-35924670.61</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>31.52</t>
+          <t>32.65</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.81</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>26000</t>
+          <t>26928</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,22 +8589,22 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2959.424</t>
+          <t>2468.394</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-9.24</t>
+          <t>-4.46</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-30.99</t>
+          <t>-52.97</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-6.73</t>
+          <t>-7.62</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,77 +8767,77 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>2951</t>
+          <t>4256</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>32.8</t>
+          <t>15.62</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>47.93</t>
+          <t>30.28</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>-4.45</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>5.35</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>109.6</t>
+          <t>107.8</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>104.03</t>
+          <t>104.1</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>104.32</t>
+          <t>104.21</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>104.64</t>
+          <t>104.62</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>46.78</t>
+          <t>8.52</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-92.31</t>
+          <t>-92.14</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,41 +8857,41 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>1681366999.147694</t>
+          <t>1679848857.064748</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>308667678.0</t>
+          <t>256751415.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>886730504.0</t>
+          <t>610105241.8</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>1285022286.6</t>
+          <t>1297204898.4</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>427982006.44</t>
+          <t>427732003.84</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-398291782</t>
+          <t>-687099656</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>176583374.7198053</t>
+          <t>151409488.9896297</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>80605505.5</v>
+        <v>12953117.47</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8955,22 +8955,22 @@
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>31.52</t>
+          <t>32.65</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.81</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>26000</t>
+          <t>26928</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>106.5</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-4.57</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>3956.697</t>
+          <t>2959.424</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-10.82</t>
+          <t>-5.48</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>58.05</t>
+          <t>-30.99</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-5.38</t>
+          <t>-6.73</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>6.53</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,177 +9198,177 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>2951</t>
+          <t>4256</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>42.41</t>
+          <t>32.8</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>69.46</t>
+          <t>47.93</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-5.89</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>7.99</t>
+          <t>5.35</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>112.1</t>
+          <t>109.6</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>103.8</t>
+          <t>104.03</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>104.4</t>
+          <t>104.32</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>104.67</t>
+          <t>104.64</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>105.65</t>
+          <t>46.78</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
+          <t>1.15</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>14.93</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr">
+        <is>
+          <t>-92.31</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>2025/10/31</t>
+        </is>
+      </c>
+      <c r="AV21" t="inlineStr">
+        <is>
+          <t>1679848857.064748</t>
+        </is>
+      </c>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>308667678.0</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>886730504.0</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>1285022286.6</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>427982006.44</t>
+        </is>
+      </c>
+      <c r="BA21" t="inlineStr">
+        <is>
+          <t>-398291782</t>
+        </is>
+      </c>
+      <c r="BB21" t="inlineStr">
+        <is>
+          <t>176583374.7198053</t>
+        </is>
+      </c>
+      <c r="BC21" t="n">
+        <v>80605505.5</v>
+      </c>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE21" t="inlineStr">
+        <is>
+          <t>101.5</t>
+        </is>
+      </c>
+      <c r="BF21" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="BG21" t="inlineStr">
+        <is>
+          <t>2.46</t>
+        </is>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>亞力</t>
+        </is>
+      </c>
+      <c r="BI21" t="inlineStr">
+        <is>
+          <t>亞力</t>
+        </is>
+      </c>
+      <c r="BJ21" t="inlineStr">
+        <is>
+          <t>電機機械</t>
+        </is>
+      </c>
+      <c r="BK21" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL21" t="inlineStr">
+        <is>
           <t>1.01</t>
         </is>
       </c>
-      <c r="AS21" t="inlineStr">
-        <is>
-          <t>14.93</t>
-        </is>
-      </c>
-      <c r="AT21" t="inlineStr">
-        <is>
-          <t>-93.21</t>
-        </is>
-      </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>2025/10/31</t>
-        </is>
-      </c>
-      <c r="AV21" t="inlineStr">
-        <is>
-          <t>1681366999.147694</t>
-        </is>
-      </c>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>424561019.0</t>
-        </is>
-      </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>2014398550.8</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>1274536171.3</t>
-        </is>
-      </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>424494347.48</t>
-        </is>
-      </c>
-      <c r="BA21" t="inlineStr">
-        <is>
-          <t>739862379</t>
-        </is>
-      </c>
-      <c r="BB21" t="inlineStr">
-        <is>
-          <t>194033896.3962396</t>
-        </is>
-      </c>
-      <c r="BC21" t="n">
-        <v>168810549.3</v>
-      </c>
-      <c r="BD21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE21" t="inlineStr">
-        <is>
-          <t>101.5</t>
-        </is>
-      </c>
-      <c r="BF21" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="BG21" t="inlineStr">
-        <is>
-          <t>3.94</t>
-        </is>
-      </c>
-      <c r="BH21" t="inlineStr">
-        <is>
-          <t>亞力</t>
-        </is>
-      </c>
-      <c r="BI21" t="inlineStr">
-        <is>
-          <t>亞力</t>
-        </is>
-      </c>
-      <c r="BJ21" t="inlineStr">
-        <is>
-          <t>電機機械</t>
-        </is>
-      </c>
-      <c r="BK21" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL21" t="inlineStr">
-        <is>
-          <t>1.01</t>
-        </is>
-      </c>
       <c r="BM21" t="inlineStr">
         <is>
           <t>-3.87807238678311</t>
@@ -9386,7 +9386,7 @@
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>31.52</t>
+          <t>32.65</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.81</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>26000</t>
+          <t>26928</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,22 +9451,22 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>109.5</t>
+          <t>106.5</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-4.74</t>
+          <t>-4.57</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>7756.599</t>
+          <t>3956.697</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-16.07</t>
+          <t>-7.0</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>84.41</t>
+          <t>58.05</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-5.38</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12.80</t>
+          <t>6.53</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,77 +9629,77 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>2951</t>
+          <t>4256</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>68.59</t>
+          <t>42.41</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>69.46</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-2.30</t>
+          <t>-5.89</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>9.16</t>
+          <t>7.99</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>113.1</t>
+          <t>112.1</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>103.6</t>
+          <t>103.8</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>104.44</t>
+          <t>104.4</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>104.68</t>
+          <t>104.67</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>223.35</t>
+          <t>105.65</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-95.00</t>
+          <t>-93.21</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,41 +9719,41 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>1681366999.147694</t>
+          <t>1679848857.064748</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>869731554.0</t>
+          <t>424561019.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>2310165733.8</t>
+          <t>2014398550.8</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>1252715915.0</t>
+          <t>1274536171.3</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>420881183.08</t>
+          <t>424494347.48</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>1057449818</t>
+          <t>739862379</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>198619959.5039042</t>
+          <t>194033896.3962396</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>276371662.87</v>
+        <v>168810549.3</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>8.87</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9827,12 +9827,12 @@
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>31.52</t>
+          <t>32.65</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.81</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>26000</t>
+          <t>26928</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,22 +9882,22 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>109.5</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>-4.74</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>10560.098</t>
+          <t>7756.599</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>110.5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-21.85</t>
+          <t>-12.07</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>87.89</t>
+          <t>84.41</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17.42</t>
+          <t>12.80</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>5.94</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,77 +10060,77 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>2951</t>
+          <t>4256</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>97.38</t>
+          <t>68.59</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>91.27</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>4.41</t>
+          <t>-2.30</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>7.73</t>
+          <t>9.16</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>111.1</t>
+          <t>113.1</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>103.13</t>
+          <t>103.6</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>104.35</t>
+          <t>104.44</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>104.64</t>
+          <t>104.68</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>593.93</t>
+          <t>223.35</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-97.79</t>
+          <t>-95.00</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>1681366999.147694</t>
+          <t>1679848857.064748</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>1190814543.0</t>
+          <t>869731554.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>2203703970.0</t>
+          <t>2310165733.8</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>1172861138.6</t>
+          <t>1252715915.0</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>406500816.74</t>
+          <t>420881183.08</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>1030842831</t>
+          <t>1057449818</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>184483286.1643741</t>
+          <t>198619959.5039042</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>372463136.97</v>
+        <v>276371662.87</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>14.29</t>
+          <t>8.87</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10258,12 +10258,12 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>5.23</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>31.52</t>
+          <t>32.65</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.81</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>26000</t>
+          <t>26928</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,7 +10313,7 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>111.0</t>
+          <t>116.0</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>109.5</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>110.5</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/配電系統.xlsx
+++ b/Result/checksun_type/配電系統.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-7.07</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>12908.308</t>
+          <t>4656.178</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>688.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>62.76</t>
+          <t>70.21</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-6.78</t>
+          <t>-4.34</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>46.03</t>
+          <t>16.60</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-13.23</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,77 +1014,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>106</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>12908</t>
+          <t>4656</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>39.68</t>
+          <t>24.72</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-5.02</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>12.71</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>724.4</t>
+          <t>718.0</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>720.75</t>
+          <t>726.45</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>639.48</t>
+          <t>641.18</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>637.48</t>
+          <t>638.1</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-24.05</t>
+          <t>-29.15</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>26.60</t>
+          <t>23.12</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>35.02</t>
+          <t>32.64</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-56.63</t>
+          <t>-59.58</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>4936949495.859914</t>
+          <t>4936987441.390244</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>9396894111.0</t>
+          <t>3308931687.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>3406595539.2</t>
+          <t>3977678243.4</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>2092972596.2</t>
+          <t>2336901368.1</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>2319670873.56</t>
+          <t>2356977274.04</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>1313622943</t>
+          <t>1640776875</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-92608315.67016768</t>
+          <t>-38539849.95401464</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>332708021.9386873</t>
+          <t>258836711.484827</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>9396894111</v>
+        <v>3308931687</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-10.88</t>
+          <t>-8.55</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>24.80</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>50.48</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>40.13</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>217325</t>
+          <t>223011</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>721.0</t>
+          <t>701.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>780.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>687.0</t>
+          <t>698.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>688.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-7.07</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>7500.722</t>
+          <t>12908.308</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>739.0</t>
+          <t>688.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-7.41</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>32.75</t>
+          <t>62.76</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-6.78</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>26.75</t>
+          <t>46.03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-7.70</t>
+          <t>-13.23</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,17 +1450,17 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>106</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>12908</t>
+          <t>4656</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>50.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -1470,57 +1470,57 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>-5.02</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>12.71</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>731.2</t>
+          <t>724.4</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>715.55</t>
+          <t>720.75</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>638.3</t>
+          <t>639.48</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>636.88</t>
+          <t>637.48</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-12.52</t>
+          <t>-24.05</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>32.48</t>
+          <t>26.60</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>37.13</t>
+          <t>35.02</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-54.03</t>
+          <t>-56.63</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>4936949495.859914</t>
+          <t>4936987441.390244</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>5759803875.0</t>
+          <t>9396894111.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>1689450518.2</t>
+          <t>3406595539.2</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>1272693479.4</t>
+          <t>2092972596.2</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>2149905312.46</t>
+          <t>2319670873.56</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>416757038</t>
+          <t>1313622943</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-169938558.8717777</t>
+          <t>-92608315.67016768</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-225925652.1964645</t>
+          <t>332708021.9386873</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>5759803875</v>
+        <v>9396894111</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-10.88</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>26.64</t>
+          <t>24.80</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>50.48</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>40.13</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>217325</t>
+          <t>223011</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>789.0</t>
+          <t>721.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>803.0</t>
+          <t>780.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>732.0</t>
+          <t>687.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>739.0</t>
+          <t>688.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1152.161</t>
+          <t>7500.722</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>739.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-9.01</t>
+          <t>-4.67</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-19.96</t>
+          <t>32.75</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>26.75</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>-7.70</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,77 +1886,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>106</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>12908</t>
+          <t>4656</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>68.25</t>
+          <t>50.79</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>31.22</t>
+          <t>39.68</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>732.4</t>
+          <t>731.2</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>708.6</t>
+          <t>715.55</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>635.96</t>
+          <t>638.3</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>635.39</t>
+          <t>636.88</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-10.37</t>
+          <t>-12.52</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>34.32</t>
+          <t>32.48</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>38.29</t>
+          <t>37.13</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-52.59</t>
+          <t>-54.03</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>4936949495.859914</t>
+          <t>4936987441.390244</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>848806811.0</t>
+          <t>5759803875.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>688943827.4</t>
+          <t>1689450518.2</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>860708905.5</t>
+          <t>1272693479.4</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>2069337538.82</t>
+          <t>2149905312.46</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-171765078</t>
+          <t>416757038</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-159759087.3581983</t>
+          <t>-169938558.8717777</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-626216745.2396646</t>
+          <t>-225925652.1964645</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>848806811</v>
+        <v>5759803875</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2079,22 +2079,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>27.04</t>
+          <t>26.64</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>50.48</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>40.13</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>217325</t>
+          <t>223011</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>789.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>803.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>732.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>739.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>799.533</t>
+          <t>1152.161</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-6.23</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-58.59</t>
+          <t>-19.96</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-4.20</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-4.53</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,77 +2322,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>106</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>12908</t>
+          <t>4656</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>68.25</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>8.47</t>
+          <t>31.22</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>10.66</t>
+          <t>11.42</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>735.4</t>
+          <t>732.4</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>701.1</t>
+          <t>708.6</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>633.54</t>
+          <t>635.96</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>634.25</t>
+          <t>635.39</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-10.78</t>
+          <t>-10.37</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>34.32</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>39.28</t>
+          <t>38.29</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-51.36</t>
+          <t>-52.59</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>4936949495.859914</t>
+          <t>4936987441.390244</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>573954733.0</t>
+          <t>848806811.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>627878031.0</t>
+          <t>688943827.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>1516353585.7</t>
+          <t>860708905.5</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>2106062606.14</t>
+          <t>2069337538.82</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-888475554</t>
+          <t>-171765078</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-74948604.10702263</t>
+          <t>-159759087.3581983</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-649518023.2571056</t>
+          <t>-626216745.2396646</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>573954733</v>
+        <v>848806811</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-8.42</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2515,22 +2515,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>25.49</t>
+          <t>27.04</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>50.48</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>40.13</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>217325</t>
+          <t>223011</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>740.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>740.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>617.266</t>
+          <t>799.533</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,72 +2642,72 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>707.0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-0.14</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>-2.9</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>-58.59</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2025-11-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2025-09-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>785.0</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
           <t>738.0</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>-7.27</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>-2.06</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>-75.86</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2025-11-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2025-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2025-09-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>785.0</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>738.0</t>
-        </is>
-      </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>785.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>-5.99</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>-4.53</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,17 +2758,17 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>106</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>12908</t>
+          <t>4656</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -2778,57 +2778,57 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>10.09</t>
+          <t>10.66</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>745.6</t>
+          <t>735.4</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>695.2</t>
+          <t>701.1</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>631.48</t>
+          <t>633.54</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>633.66</t>
+          <t>634.25</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-10.78</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>35.05</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>40.34</t>
+          <t>39.28</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-50.05</t>
+          <t>-51.36</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,50 +2848,50 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>4936949495.859914</t>
+          <t>4936987441.390244</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>453518166.0</t>
+          <t>573954733.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>696124492.8</t>
+          <t>627878031.0</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>2883970531.7</t>
+          <t>1516353585.7</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>2126707687.18</t>
+          <t>2106062606.14</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-2147483648</t>
+          <t>-888475554</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>29518563.01117429</t>
+          <t>-74948604.10702263</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-630160054.0942674</t>
+          <t>-649518023.2571056</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>453518166</v>
+        <v>573954733</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-4.40</t>
+          <t>-8.42</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>26.60</t>
+          <t>25.49</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>50.48</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>40.13</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>217325</t>
+          <t>223011</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>737.0</t>
+          <t>740.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>739.0</t>
+          <t>740.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>730.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>738.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1116.653</t>
+          <t>617.266</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-4.94</t>
+          <t>-4.53</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-80.90</t>
+          <t>-75.86</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3158,12 +3158,12 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>-8.03</t>
+          <t>-5.99</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,77 +3194,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>106</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>12908</t>
+          <t>4656</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>23.47</t>
+          <t>8.47</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-3.99</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>9.29</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>10.09</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>752.0</t>
+          <t>745.6</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>688.05</t>
+          <t>695.2</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>628.72</t>
+          <t>631.48</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>632.04</t>
+          <t>633.66</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>42.23</t>
+          <t>39.85</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>40.46</t>
+          <t>40.34</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-49.89</t>
+          <t>-50.05</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,27 +3284,27 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>4936949495.859914</t>
+          <t>4936987441.390244</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>811169006.0</t>
+          <t>453518166.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>779349653.2</t>
+          <t>696124492.8</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>4079717323.9</t>
+          <t>2883970531.7</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>2168937186.34</t>
+          <t>2126707687.18</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
@@ -3314,16 +3314,16 @@
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>149460129.7576182</t>
+          <t>29518563.01117429</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-567096178.3225608</t>
+          <t>-630160054.0942674</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>811169006</v>
+        <v>453518166</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-6.48</t>
+          <t>-4.40</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>26.03</t>
+          <t>26.60</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>50.48</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>40.13</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>217325</t>
+          <t>223011</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>725.0</t>
+          <t>737.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>736.0</t>
+          <t>739.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>730.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1008.586</t>
+          <t>1116.653</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>745.0</t>
+          <t>722.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-8.28</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-82.40</t>
+          <t>-80.90</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>-5.10</t>
+          <t>-8.03</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,12 +3630,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>106</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>12908</t>
+          <t>4656</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3645,62 +3645,62 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>49.94</t>
+          <t>23.47</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-3.99</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>11.02</t>
+          <t>9.29</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>8.78</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>756.8</t>
+          <t>752.0</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>681.7</t>
+          <t>688.05</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>626.7</t>
+          <t>628.72</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>630.91</t>
+          <t>632.04</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>15.69</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>46.30</t>
+          <t>42.23</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>40.02</t>
+          <t>40.46</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-50.44</t>
+          <t>-49.89</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,27 +3720,27 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>4936949495.859914</t>
+          <t>4936987441.390244</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>757270421.0</t>
+          <t>811169006.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>855936440.6</t>
+          <t>779349653.2</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>4864530439.2</t>
+          <t>4079717323.9</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>2227082877.5</t>
+          <t>2168937186.34</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -3750,16 +3750,16 @@
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>279743094.8631054</t>
+          <t>149460129.7576182</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-495071225.1371737</t>
+          <t>-567096178.3225608</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>757270421</v>
+        <v>811169006</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-3.50</t>
+          <t>-6.48</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3828,17 +3828,17 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>26.86</t>
+          <t>26.03</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>50.48</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>40.13</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>217325</t>
+          <t>223011</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>769.0</t>
+          <t>725.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>769.0</t>
+          <t>736.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>737.0</t>
+          <t>722.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>745.0</t>
+          <t>722.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>711.087</t>
+          <t>1008.586</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>765.0</t>
+          <t>745.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-11.19</t>
+          <t>-5.52</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-81.30</t>
+          <t>-82.40</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4030,12 +4030,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-5.10</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,77 +4066,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>106</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>12908</t>
+          <t>4656</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>70.42</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>80.35</t>
+          <t>49.94</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>13.05</t>
+          <t>11.02</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>8.78</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>760.8</t>
+          <t>756.8</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>673.0</t>
+          <t>681.7</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>624.74</t>
+          <t>626.7</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>629.5</t>
+          <t>630.91</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>26.07</t>
+          <t>15.69</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>48.47</t>
+          <t>46.30</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>38.45</t>
+          <t>40.02</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-52.39</t>
+          <t>-50.44</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,27 +4156,27 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>4936949495.859914</t>
+          <t>4936987441.390244</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>543477829.0</t>
+          <t>757270421.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>1032473983.6</t>
+          <t>855936440.6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>5522062366.6</t>
+          <t>4864530439.2</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>2292721646.52</t>
+          <t>2227082877.5</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -4186,16 +4186,16 @@
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>420618425.772247</t>
+          <t>279743094.8631054</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-368722471.2960072</t>
+          <t>-495071225.1371737</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>543477829</v>
+        <v>757270421</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-3.50</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4259,22 +4259,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>27.58</t>
+          <t>26.86</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>50.48</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>40.13</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>217325</t>
+          <t>223011</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>765.0</t>
+          <t>769.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>770.0</t>
+          <t>769.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>759.0</t>
+          <t>737.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>765.0</t>
+          <t>745.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1193.09</t>
+          <t>711.087</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>758.0</t>
+          <t>765.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-10.17</t>
+          <t>-8.36</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-57.71</t>
+          <t>-81.30</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.90</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,77 +4502,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>106</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>12908</t>
+          <t>4656</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>79.41</t>
+          <t>70.42</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>82.88</t>
+          <t>80.35</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>15.48</t>
+          <t>13.05</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>6.51</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>764.8</t>
+          <t>760.8</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>662.3</t>
+          <t>673.0</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>621.8</t>
+          <t>624.74</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>627.64</t>
+          <t>629.5</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>34.94</t>
+          <t>26.07</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>48.50</t>
+          <t>48.47</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>35.94</t>
+          <t>38.45</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-55.49</t>
+          <t>-52.39</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,27 +4592,27 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>4936949495.859914</t>
+          <t>4936987441.390244</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>915187042.0</t>
+          <t>543477829.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>2404829140.4</t>
+          <t>1032473983.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>5686609711.2</t>
+          <t>5522062366.6</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>2312774767.92</t>
+          <t>2292721646.52</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
@@ -4622,16 +4622,16 @@
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>564134952.5119295</t>
+          <t>420618425.772247</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-152149242.6909127</t>
+          <t>-368722471.2960072</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>915187042</v>
+        <v>543477829</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4705,12 +4705,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>27.33</t>
+          <t>27.58</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>50.48</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>40.13</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>217325</t>
+          <t>223011</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>775.0</t>
+          <t>765.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>780.0</t>
+          <t>770.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>758.0</t>
+          <t>759.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>758.0</t>
+          <t>765.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1144.535</t>
+          <t>1193.09</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>770.0</t>
+          <t>758.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-11.92</t>
+          <t>-7.37</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-15.19</t>
+          <t>-57.71</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>-2.90</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,77 +4938,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>106</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>12908</t>
+          <t>4656</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>91.21</t>
+          <t>79.41</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>86.14</t>
+          <t>82.88</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>17.70</t>
+          <t>15.48</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>5.32</t>
+          <t>6.51</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>767.6</t>
+          <t>764.8</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>652.15</t>
+          <t>662.3</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>619.2</t>
+          <t>621.8</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>625.75</t>
+          <t>627.64</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>48.00</t>
+          <t>34.94</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>48.55</t>
+          <t>48.50</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>32.80</t>
+          <t>35.94</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-59.38</t>
+          <t>-55.49</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>4936949495.859914</t>
+          <t>4936987441.390244</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>869643968.0</t>
+          <t>915187042.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>5071816570.6</t>
+          <t>2404829140.4</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>5980378748.8</t>
+          <t>5686609711.2</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>2324099002.48</t>
+          <t>2312774767.92</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-908562178</t>
+          <t>-2147483648</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>694368442.54881</t>
+          <t>564134952.5119295</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>122848998.3053265</t>
+          <t>-152149242.6909127</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>869643968</v>
+        <v>915187042</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>27.76</t>
+          <t>27.33</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>50.48</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>40.13</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>217325</t>
+          <t>223011</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>765.0</t>
+          <t>775.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>770.0</t>
+          <t>780.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>758.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>770.0</t>
+          <t>758.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1587.408</t>
+          <t>1144.535</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>746.0</t>
+          <t>770.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-8.43</t>
+          <t>-9.07</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>23.64</t>
+          <t>-15.19</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5338,12 +5338,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>-4.97</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,77 +5374,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>106</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>12908</t>
+          <t>4656</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>78.02</t>
+          <t>91.21</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>88.9</t>
+          <t>86.14</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>20.18</t>
+          <t>17.70</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>770.8</t>
+          <t>767.6</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>641.35</t>
+          <t>652.15</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>616.0</t>
+          <t>619.2</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>624.02</t>
+          <t>625.75</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>61.71</t>
+          <t>48.00</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>46.68</t>
+          <t>48.55</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>28.87</t>
+          <t>32.80</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-64.25</t>
+          <t>-59.38</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>4936949495.859914</t>
+          <t>4936987441.390244</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>1194102943.0</t>
+          <t>869643968.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>7380084994.6</t>
+          <t>5071816570.6</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>5968914067.6</t>
+          <t>5980378748.8</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>2329253341.64</t>
+          <t>2324099002.48</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>1411170927</t>
+          <t>-908562178</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>798281068.7748979</t>
+          <t>694368442.54881</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>516195779.1461916</t>
+          <t>122848998.3053265</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>1194102943</v>
+        <v>869643968</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>26.89</t>
+          <t>27.76</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>50.48</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>40.13</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>217325</t>
+          <t>223011</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>755.0</t>
+          <t>765.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>774.0</t>
+          <t>770.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>743.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>746.0</t>
+          <t>770.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-3.53</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>7327.598</t>
+          <t>1914.684</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>95.3</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>14.67</t>
+          <t>16.80</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-14.62</t>
+          <t>-14.53</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5789,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12.09</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-4.94</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5810,77 +5810,77 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>7328</t>
+          <t>1915</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>12.88</t>
+          <t>13.41</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-6.09</t>
+          <t>-6.38</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>96.56</t>
+          <t>96.12</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>102.82</t>
+          <t>102.68</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>102.56</t>
+          <t>102.33</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>104.04</t>
+          <t>103.93</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-159.05</t>
+          <t>-109.29</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-104.84</t>
+          <t>-106.66</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5900,46 +5900,46 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>1678974082.870689</t>
+          <t>1676957626.954089</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>714004012.0</t>
+          <t>182336206.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>384535008.4</t>
+          <t>376915742.6</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>335344540.6</t>
+          <t>322711393.4</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>431976435.3</t>
+          <t>429470961.98</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>49190467</t>
+          <t>54204349</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-21269455.67571436</t>
+          <t>-29560237.64442549</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-59783782.19320107</t>
+          <t>-75159538.47233671</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>714004012</v>
+        <v>182336206</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-6.21</t>
+          <t>-6.11</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>31.52</t>
+          <t>31.56</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>40.13</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>26000</t>
+          <t>26027</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6068,22 +6068,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>95.8</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>96.6</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>95.1</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>95.3</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>-3.53</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>4255.671</t>
+          <t>7327.598</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6140,17 +6140,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-3.57</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>14.67</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-11.57</t>
+          <t>-14.62</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6225,17 +6225,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>7.02</t>
+          <t>12.09</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>-4.94</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6246,17 +6246,17 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>7328</t>
+          <t>1915</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>38.64</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
@@ -6266,57 +6266,57 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-5.63</t>
+          <t>-6.09</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>97.24000000000001</t>
+          <t>96.56</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>103.04</t>
+          <t>102.82</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>102.79</t>
+          <t>102.56</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>104.13</t>
+          <t>104.04</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-260.17</t>
+          <t>-159.05</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-102.92</t>
+          <t>-104.84</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6336,46 +6336,46 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>1678974082.870689</t>
+          <t>1676957626.954089</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>417505501.0</t>
+          <t>714004012.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>313755822.4</t>
+          <t>384535008.4</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>306400241.3</t>
+          <t>335344540.6</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>420660383.62</t>
+          <t>431976435.3</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>7355581</t>
+          <t>49190467</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-14266850.85435314</t>
+          <t>-21269455.67571436</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-92647688.78753585</t>
+          <t>-59783782.19320107</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>417505501</v>
+        <v>714004012</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-2.86</t>
+          <t>-6.21</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6419,7 +6419,7 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
@@ -6439,22 +6439,22 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>31.52</t>
+          <t>31.56</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>40.13</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>26000</t>
+          <t>26027</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6504,7 +6504,7 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>98.4</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
@@ -6514,12 +6514,12 @@
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>95.1</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2950.547</t>
+          <t>4255.671</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6576,17 +6576,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-3.46</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-19.47</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-14.62</t>
+          <t>-11.57</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>7.02</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6682,77 +6682,77 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>7328</t>
+          <t>1915</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>38.64</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.88</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-5.20</t>
+          <t>-5.63</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>97.82</t>
+          <t>97.24000000000001</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>103.19</t>
+          <t>103.04</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>102.95</t>
+          <t>102.79</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>104.19</t>
+          <t>104.13</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-887.49</t>
+          <t>-260.17</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-101.02</t>
+          <t>-102.92</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6772,46 +6772,46 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>1678974082.870689</t>
+          <t>1676957626.954089</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>281468682.0</t>
+          <t>417505501.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>283145846.4</t>
+          <t>313755822.4</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>351622846.6</t>
+          <t>306400241.3</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>414970230.06</t>
+          <t>420660383.62</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-68477000</t>
+          <t>7355581</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-15789.41195628047</t>
+          <t>-14266850.85435314</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-104519583.1441735</t>
+          <t>-92647688.78753585</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>281468682</v>
+        <v>417505501</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-6.21</t>
+          <t>-2.86</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
@@ -6875,22 +6875,22 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6900,7 +6900,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>31.52</t>
+          <t>31.56</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>40.13</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>26000</t>
+          <t>26027</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6940,22 +6940,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>98.4</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>97.9</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>94.1</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>3012.776</t>
+          <t>2950.547</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7012,17 +7012,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-37.86</t>
+          <t>-19.47</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-13.63</t>
+          <t>-14.62</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7097,17 +7097,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7118,12 +7118,12 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>7328</t>
+          <t>1915</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7138,57 +7138,57 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-5.20</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>99.08000000000001</t>
+          <t>97.82</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>103.19</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>103.2</t>
+          <t>102.95</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>104.3</t>
+          <t>104.19</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-667.15</t>
+          <t>-887.49</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-98.76</t>
+          <t>-101.02</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7208,46 +7208,46 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>1678974082.870689</t>
+          <t>1676957626.954089</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>289264312.0</t>
+          <t>281468682.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>275009623.6</t>
+          <t>283145846.4</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>442557432.7</t>
+          <t>351622846.6</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>412480726.12</t>
+          <t>414970230.06</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-167547809</t>
+          <t>-68477000</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>18984900.35753776</t>
+          <t>-15789.41195628047</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-103171216.5056498</t>
+          <t>-104519583.1441735</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>289264312</v>
+        <v>281468682</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-5.12</t>
+          <t>-6.21</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
@@ -7311,7 +7311,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7321,12 +7321,12 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>31.52</t>
+          <t>31.56</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>40.13</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>26000</t>
+          <t>26027</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7376,22 +7376,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>97.2</t>
+          <t>97.9</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>94.1</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2248.507</t>
+          <t>3012.776</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>96.3</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7448,17 +7448,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-53.51</t>
+          <t>-37.86</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-12.56</t>
+          <t>-13.63</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7533,17 +7533,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7554,12 +7554,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>7328</t>
+          <t>1915</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -7589,42 +7589,42 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>100.42</t>
+          <t>99.08000000000001</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>103.72</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>103.4</t>
+          <t>103.2</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>104.41</t>
+          <t>104.3</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-215.80</t>
+          <t>-667.15</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-96.68</t>
+          <t>-98.76</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7644,46 +7644,46 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>1678974082.870689</t>
+          <t>1676957626.954089</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>220432535.0</t>
+          <t>289264312.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>268507044.2</t>
+          <t>275009623.6</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>577618774.1</t>
+          <t>442557432.7</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>409190484.56</t>
+          <t>412480726.12</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-309111729</t>
+          <t>-167547809</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>41195103.42357187</t>
+          <t>18984900.35753776</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-98395538.21827114</t>
+          <t>-103171216.5056498</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>220432535</v>
+        <v>289264312</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-3.94</t>
+          <t>-5.12</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>4.40</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>31.52</t>
+          <t>31.56</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>40.13</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>26000</t>
+          <t>26027</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7812,22 +7812,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>99.2</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>97.2</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>97.2</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>96.3</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-2.9</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>3626.375</t>
+          <t>2248.507</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-3.57</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-75.12</t>
+          <t>-53.51</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7959,7 +7959,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-11.57</t>
+          <t>-12.56</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7969,33 +7969,33 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>5.98</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>7328</t>
+          <t>1915</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -8010,57 +8010,57 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>101.72</t>
+          <t>100.42</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>103.96</t>
+          <t>103.72</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>103.6</t>
+          <t>103.4</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>104.44</t>
+          <t>104.41</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-109.91</t>
+          <t>-215.80</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-94.89</t>
+          <t>-96.68</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -8080,46 +8080,46 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1678974082.870689</t>
+          <t>1676957626.954089</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>360108082.0</t>
+          <t>220432535.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>286154072.8</t>
+          <t>268507044.2</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>1150276311.8</t>
+          <t>577618774.1</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>408529389.62</t>
+          <t>409190484.56</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-864122239</t>
+          <t>-309111729</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>66575220.08572514</t>
+          <t>41195103.42357187</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-80684181.04993486</t>
+          <t>-98395538.21827114</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>360108082</v>
+        <v>220432535</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-2.86</t>
+          <t>-3.94</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8163,7 +8163,7 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
@@ -8183,7 +8183,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>4.40</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>31.52</t>
+          <t>31.56</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>40.13</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>26000</t>
+          <t>26027</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8248,22 +8248,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>99.2</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>99.6</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>97.2</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2607.704</t>
+          <t>3626.375</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8320,17 +8320,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-6.62</t>
+          <t>-3.46</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-77.08</t>
+          <t>-75.12</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-8.97</t>
+          <t>-11.57</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8405,33 +8405,33 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>5.98</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>7328</t>
+          <t>1915</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8441,62 +8441,62 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>5.21</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>103.1</t>
+          <t>101.72</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>104.18</t>
+          <t>103.96</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>103.79</t>
+          <t>103.6</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>104.52</t>
+          <t>104.44</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-53.80</t>
+          <t>-109.91</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-93.49</t>
+          <t>-94.89</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8516,46 +8516,46 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>1678974082.870689</t>
+          <t>1676957626.954089</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>264455621.0</t>
+          <t>360108082.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>299044660.2</t>
+          <t>286154072.8</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>1304605197.0</t>
+          <t>1150276311.8</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>411510598.5</t>
+          <t>408529389.62</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-1005560536</t>
+          <t>-864122239</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>93349656.65584514</t>
+          <t>66575220.08572514</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-67465901.52195692</t>
+          <t>-80684181.04993486</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>264455621</v>
+        <v>360108082</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.86</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8599,7 +8599,7 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
@@ -8619,7 +8619,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>31.52</t>
+          <t>31.56</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>40.13</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>26000</t>
+          <t>26027</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8684,22 +8684,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2354.931</t>
+          <t>2607.704</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8756,17 +8756,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-6.62</t>
+          <t>-6.51</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-67.98</t>
+          <t>-77.08</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8841,17 +8841,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>3.89</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8862,12 +8862,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>7328</t>
+          <t>1915</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8877,32 +8877,32 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>16.14</t>
+          <t>5.21</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>104.9</t>
+          <t>103.1</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
@@ -8912,27 +8912,27 @@
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>104.03</t>
+          <t>103.79</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>104.57</t>
+          <t>104.52</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-25.93</t>
+          <t>-53.80</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-92.62</t>
+          <t>-93.49</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8952,46 +8952,46 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>1678974082.870689</t>
+          <t>1676957626.954089</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>240787568.0</t>
+          <t>264455621.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>420099846.8</t>
+          <t>299044660.2</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>1311901908.4</t>
+          <t>1304605197.0</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>422014478.54</t>
+          <t>411510598.5</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-891802061</t>
+          <t>-1005560536</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>122588849.0518091</t>
+          <t>93349656.65584514</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-35924670.60620415</t>
+          <t>-67465901.52195692</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>240787568</v>
+        <v>264455621</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9035,7 +9035,7 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
@@ -9055,12 +9055,12 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
@@ -9070,7 +9070,7 @@
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -9080,7 +9080,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>31.52</t>
+          <t>31.56</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -9095,12 +9095,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>40.13</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>26000</t>
+          <t>26027</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9120,17 +9120,17 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2468.394</t>
+          <t>2354.931</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9192,17 +9192,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-8.19</t>
+          <t>-6.51</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-52.97</t>
+          <t>-67.98</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-7.62</t>
+          <t>-8.97</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9277,17 +9277,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9298,77 +9298,77 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>7328</t>
+          <t>1915</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>15.62</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>30.28</t>
+          <t>16.14</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-4.45</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>107.8</t>
+          <t>104.9</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>104.1</t>
+          <t>104.18</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>104.21</t>
+          <t>104.03</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>104.62</t>
+          <t>104.57</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>8.52</t>
+          <t>-25.93</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-92.14</t>
+          <t>-92.62</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9388,46 +9388,46 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>1678974082.870689</t>
+          <t>1676957626.954089</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>256751415.0</t>
+          <t>240787568.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>610105241.8</t>
+          <t>420099846.8</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>1297204898.4</t>
+          <t>1311901908.4</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>427732003.84</t>
+          <t>422014478.54</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-687099656</t>
+          <t>-891802061</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>151409488.9896297</t>
+          <t>122588849.0518091</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>12953117.47366416</t>
+          <t>-35924670.60620415</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>256751415</v>
+        <v>240787568</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9471,7 +9471,7 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
@@ -9491,22 +9491,22 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>31.52</t>
+          <t>31.56</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9531,12 +9531,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>40.13</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>26000</t>
+          <t>26027</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9556,22 +9556,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2959.424</t>
+          <t>2468.394</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9628,17 +9628,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-9.24</t>
+          <t>-8.08</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-30.99</t>
+          <t>-52.97</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-6.73</t>
+          <t>-7.62</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9713,17 +9713,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9734,77 +9734,77 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>7328</t>
+          <t>1915</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>32.8</t>
+          <t>15.62</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>47.93</t>
+          <t>30.28</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>-4.45</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>5.35</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>109.6</t>
+          <t>107.8</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>104.03</t>
+          <t>104.1</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>104.32</t>
+          <t>104.21</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>104.64</t>
+          <t>104.62</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>46.78</t>
+          <t>8.52</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-92.31</t>
+          <t>-92.14</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9824,46 +9824,46 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>1678974082.870689</t>
+          <t>1676957626.954089</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>308667678.0</t>
+          <t>256751415.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>886730504.0</t>
+          <t>610105241.8</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>1285022286.6</t>
+          <t>1297204898.4</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>427982006.44</t>
+          <t>427732003.84</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-398291782</t>
+          <t>-687099656</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>176583374.7198053</t>
+          <t>151409488.9896297</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>80605505.49941671</t>
+          <t>12953117.47366416</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>308667678</v>
+        <v>256751415</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>31.52</t>
+          <t>31.56</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>40.13</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>26000</t>
+          <t>26027</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9992,22 +9992,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>106.5</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-4.57</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>3956.697</t>
+          <t>2959.424</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -10064,17 +10064,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-10.82</t>
+          <t>-9.13</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>58.05</t>
+          <t>-30.99</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-5.38</t>
+          <t>-6.73</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10149,17 +10149,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>6.53</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10170,182 +10170,182 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>7328</t>
+          <t>1915</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>42.41</t>
+          <t>32.8</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>69.46</t>
+          <t>47.93</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-5.89</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>7.99</t>
+          <t>5.35</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>112.1</t>
+          <t>109.6</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>103.8</t>
+          <t>104.03</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>104.4</t>
+          <t>104.32</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>104.67</t>
+          <t>104.64</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>105.65</t>
+          <t>46.78</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
+          <t>1.15</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>14.93</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr">
+        <is>
+          <t>-92.31</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>2025/10/31</t>
+        </is>
+      </c>
+      <c r="AV23" t="inlineStr">
+        <is>
+          <t>1676957626.954089</t>
+        </is>
+      </c>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>308667678.0</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>886730504.0</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>1285022286.6</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>427982006.44</t>
+        </is>
+      </c>
+      <c r="BA23" t="inlineStr">
+        <is>
+          <t>-398291782</t>
+        </is>
+      </c>
+      <c r="BB23" t="inlineStr">
+        <is>
+          <t>176583374.7198053</t>
+        </is>
+      </c>
+      <c r="BC23" t="inlineStr">
+        <is>
+          <t>80605505.49941671</t>
+        </is>
+      </c>
+      <c r="BD23" t="n">
+        <v>308667678</v>
+      </c>
+      <c r="BE23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF23" t="inlineStr">
+        <is>
+          <t>101.5</t>
+        </is>
+      </c>
+      <c r="BG23" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>2.46</t>
+        </is>
+      </c>
+      <c r="BI23" t="inlineStr">
+        <is>
+          <t>亞力</t>
+        </is>
+      </c>
+      <c r="BJ23" t="inlineStr">
+        <is>
+          <t>亞力</t>
+        </is>
+      </c>
+      <c r="BK23" t="inlineStr">
+        <is>
+          <t>電機機械</t>
+        </is>
+      </c>
+      <c r="BL23" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM23" t="inlineStr">
+        <is>
           <t>1.01</t>
         </is>
       </c>
-      <c r="AS23" t="inlineStr">
-        <is>
-          <t>14.93</t>
-        </is>
-      </c>
-      <c r="AT23" t="inlineStr">
-        <is>
-          <t>-93.21</t>
-        </is>
-      </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>2025/10/31</t>
-        </is>
-      </c>
-      <c r="AV23" t="inlineStr">
-        <is>
-          <t>1678974082.870689</t>
-        </is>
-      </c>
-      <c r="AW23" t="inlineStr">
-        <is>
-          <t>424561019.0</t>
-        </is>
-      </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>2014398550.8</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>1274536171.3</t>
-        </is>
-      </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>424494347.48</t>
-        </is>
-      </c>
-      <c r="BA23" t="inlineStr">
-        <is>
-          <t>739862379</t>
-        </is>
-      </c>
-      <c r="BB23" t="inlineStr">
-        <is>
-          <t>194033896.3962396</t>
-        </is>
-      </c>
-      <c r="BC23" t="inlineStr">
-        <is>
-          <t>168810549.3040841</t>
-        </is>
-      </c>
-      <c r="BD23" t="n">
-        <v>424561019</v>
-      </c>
-      <c r="BE23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF23" t="inlineStr">
-        <is>
-          <t>101.5</t>
-        </is>
-      </c>
-      <c r="BG23" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="BH23" t="inlineStr">
-        <is>
-          <t>3.94</t>
-        </is>
-      </c>
-      <c r="BI23" t="inlineStr">
-        <is>
-          <t>亞力</t>
-        </is>
-      </c>
-      <c r="BJ23" t="inlineStr">
-        <is>
-          <t>亞力</t>
-        </is>
-      </c>
-      <c r="BK23" t="inlineStr">
-        <is>
-          <t>電機機械</t>
-        </is>
-      </c>
-      <c r="BL23" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM23" t="inlineStr">
-        <is>
-          <t>0.99</t>
-        </is>
-      </c>
       <c r="BN23" t="inlineStr">
         <is>
           <t>-3.87807238678311</t>
@@ -10363,7 +10363,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>31.52</t>
+          <t>31.56</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>40.13</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>26000</t>
+          <t>26027</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10428,22 +10428,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>109.5</t>
+          <t>106.5</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/配電系統.xlsx
+++ b/Result/checksun_type/配電系統.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4656.178</t>
+          <t>4210.877</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>681.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.9</t>
+          <t>-6.5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>70.21</t>
+          <t>75.25</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>-7.72</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16.60</t>
+          <t>15.02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-5.28</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,77 +1014,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>229</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>4656</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-4.46</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-2.30</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>13.59</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>718.0</t>
+          <t>712.8</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>726.45</t>
+          <t>729.6</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>641.18</t>
+          <t>642.32</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>638.1</t>
+          <t>638.33</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-29.15</t>
+          <t>-38.99</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>23.12</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>32.64</t>
+          <t>29.74</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-59.58</t>
+          <t>-63.17</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>4936987441.390244</t>
+          <t>4936184159.673353</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>3308931687.0</t>
+          <t>2917531202.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>3977678243.4</t>
+          <t>4446393537.2</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>2336901368.1</t>
+          <t>2537135784.1</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>2356977274.04</t>
+          <t>2394527724.36</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>1640776875</t>
+          <t>1909257753</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-38539849.95401464</t>
+          <t>-6256666.883396398</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>258836711.484827</t>
+          <t>171300840.0050039</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>3308931687</v>
+        <v>2917531202</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-8.55</t>
+          <t>-11.79</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>49.96</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>223011</t>
+          <t>215114</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>701.0</t>
+          <t>720.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>721.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>698.0</t>
+          <t>677.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>681.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-7.07</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>12908.308</t>
+          <t>4656.178</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>688.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.9</t>
+          <t>-6.5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>62.76</t>
+          <t>70.21</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-6.78</t>
+          <t>-4.34</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>46.03</t>
+          <t>16.60</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-13.23</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,77 +1450,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>229</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>4656</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>39.68</t>
+          <t>24.72</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-5.02</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>12.71</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>724.4</t>
+          <t>718.0</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>720.75</t>
+          <t>726.45</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>639.48</t>
+          <t>641.18</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>637.48</t>
+          <t>638.1</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-24.05</t>
+          <t>-29.15</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>26.60</t>
+          <t>23.12</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>35.02</t>
+          <t>32.64</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-56.63</t>
+          <t>-59.58</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>4936987441.390244</t>
+          <t>4936184159.673353</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>9396894111.0</t>
+          <t>3308931687.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>3406595539.2</t>
+          <t>3977678243.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>2092972596.2</t>
+          <t>2336901368.1</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>2319670873.56</t>
+          <t>2356977274.04</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>1313622943</t>
+          <t>1640776875</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-92608315.67016768</t>
+          <t>-38539849.95401464</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>332708021.9386873</t>
+          <t>258836711.484827</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>9396894111</v>
+        <v>3308931687</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-10.88</t>
+          <t>-8.55</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>24.80</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>49.96</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>223011</t>
+          <t>215114</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>721.0</t>
+          <t>701.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>780.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>687.0</t>
+          <t>698.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>688.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-7.07</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>7500.722</t>
+          <t>12908.308</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>739.0</t>
+          <t>688.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-4.67</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.9</t>
+          <t>-6.5</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>32.75</t>
+          <t>62.76</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-6.78</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>26.75</t>
+          <t>46.03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-7.70</t>
+          <t>-13.23</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,17 +1886,17 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>229</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>4656</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>50.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1906,57 +1906,57 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>-5.02</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>12.71</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>731.2</t>
+          <t>724.4</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>715.55</t>
+          <t>720.75</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>638.3</t>
+          <t>639.48</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>636.88</t>
+          <t>637.48</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-12.52</t>
+          <t>-24.05</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>32.48</t>
+          <t>26.60</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>37.13</t>
+          <t>35.02</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-54.03</t>
+          <t>-56.63</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>4936987441.390244</t>
+          <t>4936184159.673353</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>5759803875.0</t>
+          <t>9396894111.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>1689450518.2</t>
+          <t>3406595539.2</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>1272693479.4</t>
+          <t>2092972596.2</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>2149905312.46</t>
+          <t>2319670873.56</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>416757038</t>
+          <t>1313622943</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-169938558.8717777</t>
+          <t>-92608315.67016768</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-225925652.1964645</t>
+          <t>332708021.9386873</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>5759803875</v>
+        <v>9396894111</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-10.88</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2089,12 +2089,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>26.64</t>
+          <t>24.80</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>49.96</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>223011</t>
+          <t>215114</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>789.0</t>
+          <t>721.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>803.0</t>
+          <t>780.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>732.0</t>
+          <t>687.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>739.0</t>
+          <t>688.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1152.161</t>
+          <t>7500.722</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>739.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-6.23</t>
+          <t>-8.52</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.9</t>
+          <t>-6.5</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-19.96</t>
+          <t>32.75</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>26.75</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>-7.70</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,77 +2322,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>229</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>4656</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>68.25</t>
+          <t>50.79</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>31.22</t>
+          <t>39.68</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>732.4</t>
+          <t>731.2</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>708.6</t>
+          <t>715.55</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>635.96</t>
+          <t>638.3</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>635.39</t>
+          <t>636.88</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-10.37</t>
+          <t>-12.52</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>34.32</t>
+          <t>32.48</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>38.29</t>
+          <t>37.13</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-52.59</t>
+          <t>-54.03</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>4936987441.390244</t>
+          <t>4936184159.673353</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>848806811.0</t>
+          <t>5759803875.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>688943827.4</t>
+          <t>1689450518.2</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>860708905.5</t>
+          <t>1272693479.4</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>2069337538.82</t>
+          <t>2149905312.46</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-171765078</t>
+          <t>416757038</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-159759087.3581983</t>
+          <t>-169938558.8717777</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-626216745.2396646</t>
+          <t>-225925652.1964645</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>848806811</v>
+        <v>5759803875</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2515,22 +2515,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>27.04</t>
+          <t>26.64</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>49.96</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>223011</t>
+          <t>215114</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>789.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>803.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>732.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>739.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>799.533</t>
+          <t>1152.161</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-10.13</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.9</t>
+          <t>-6.5</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-58.59</t>
+          <t>-19.96</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-4.20</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-4.53</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,77 +2758,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>229</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>4656</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>68.25</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>8.47</t>
+          <t>31.22</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>10.66</t>
+          <t>11.42</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>735.4</t>
+          <t>732.4</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>701.1</t>
+          <t>708.6</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>633.54</t>
+          <t>635.96</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>634.25</t>
+          <t>635.39</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-10.78</t>
+          <t>-10.37</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>34.32</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>39.28</t>
+          <t>38.29</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-51.36</t>
+          <t>-52.59</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>4936987441.390244</t>
+          <t>4936184159.673353</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>573954733.0</t>
+          <t>848806811.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>627878031.0</t>
+          <t>688943827.4</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>1516353585.7</t>
+          <t>860708905.5</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>2106062606.14</t>
+          <t>2069337538.82</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-888475554</t>
+          <t>-171765078</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-74948604.10702263</t>
+          <t>-159759087.3581983</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-649518023.2571056</t>
+          <t>-626216745.2396646</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>573954733</v>
+        <v>848806811</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-8.42</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2951,22 +2951,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>25.49</t>
+          <t>27.04</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>49.96</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>223011</t>
+          <t>215114</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>740.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>740.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>617.266</t>
+          <t>799.533</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,112 +3078,112 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>707.0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-3.82</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>-6.5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>-58.59</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2025-11-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2025-09-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>785.0</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
           <t>738.0</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>624.0</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>605.0</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>-4.20</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>29.75</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
         <is>
           <t>-4.53</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>-2.9</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>-75.86</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2025-11-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2025-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2025-09-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>785.0</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>738.0</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>785.0</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>624.0</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>605.0</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>-5.99</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>29.75</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>0.96</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,17 +3194,17 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>229</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>4656</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
@@ -3214,57 +3214,57 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>10.09</t>
+          <t>10.66</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>745.6</t>
+          <t>735.4</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>695.2</t>
+          <t>701.1</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>631.48</t>
+          <t>633.54</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>633.66</t>
+          <t>634.25</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-10.78</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>35.05</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>40.34</t>
+          <t>39.28</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-50.05</t>
+          <t>-51.36</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,50 +3284,50 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>4936987441.390244</t>
+          <t>4936184159.673353</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>453518166.0</t>
+          <t>573954733.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>696124492.8</t>
+          <t>627878031.0</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>2883970531.7</t>
+          <t>1516353585.7</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>2126707687.18</t>
+          <t>2106062606.14</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-2147483648</t>
+          <t>-888475554</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>29518563.01117429</t>
+          <t>-74948604.10702263</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-630160054.0942674</t>
+          <t>-649518023.2571056</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>453518166</v>
+        <v>573954733</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-4.40</t>
+          <t>-8.42</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>26.60</t>
+          <t>25.49</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>49.96</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>223011</t>
+          <t>215114</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>737.0</t>
+          <t>740.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>739.0</t>
+          <t>740.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>730.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>738.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1116.653</t>
+          <t>617.266</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-8.37</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.9</t>
+          <t>-6.5</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-80.90</t>
+          <t>-75.86</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>-8.03</t>
+          <t>-5.99</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,77 +3630,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>229</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>4656</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>23.47</t>
+          <t>8.47</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-3.99</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>9.29</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>10.09</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>752.0</t>
+          <t>745.6</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>688.05</t>
+          <t>695.2</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>628.72</t>
+          <t>631.48</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>632.04</t>
+          <t>633.66</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>42.23</t>
+          <t>39.85</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>40.46</t>
+          <t>40.34</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-49.89</t>
+          <t>-50.05</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,27 +3720,27 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>4936987441.390244</t>
+          <t>4936184159.673353</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>811169006.0</t>
+          <t>453518166.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>779349653.2</t>
+          <t>696124492.8</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>4079717323.9</t>
+          <t>2883970531.7</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>2168937186.34</t>
+          <t>2126707687.18</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -3750,16 +3750,16 @@
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>149460129.7576182</t>
+          <t>29518563.01117429</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-567096178.3225608</t>
+          <t>-630160054.0942674</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>811169006</v>
+        <v>453518166</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-6.48</t>
+          <t>-4.40</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>26.03</t>
+          <t>26.60</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>49.96</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>223011</t>
+          <t>215114</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>725.0</t>
+          <t>737.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>736.0</t>
+          <t>739.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>730.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1008.586</t>
+          <t>1116.653</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>745.0</t>
+          <t>722.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-5.52</t>
+          <t>-6.02</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.9</t>
+          <t>-6.5</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-82.40</t>
+          <t>-80.90</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4030,12 +4030,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>-5.10</t>
+          <t>-8.03</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,12 +4066,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>229</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>4656</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4081,62 +4081,62 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>49.94</t>
+          <t>23.47</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-3.99</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>11.02</t>
+          <t>9.29</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>8.78</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>756.8</t>
+          <t>752.0</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>681.7</t>
+          <t>688.05</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>626.7</t>
+          <t>628.72</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>630.91</t>
+          <t>632.04</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>15.69</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>46.30</t>
+          <t>42.23</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>40.02</t>
+          <t>40.46</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-50.44</t>
+          <t>-49.89</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,27 +4156,27 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>4936987441.390244</t>
+          <t>4936184159.673353</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>757270421.0</t>
+          <t>811169006.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>855936440.6</t>
+          <t>779349653.2</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>4864530439.2</t>
+          <t>4079717323.9</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>2227082877.5</t>
+          <t>2168937186.34</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -4186,16 +4186,16 @@
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>279743094.8631054</t>
+          <t>149460129.7576182</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-495071225.1371737</t>
+          <t>-567096178.3225608</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>757270421</v>
+        <v>811169006</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-3.50</t>
+          <t>-6.48</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4264,17 +4264,17 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>26.86</t>
+          <t>26.03</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>49.96</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>223011</t>
+          <t>215114</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>769.0</t>
+          <t>725.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>769.0</t>
+          <t>736.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>737.0</t>
+          <t>722.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>745.0</t>
+          <t>722.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>711.087</t>
+          <t>1008.586</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>765.0</t>
+          <t>745.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-8.36</t>
+          <t>-9.4</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.9</t>
+          <t>-6.5</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-81.30</t>
+          <t>-82.40</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-5.10</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,77 +4502,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>229</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>4656</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>70.42</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>80.35</t>
+          <t>49.94</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>13.05</t>
+          <t>11.02</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>8.78</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>760.8</t>
+          <t>756.8</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>673.0</t>
+          <t>681.7</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>624.74</t>
+          <t>626.7</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>629.5</t>
+          <t>630.91</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>26.07</t>
+          <t>15.69</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>48.47</t>
+          <t>46.30</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>38.45</t>
+          <t>40.02</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-52.39</t>
+          <t>-50.44</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,27 +4592,27 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>4936987441.390244</t>
+          <t>4936184159.673353</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>543477829.0</t>
+          <t>757270421.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>1032473983.6</t>
+          <t>855936440.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>5522062366.6</t>
+          <t>4864530439.2</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>2292721646.52</t>
+          <t>2227082877.5</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
@@ -4622,16 +4622,16 @@
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>420618425.772247</t>
+          <t>279743094.8631054</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-368722471.2960072</t>
+          <t>-495071225.1371737</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>543477829</v>
+        <v>757270421</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-3.50</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4705,12 +4705,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>27.58</t>
+          <t>26.86</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>49.96</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>223011</t>
+          <t>215114</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>765.0</t>
+          <t>769.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>770.0</t>
+          <t>769.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>759.0</t>
+          <t>737.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>765.0</t>
+          <t>745.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1193.09</t>
+          <t>711.087</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>758.0</t>
+          <t>765.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-7.37</t>
+          <t>-12.33</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.9</t>
+          <t>-6.5</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-57.71</t>
+          <t>-81.30</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.90</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,77 +4938,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>229</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>4656</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>79.41</t>
+          <t>70.42</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>82.88</t>
+          <t>80.35</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>15.48</t>
+          <t>13.05</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>6.51</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>764.8</t>
+          <t>760.8</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>662.3</t>
+          <t>673.0</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>621.8</t>
+          <t>624.74</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>627.64</t>
+          <t>629.5</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>34.94</t>
+          <t>26.07</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>48.50</t>
+          <t>48.47</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>35.94</t>
+          <t>38.45</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-55.49</t>
+          <t>-52.39</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,27 +5028,27 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>4936987441.390244</t>
+          <t>4936184159.673353</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>915187042.0</t>
+          <t>543477829.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>2404829140.4</t>
+          <t>1032473983.6</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>5686609711.2</t>
+          <t>5522062366.6</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>2312774767.92</t>
+          <t>2292721646.52</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
@@ -5058,16 +5058,16 @@
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>564134952.5119295</t>
+          <t>420618425.772247</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-152149242.6909127</t>
+          <t>-368722471.2960072</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>915187042</v>
+        <v>543477829</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>27.33</t>
+          <t>27.58</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>49.96</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>223011</t>
+          <t>215114</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>775.0</t>
+          <t>765.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>780.0</t>
+          <t>770.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>758.0</t>
+          <t>759.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>758.0</t>
+          <t>765.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1144.535</t>
+          <t>1193.09</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>770.0</t>
+          <t>758.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-9.07</t>
+          <t>-11.31</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.9</t>
+          <t>-6.5</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-15.19</t>
+          <t>-57.71</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5338,12 +5338,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>-2.90</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,77 +5374,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>229</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>4656</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>91.21</t>
+          <t>79.41</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>86.14</t>
+          <t>82.88</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>17.70</t>
+          <t>15.48</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>5.32</t>
+          <t>6.51</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>767.6</t>
+          <t>764.8</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>652.15</t>
+          <t>662.3</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>619.2</t>
+          <t>621.8</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>625.75</t>
+          <t>627.64</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>48.00</t>
+          <t>34.94</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>48.55</t>
+          <t>48.50</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>32.80</t>
+          <t>35.94</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-59.38</t>
+          <t>-55.49</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>4936987441.390244</t>
+          <t>4936184159.673353</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>869643968.0</t>
+          <t>915187042.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>5071816570.6</t>
+          <t>2404829140.4</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>5980378748.8</t>
+          <t>5686609711.2</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>2324099002.48</t>
+          <t>2312774767.92</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-908562178</t>
+          <t>-2147483648</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>694368442.54881</t>
+          <t>564134952.5119295</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>122848998.3053265</t>
+          <t>-152149242.6909127</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>869643968</v>
+        <v>915187042</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>27.76</t>
+          <t>27.33</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>49.96</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>223011</t>
+          <t>215114</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>765.0</t>
+          <t>775.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>770.0</t>
+          <t>780.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>758.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>770.0</t>
+          <t>758.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1914.684</t>
+          <t>1536.151</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>95.3</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>16.80</t>
+          <t>11.75</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-14.53</t>
+          <t>-15.25</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5789,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5810,77 +5810,77 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1536</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>13.41</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-6.38</t>
+          <t>-6.60</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>96.12</t>
+          <t>95.75999999999999</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>102.68</t>
+          <t>102.53</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>102.33</t>
+          <t>102.08</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>103.93</t>
+          <t>103.82</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-109.29</t>
+          <t>-82.43</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-106.66</t>
+          <t>-108.39</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5900,46 +5900,46 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>1676957626.954089</t>
+          <t>1674868559.974212</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>182336206.0</t>
+          <t>145859250.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>376915742.6</t>
+          <t>348234730.2</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>322711393.4</t>
+          <t>311622176.9</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>429470961.98</t>
+          <t>429640696.94</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>54204349</t>
+          <t>36612553</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-29560237.64442549</t>
+          <t>-38363178.1769636</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-75159538.47233671</t>
+          <t>-86779351.10592324</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>182336206</v>
+        <v>145859250</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-6.11</t>
+          <t>-6.90</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>31.56</t>
+          <t>31.29</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>26027</t>
+          <t>25809</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6068,22 +6068,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>95.8</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>96.3</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>95.3</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-3.53</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>7327.598</t>
+          <t>1914.684</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>95.3</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6140,17 +6140,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>14.67</t>
+          <t>16.80</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-14.62</t>
+          <t>-14.53</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6225,17 +6225,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12.09</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-4.94</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6246,77 +6246,77 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1536</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>12.88</t>
+          <t>13.41</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-6.09</t>
+          <t>-6.38</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>96.56</t>
+          <t>96.12</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>102.82</t>
+          <t>102.68</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>102.56</t>
+          <t>102.33</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>104.04</t>
+          <t>103.93</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-159.05</t>
+          <t>-109.29</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-104.84</t>
+          <t>-106.66</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6336,46 +6336,46 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>1676957626.954089</t>
+          <t>1674868559.974212</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>714004012.0</t>
+          <t>182336206.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>384535008.4</t>
+          <t>376915742.6</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>335344540.6</t>
+          <t>322711393.4</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>431976435.3</t>
+          <t>429470961.98</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>49190467</t>
+          <t>54204349</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-21269455.67571436</t>
+          <t>-29560237.64442549</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-59783782.19320107</t>
+          <t>-75159538.47233671</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>714004012</v>
+        <v>182336206</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-6.21</t>
+          <t>-6.11</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6419,7 +6419,7 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
@@ -6439,22 +6439,22 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>31.56</t>
+          <t>31.29</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>26027</t>
+          <t>25809</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6504,22 +6504,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>95.8</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>96.6</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>95.1</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>95.3</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>-3.53</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>4255.671</t>
+          <t>7327.598</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6576,17 +6576,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-3.46</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>14.67</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-11.57</t>
+          <t>-14.62</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>7.02</t>
+          <t>12.09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>-4.94</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6682,17 +6682,17 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1536</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>38.64</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
@@ -6702,57 +6702,57 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-5.63</t>
+          <t>-6.09</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>97.24000000000001</t>
+          <t>96.56</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>103.04</t>
+          <t>102.82</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>102.79</t>
+          <t>102.56</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>104.13</t>
+          <t>104.04</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-260.17</t>
+          <t>-159.05</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-102.92</t>
+          <t>-104.84</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6772,46 +6772,46 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>1676957626.954089</t>
+          <t>1674868559.974212</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>417505501.0</t>
+          <t>714004012.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>313755822.4</t>
+          <t>384535008.4</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>306400241.3</t>
+          <t>335344540.6</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>420660383.62</t>
+          <t>431976435.3</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>7355581</t>
+          <t>49190467</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-14266850.85435314</t>
+          <t>-21269455.67571436</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-92647688.78753585</t>
+          <t>-59783782.19320107</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>417505501</v>
+        <v>714004012</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-2.86</t>
+          <t>-6.21</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
@@ -6875,22 +6875,22 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6900,7 +6900,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>31.56</t>
+          <t>31.29</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>26027</t>
+          <t>25809</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6940,7 +6940,7 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>98.4</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
@@ -6950,12 +6950,12 @@
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>95.1</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2950.547</t>
+          <t>4255.671</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7012,17 +7012,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>-4.34</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-19.47</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-14.62</t>
+          <t>-11.57</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7097,17 +7097,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>7.02</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7118,77 +7118,77 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1536</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>38.64</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.88</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-5.20</t>
+          <t>-5.63</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>97.82</t>
+          <t>97.24000000000001</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>103.19</t>
+          <t>103.04</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>102.95</t>
+          <t>102.79</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>104.19</t>
+          <t>104.13</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-887.49</t>
+          <t>-260.17</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-101.02</t>
+          <t>-102.92</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7208,46 +7208,46 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>1676957626.954089</t>
+          <t>1674868559.974212</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>281468682.0</t>
+          <t>417505501.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>283145846.4</t>
+          <t>313755822.4</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>351622846.6</t>
+          <t>306400241.3</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>414970230.06</t>
+          <t>420660383.62</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-68477000</t>
+          <t>7355581</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-15789.41195628047</t>
+          <t>-14266850.85435314</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-104519583.1441735</t>
+          <t>-92647688.78753585</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>281468682</v>
+        <v>417505501</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-6.21</t>
+          <t>-2.86</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
@@ -7311,22 +7311,22 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>31.56</t>
+          <t>31.29</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>26027</t>
+          <t>25809</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7376,22 +7376,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>98.4</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>97.9</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>94.1</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>3012.776</t>
+          <t>2950.547</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7448,17 +7448,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-37.86</t>
+          <t>-19.47</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-13.63</t>
+          <t>-14.62</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7533,17 +7533,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7554,12 +7554,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1536</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7574,57 +7574,57 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-5.20</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>99.08000000000001</t>
+          <t>97.82</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>103.19</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>103.2</t>
+          <t>102.95</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>104.3</t>
+          <t>104.19</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-667.15</t>
+          <t>-887.49</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-98.76</t>
+          <t>-101.02</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7644,46 +7644,46 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>1676957626.954089</t>
+          <t>1674868559.974212</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>289264312.0</t>
+          <t>281468682.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>275009623.6</t>
+          <t>283145846.4</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>442557432.7</t>
+          <t>351622846.6</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>412480726.12</t>
+          <t>414970230.06</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-167547809</t>
+          <t>-68477000</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>18984900.35753776</t>
+          <t>-15789.41195628047</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-103171216.5056498</t>
+          <t>-104519583.1441735</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>289264312</v>
+        <v>281468682</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-5.12</t>
+          <t>-6.21</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>31.56</t>
+          <t>31.29</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>26027</t>
+          <t>25809</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7812,22 +7812,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>97.2</t>
+          <t>97.9</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>94.1</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2248.507</t>
+          <t>3012.776</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>96.3</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-53.51</t>
+          <t>-37.86</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7959,7 +7959,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-12.56</t>
+          <t>-13.63</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7969,17 +7969,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7990,12 +7990,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1536</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -8010,12 +8010,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -8025,42 +8025,42 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>100.42</t>
+          <t>99.08000000000001</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>103.72</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>103.4</t>
+          <t>103.2</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>104.41</t>
+          <t>104.3</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-215.80</t>
+          <t>-667.15</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-96.68</t>
+          <t>-98.76</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -8080,46 +8080,46 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1676957626.954089</t>
+          <t>1674868559.974212</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>220432535.0</t>
+          <t>289264312.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>268507044.2</t>
+          <t>275009623.6</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>577618774.1</t>
+          <t>442557432.7</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>409190484.56</t>
+          <t>412480726.12</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-309111729</t>
+          <t>-167547809</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>41195103.42357187</t>
+          <t>18984900.35753776</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-98395538.21827114</t>
+          <t>-103171216.5056498</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>220432535</v>
+        <v>289264312</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-3.94</t>
+          <t>-5.12</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8163,7 +8163,7 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
@@ -8183,7 +8183,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>4.40</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>31.56</t>
+          <t>31.29</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>26027</t>
+          <t>25809</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8248,22 +8248,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>99.2</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>97.2</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>97.2</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>96.3</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-2.9</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>3626.375</t>
+          <t>2248.507</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8320,17 +8320,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-3.46</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-75.12</t>
+          <t>-53.51</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-11.57</t>
+          <t>-12.56</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8405,33 +8405,33 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>5.98</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1536</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8446,57 +8446,57 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>101.72</t>
+          <t>100.42</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>103.96</t>
+          <t>103.72</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>103.6</t>
+          <t>103.4</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>104.44</t>
+          <t>104.41</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-109.91</t>
+          <t>-215.80</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-94.89</t>
+          <t>-96.68</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8516,46 +8516,46 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>1676957626.954089</t>
+          <t>1674868559.974212</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>360108082.0</t>
+          <t>220432535.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>286154072.8</t>
+          <t>268507044.2</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>1150276311.8</t>
+          <t>577618774.1</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>408529389.62</t>
+          <t>409190484.56</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-864122239</t>
+          <t>-309111729</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>66575220.08572514</t>
+          <t>41195103.42357187</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-80684181.04993486</t>
+          <t>-98395538.21827114</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>360108082</v>
+        <v>220432535</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-2.86</t>
+          <t>-3.94</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8599,7 +8599,7 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
@@ -8619,7 +8619,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>4.40</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>31.56</t>
+          <t>31.29</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>26027</t>
+          <t>25809</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8684,22 +8684,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>99.2</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>99.6</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>97.2</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2607.704</t>
+          <t>3626.375</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8756,17 +8756,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-6.51</t>
+          <t>-4.34</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-77.08</t>
+          <t>-75.12</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-8.97</t>
+          <t>-11.57</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8841,33 +8841,33 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>5.98</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1536</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8877,62 +8877,62 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>5.21</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>103.1</t>
+          <t>101.72</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>104.18</t>
+          <t>103.96</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>103.79</t>
+          <t>103.6</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>104.52</t>
+          <t>104.44</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-53.80</t>
+          <t>-109.91</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-93.49</t>
+          <t>-94.89</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8952,46 +8952,46 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>1676957626.954089</t>
+          <t>1674868559.974212</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>264455621.0</t>
+          <t>360108082.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>299044660.2</t>
+          <t>286154072.8</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>1304605197.0</t>
+          <t>1150276311.8</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>411510598.5</t>
+          <t>408529389.62</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-1005560536</t>
+          <t>-864122239</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>93349656.65584514</t>
+          <t>66575220.08572514</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-67465901.52195692</t>
+          <t>-80684181.04993486</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>264455621</v>
+        <v>360108082</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.86</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -9035,7 +9035,7 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
@@ -9055,7 +9055,7 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -9065,12 +9065,12 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -9080,7 +9080,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>31.56</t>
+          <t>31.29</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -9095,12 +9095,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>26027</t>
+          <t>25809</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9120,22 +9120,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2354.931</t>
+          <t>2607.704</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9192,17 +9192,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-6.51</t>
+          <t>-7.41</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-67.98</t>
+          <t>-77.08</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9277,17 +9277,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>3.89</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9298,12 +9298,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1536</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9313,32 +9313,32 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>16.14</t>
+          <t>5.21</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>104.9</t>
+          <t>103.1</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
@@ -9348,27 +9348,27 @@
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>104.03</t>
+          <t>103.79</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>104.57</t>
+          <t>104.52</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-25.93</t>
+          <t>-53.80</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-92.62</t>
+          <t>-93.49</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9388,46 +9388,46 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>1676957626.954089</t>
+          <t>1674868559.974212</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>240787568.0</t>
+          <t>264455621.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>420099846.8</t>
+          <t>299044660.2</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>1311901908.4</t>
+          <t>1304605197.0</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>422014478.54</t>
+          <t>411510598.5</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-891802061</t>
+          <t>-1005560536</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>122588849.0518091</t>
+          <t>93349656.65584514</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-35924670.60620415</t>
+          <t>-67465901.52195692</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>240787568</v>
+        <v>264455621</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9471,7 +9471,7 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9506,7 +9506,7 @@
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>31.56</t>
+          <t>31.29</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9531,12 +9531,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>26027</t>
+          <t>25809</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9556,17 +9556,17 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2468.394</t>
+          <t>2354.931</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9628,17 +9628,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-8.08</t>
+          <t>-7.41</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-52.97</t>
+          <t>-67.98</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-7.62</t>
+          <t>-8.97</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9713,17 +9713,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9734,77 +9734,77 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1536</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>15.62</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>30.28</t>
+          <t>16.14</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-4.45</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>107.8</t>
+          <t>104.9</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>104.1</t>
+          <t>104.18</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>104.21</t>
+          <t>104.03</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>104.62</t>
+          <t>104.57</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>8.52</t>
+          <t>-25.93</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-92.14</t>
+          <t>-92.62</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9824,46 +9824,46 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>1676957626.954089</t>
+          <t>1674868559.974212</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>256751415.0</t>
+          <t>240787568.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>610105241.8</t>
+          <t>420099846.8</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>1297204898.4</t>
+          <t>1311901908.4</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>427732003.84</t>
+          <t>422014478.54</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-687099656</t>
+          <t>-891802061</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>151409488.9896297</t>
+          <t>122588849.0518091</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>12953117.47366416</t>
+          <t>-35924670.60620415</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>256751415</v>
+        <v>240787568</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>31.56</t>
+          <t>31.29</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>26027</t>
+          <t>25809</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9992,22 +9992,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2959.424</t>
+          <t>2468.394</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -10064,17 +10064,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-9.13</t>
+          <t>-8.99</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-30.99</t>
+          <t>-52.97</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-6.73</t>
+          <t>-7.62</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10149,17 +10149,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10170,77 +10170,77 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1536</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>32.8</t>
+          <t>15.62</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>47.93</t>
+          <t>30.28</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>-4.45</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>5.35</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>109.6</t>
+          <t>107.8</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>104.03</t>
+          <t>104.1</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>104.32</t>
+          <t>104.21</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>104.64</t>
+          <t>104.62</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>46.78</t>
+          <t>8.52</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-92.31</t>
+          <t>-92.14</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10260,46 +10260,46 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>1676957626.954089</t>
+          <t>1674868559.974212</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>308667678.0</t>
+          <t>256751415.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>886730504.0</t>
+          <t>610105241.8</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>1285022286.6</t>
+          <t>1297204898.4</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>427982006.44</t>
+          <t>427732003.84</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-398291782</t>
+          <t>-687099656</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>176583374.7198053</t>
+          <t>151409488.9896297</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>80605505.49941671</t>
+          <t>12953117.47366416</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>308667678</v>
+        <v>256751415</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10343,7 +10343,7 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>31.56</t>
+          <t>31.29</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>26027</t>
+          <t>25809</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10428,22 +10428,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>106.5</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/配電系統.xlsx
+++ b/Result/checksun_type/配電系統.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4210.877</t>
+          <t>3102.28</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>681.0</t>
+          <t>695.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-6.5</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>75.25</t>
+          <t>74.46</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-7.72</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15.02</t>
+          <t>11.06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-5.28</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,77 +1014,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>99</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>3102</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.29</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>14.56</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-4.46</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-2.30</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>13.59</t>
+          <t>13.98</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>712.8</t>
+          <t>701.8</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>729.6</t>
+          <t>734.15</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>642.32</t>
+          <t>644.12</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>638.33</t>
+          <t>638.67</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-38.99</t>
+          <t>-43.51</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>15.15</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>29.74</t>
+          <t>26.82</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-63.17</t>
+          <t>-66.78</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>4936184159.673353</t>
+          <t>4933726257.051502</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>2917531202.0</t>
+          <t>2145406818.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>4446393537.2</t>
+          <t>4705713538.6</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>2537135784.1</t>
+          <t>2697328683.0</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>2394527724.36</t>
+          <t>2381458909.08</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>1909257753</t>
+          <t>2008384855</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-6256666.883396398</t>
+          <t>2064955.740049592</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>171300840.0050039</t>
+          <t>47833880.16900253</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>2917531202</v>
+        <v>2145406818</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-11.79</t>
+          <t>-9.97</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>49.96</t>
+          <t>50.99</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>215114</t>
+          <t>219537</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>720.0</t>
+          <t>689.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>721.0</t>
+          <t>704.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>681.0</t>
+          <t>695.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4656.178</t>
+          <t>4210.877</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>681.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-6.5</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>70.21</t>
+          <t>75.25</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>-7.72</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16.60</t>
+          <t>15.02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-5.28</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,77 +1450,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>99</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>3102</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-4.46</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-2.30</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>13.59</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>718.0</t>
+          <t>712.8</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>726.45</t>
+          <t>729.6</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>641.18</t>
+          <t>642.32</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>638.1</t>
+          <t>638.33</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-29.15</t>
+          <t>-38.99</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>23.12</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>32.64</t>
+          <t>29.74</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-59.58</t>
+          <t>-63.17</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>4936184159.673353</t>
+          <t>4933726257.051502</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>3308931687.0</t>
+          <t>2917531202.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>3977678243.4</t>
+          <t>4446393537.2</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>2336901368.1</t>
+          <t>2537135784.1</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>2356977274.04</t>
+          <t>2394527724.36</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>1640776875</t>
+          <t>1909257753</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-38539849.95401464</t>
+          <t>-6256666.883396398</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>258836711.484827</t>
+          <t>171300840.0050039</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>3308931687</v>
+        <v>2917531202</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-8.55</t>
+          <t>-11.79</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1648,17 +1648,17 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>49.96</t>
+          <t>50.99</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>215114</t>
+          <t>219537</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>701.0</t>
+          <t>720.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>721.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>698.0</t>
+          <t>677.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>681.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-7.07</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>12908.308</t>
+          <t>4656.178</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>688.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-6.5</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>62.76</t>
+          <t>70.21</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-6.78</t>
+          <t>-4.34</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>46.03</t>
+          <t>16.60</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-13.23</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,77 +1886,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>99</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>3102</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>39.68</t>
+          <t>24.72</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-5.02</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>12.71</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>724.4</t>
+          <t>718.0</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>720.75</t>
+          <t>726.45</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>639.48</t>
+          <t>641.18</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>637.48</t>
+          <t>638.1</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-24.05</t>
+          <t>-29.15</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>26.60</t>
+          <t>23.12</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>35.02</t>
+          <t>32.64</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-56.63</t>
+          <t>-59.58</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>4936184159.673353</t>
+          <t>4933726257.051502</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>9396894111.0</t>
+          <t>3308931687.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>3406595539.2</t>
+          <t>3977678243.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>2092972596.2</t>
+          <t>2336901368.1</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>2319670873.56</t>
+          <t>2356977274.04</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>1313622943</t>
+          <t>1640776875</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-92608315.67016768</t>
+          <t>-38539849.95401464</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>332708021.9386873</t>
+          <t>258836711.484827</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>9396894111</v>
+        <v>3308931687</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-10.88</t>
+          <t>-8.55</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2089,12 +2089,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>24.80</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>49.96</t>
+          <t>50.99</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>215114</t>
+          <t>219537</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>721.0</t>
+          <t>701.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>780.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>687.0</t>
+          <t>698.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>688.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-7.07</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7500.722</t>
+          <t>12908.308</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>739.0</t>
+          <t>688.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-8.52</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-6.5</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>32.75</t>
+          <t>62.76</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-6.78</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>26.75</t>
+          <t>46.03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-7.70</t>
+          <t>-13.23</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,17 +2322,17 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>99</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>3102</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>50.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -2342,57 +2342,57 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>-5.02</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>12.71</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>731.2</t>
+          <t>724.4</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>715.55</t>
+          <t>720.75</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>638.3</t>
+          <t>639.48</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>636.88</t>
+          <t>637.48</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-12.52</t>
+          <t>-24.05</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>32.48</t>
+          <t>26.60</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>37.13</t>
+          <t>35.02</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-54.03</t>
+          <t>-56.63</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>4936184159.673353</t>
+          <t>4933726257.051502</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>5759803875.0</t>
+          <t>9396894111.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>1689450518.2</t>
+          <t>3406595539.2</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>1272693479.4</t>
+          <t>2092972596.2</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>2149905312.46</t>
+          <t>2319670873.56</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>416757038</t>
+          <t>1313622943</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-169938558.8717777</t>
+          <t>-92608315.67016768</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-225925652.1964645</t>
+          <t>332708021.9386873</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>5759803875</v>
+        <v>9396894111</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-10.88</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>26.64</t>
+          <t>24.80</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>49.96</t>
+          <t>50.99</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>215114</t>
+          <t>219537</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>789.0</t>
+          <t>721.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>803.0</t>
+          <t>780.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>732.0</t>
+          <t>687.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>739.0</t>
+          <t>688.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1152.161</t>
+          <t>7500.722</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>739.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-10.13</t>
+          <t>-6.33</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-6.5</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-19.96</t>
+          <t>32.75</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>26.75</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>-7.70</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,77 +2758,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>99</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>3102</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>68.25</t>
+          <t>50.79</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>31.22</t>
+          <t>39.68</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>732.4</t>
+          <t>731.2</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>708.6</t>
+          <t>715.55</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>635.96</t>
+          <t>638.3</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>635.39</t>
+          <t>636.88</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-10.37</t>
+          <t>-12.52</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>34.32</t>
+          <t>32.48</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>38.29</t>
+          <t>37.13</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-52.59</t>
+          <t>-54.03</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>4936184159.673353</t>
+          <t>4933726257.051502</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>848806811.0</t>
+          <t>5759803875.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>688943827.4</t>
+          <t>1689450518.2</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>860708905.5</t>
+          <t>1272693479.4</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>2069337538.82</t>
+          <t>2149905312.46</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-171765078</t>
+          <t>416757038</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-159759087.3581983</t>
+          <t>-169938558.8717777</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-626216745.2396646</t>
+          <t>-225925652.1964645</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>848806811</v>
+        <v>5759803875</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2951,22 +2951,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>27.04</t>
+          <t>26.64</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>49.96</t>
+          <t>50.99</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>215114</t>
+          <t>219537</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>789.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>803.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>732.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>739.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>799.533</t>
+          <t>1152.161</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-3.82</t>
+          <t>-7.91</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-6.5</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-58.59</t>
+          <t>-19.96</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-4.20</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-4.53</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,77 +3194,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>99</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>3102</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>68.25</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>8.47</t>
+          <t>31.22</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>10.66</t>
+          <t>11.42</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>735.4</t>
+          <t>732.4</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>701.1</t>
+          <t>708.6</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>633.54</t>
+          <t>635.96</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>634.25</t>
+          <t>635.39</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-10.78</t>
+          <t>-10.37</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>34.32</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>39.28</t>
+          <t>38.29</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-51.36</t>
+          <t>-52.59</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>4936184159.673353</t>
+          <t>4933726257.051502</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>573954733.0</t>
+          <t>848806811.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>627878031.0</t>
+          <t>688943827.4</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>1516353585.7</t>
+          <t>860708905.5</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>2106062606.14</t>
+          <t>2069337538.82</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-888475554</t>
+          <t>-171765078</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-74948604.10702263</t>
+          <t>-159759087.3581983</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-649518023.2571056</t>
+          <t>-626216745.2396646</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>573954733</v>
+        <v>848806811</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-8.42</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3387,22 +3387,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>25.49</t>
+          <t>27.04</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>49.96</t>
+          <t>50.99</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>215114</t>
+          <t>219537</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>740.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>740.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>617.266</t>
+          <t>799.533</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,72 +3514,72 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>707.0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-1.73</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>-4.01</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>-58.59</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2025-11-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2025-09-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>785.0</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
           <t>738.0</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>-8.37</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>-6.5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>-75.86</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>2025-11-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2025-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2025-09-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>785.0</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>738.0</t>
-        </is>
-      </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>785.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>-5.99</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>-4.53</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,17 +3630,17 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>99</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>3102</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -3650,57 +3650,57 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>10.09</t>
+          <t>10.66</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>745.6</t>
+          <t>735.4</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>695.2</t>
+          <t>701.1</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>631.48</t>
+          <t>633.54</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>633.66</t>
+          <t>634.25</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-10.78</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>35.05</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>40.34</t>
+          <t>39.28</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-50.05</t>
+          <t>-51.36</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,50 +3720,50 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>4936184159.673353</t>
+          <t>4933726257.051502</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>453518166.0</t>
+          <t>573954733.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>696124492.8</t>
+          <t>627878031.0</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>2883970531.7</t>
+          <t>1516353585.7</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>2126707687.18</t>
+          <t>2106062606.14</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-2147483648</t>
+          <t>-888475554</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>29518563.01117429</t>
+          <t>-74948604.10702263</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-630160054.0942674</t>
+          <t>-649518023.2571056</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>453518166</v>
+        <v>573954733</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-4.40</t>
+          <t>-8.42</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>26.60</t>
+          <t>25.49</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>49.96</t>
+          <t>50.99</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>215114</t>
+          <t>219537</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>737.0</t>
+          <t>740.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>739.0</t>
+          <t>740.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>730.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>738.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1116.653</t>
+          <t>617.266</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-6.02</t>
+          <t>-6.19</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-6.5</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-80.90</t>
+          <t>-75.86</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4030,12 +4030,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>-8.03</t>
+          <t>-5.99</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,77 +4066,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>99</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>3102</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>23.47</t>
+          <t>8.47</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-3.99</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>9.29</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>10.09</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>752.0</t>
+          <t>745.6</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>688.05</t>
+          <t>695.2</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>628.72</t>
+          <t>631.48</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>632.04</t>
+          <t>633.66</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>42.23</t>
+          <t>39.85</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>40.46</t>
+          <t>40.34</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-49.89</t>
+          <t>-50.05</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,27 +4156,27 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>4936184159.673353</t>
+          <t>4933726257.051502</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>811169006.0</t>
+          <t>453518166.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>779349653.2</t>
+          <t>696124492.8</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>4079717323.9</t>
+          <t>2883970531.7</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>2168937186.34</t>
+          <t>2126707687.18</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -4186,16 +4186,16 @@
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>149460129.7576182</t>
+          <t>29518563.01117429</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-567096178.3225608</t>
+          <t>-630160054.0942674</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>811169006</v>
+        <v>453518166</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-6.48</t>
+          <t>-4.40</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>26.03</t>
+          <t>26.60</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>49.96</t>
+          <t>50.99</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>215114</t>
+          <t>219537</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>725.0</t>
+          <t>737.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>736.0</t>
+          <t>739.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>730.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1008.586</t>
+          <t>1116.653</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>745.0</t>
+          <t>722.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-9.4</t>
+          <t>-3.88</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-6.5</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-82.40</t>
+          <t>-80.90</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>-5.10</t>
+          <t>-8.03</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,12 +4502,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>99</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>3102</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4517,62 +4517,62 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>49.94</t>
+          <t>23.47</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-3.99</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>11.02</t>
+          <t>9.29</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>8.78</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>756.8</t>
+          <t>752.0</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>681.7</t>
+          <t>688.05</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>626.7</t>
+          <t>628.72</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>630.91</t>
+          <t>632.04</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>15.69</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>46.30</t>
+          <t>42.23</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>40.02</t>
+          <t>40.46</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-50.44</t>
+          <t>-49.89</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,27 +4592,27 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>4936184159.673353</t>
+          <t>4933726257.051502</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>757270421.0</t>
+          <t>811169006.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>855936440.6</t>
+          <t>779349653.2</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>4864530439.2</t>
+          <t>4079717323.9</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>2227082877.5</t>
+          <t>2168937186.34</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
@@ -4622,16 +4622,16 @@
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>279743094.8631054</t>
+          <t>149460129.7576182</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-495071225.1371737</t>
+          <t>-567096178.3225608</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>757270421</v>
+        <v>811169006</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-3.50</t>
+          <t>-6.48</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4700,17 +4700,17 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>26.86</t>
+          <t>26.03</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>49.96</t>
+          <t>50.99</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>215114</t>
+          <t>219537</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>769.0</t>
+          <t>725.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>769.0</t>
+          <t>736.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>737.0</t>
+          <t>722.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>745.0</t>
+          <t>722.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>711.087</t>
+          <t>1008.586</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>765.0</t>
+          <t>745.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-12.33</t>
+          <t>-7.19</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-6.5</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-81.30</t>
+          <t>-82.40</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-5.10</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,77 +4938,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>99</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>3102</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>70.42</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>80.35</t>
+          <t>49.94</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>13.05</t>
+          <t>11.02</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>8.78</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>760.8</t>
+          <t>756.8</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>673.0</t>
+          <t>681.7</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>624.74</t>
+          <t>626.7</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>629.5</t>
+          <t>630.91</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>26.07</t>
+          <t>15.69</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>48.47</t>
+          <t>46.30</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>38.45</t>
+          <t>40.02</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-52.39</t>
+          <t>-50.44</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,27 +5028,27 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>4936184159.673353</t>
+          <t>4933726257.051502</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>543477829.0</t>
+          <t>757270421.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>1032473983.6</t>
+          <t>855936440.6</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>5522062366.6</t>
+          <t>4864530439.2</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>2292721646.52</t>
+          <t>2227082877.5</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
@@ -5058,16 +5058,16 @@
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>420618425.772247</t>
+          <t>279743094.8631054</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-368722471.2960072</t>
+          <t>-495071225.1371737</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>543477829</v>
+        <v>757270421</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-3.50</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>27.58</t>
+          <t>26.86</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>49.96</t>
+          <t>50.99</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>215114</t>
+          <t>219537</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>765.0</t>
+          <t>769.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>770.0</t>
+          <t>769.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>759.0</t>
+          <t>737.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>765.0</t>
+          <t>745.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1193.09</t>
+          <t>711.087</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>758.0</t>
+          <t>765.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-11.31</t>
+          <t>-10.07</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-6.5</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-57.71</t>
+          <t>-81.30</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5338,12 +5338,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.90</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,77 +5374,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>99</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>3102</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>79.41</t>
+          <t>70.42</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>82.88</t>
+          <t>80.35</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>15.48</t>
+          <t>13.05</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>6.51</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>764.8</t>
+          <t>760.8</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>662.3</t>
+          <t>673.0</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>621.8</t>
+          <t>624.74</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>627.64</t>
+          <t>629.5</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>34.94</t>
+          <t>26.07</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>48.50</t>
+          <t>48.47</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>35.94</t>
+          <t>38.45</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-55.49</t>
+          <t>-52.39</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,27 +5464,27 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>4936184159.673353</t>
+          <t>4933726257.051502</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>915187042.0</t>
+          <t>543477829.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>2404829140.4</t>
+          <t>1032473983.6</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>5686609711.2</t>
+          <t>5522062366.6</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>2312774767.92</t>
+          <t>2292721646.52</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
@@ -5494,16 +5494,16 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>564134952.5119295</t>
+          <t>420618425.772247</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-152149242.6909127</t>
+          <t>-368722471.2960072</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>915187042</v>
+        <v>543477829</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>27.33</t>
+          <t>27.58</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>49.96</t>
+          <t>50.99</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>215114</t>
+          <t>219537</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>775.0</t>
+          <t>765.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>780.0</t>
+          <t>770.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>758.0</t>
+          <t>759.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>758.0</t>
+          <t>765.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1536.151</t>
+          <t>1654.541</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>97.2</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>11.75</t>
+          <t>6.72</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-15.25</t>
+          <t>-12.83</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5789,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5810,77 +5810,77 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>1536</t>
+          <t>1655</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>65.85</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>22.48</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-6.60</t>
+          <t>-6.18</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>95.75999999999999</t>
+          <t>96.16</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>102.53</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>102.08</t>
+          <t>101.88</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>103.82</t>
+          <t>103.75</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-82.43</t>
+          <t>-52.73</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-108.39</t>
+          <t>-109.67</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5900,46 +5900,46 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>1674868559.974212</t>
+          <t>1672815479.585837</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>145859250.0</t>
+          <t>159843579.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>348234730.2</t>
+          <t>323909709.6</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>311622176.9</t>
+          <t>303527778.0</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>429640696.94</t>
+          <t>427891465.06</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>36612553</t>
+          <t>20381931</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-38363178.1769636</t>
+          <t>-46568060.22616701</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-86779351.10592324</t>
+          <t>-91694911.4967857</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>145859250</v>
+        <v>159843579</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-6.90</t>
+          <t>-4.24</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>31.29</t>
+          <t>32.19</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>25809</t>
+          <t>26546</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6068,22 +6068,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>97.2</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>97.2</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1914.684</t>
+          <t>1536.151</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>95.3</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6140,17 +6140,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>16.80</t>
+          <t>11.75</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-14.53</t>
+          <t>-15.25</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6225,17 +6225,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6246,77 +6246,77 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>1536</t>
+          <t>1655</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>13.41</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-6.38</t>
+          <t>-6.60</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>96.12</t>
+          <t>95.75999999999999</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>102.68</t>
+          <t>102.53</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>102.33</t>
+          <t>102.08</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>103.93</t>
+          <t>103.82</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-109.29</t>
+          <t>-82.43</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-106.66</t>
+          <t>-108.39</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6336,46 +6336,46 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>1674868559.974212</t>
+          <t>1672815479.585837</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>182336206.0</t>
+          <t>145859250.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>376915742.6</t>
+          <t>348234730.2</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>322711393.4</t>
+          <t>311622176.9</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>429470961.98</t>
+          <t>429640696.94</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>54204349</t>
+          <t>36612553</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-29560237.64442549</t>
+          <t>-38363178.1769636</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-75159538.47233671</t>
+          <t>-86779351.10592324</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>182336206</v>
+        <v>145859250</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-6.11</t>
+          <t>-6.90</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6439,22 +6439,22 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>31.29</t>
+          <t>32.19</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>25809</t>
+          <t>26546</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6504,22 +6504,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>95.8</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>96.3</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>95.3</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-3.53</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>7327.598</t>
+          <t>1914.684</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>95.3</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6576,17 +6576,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>14.67</t>
+          <t>16.80</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-14.62</t>
+          <t>-14.53</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12.09</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-4.94</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6682,77 +6682,77 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>1536</t>
+          <t>1655</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>12.88</t>
+          <t>13.41</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-6.09</t>
+          <t>-6.38</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>96.56</t>
+          <t>96.12</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>102.82</t>
+          <t>102.68</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>102.56</t>
+          <t>102.33</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>104.04</t>
+          <t>103.93</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-159.05</t>
+          <t>-109.29</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-104.84</t>
+          <t>-106.66</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6772,46 +6772,46 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>1674868559.974212</t>
+          <t>1672815479.585837</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>714004012.0</t>
+          <t>182336206.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>384535008.4</t>
+          <t>376915742.6</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>335344540.6</t>
+          <t>322711393.4</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>431976435.3</t>
+          <t>429470961.98</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>49190467</t>
+          <t>54204349</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-21269455.67571436</t>
+          <t>-29560237.64442549</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-59783782.19320107</t>
+          <t>-75159538.47233671</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>714004012</v>
+        <v>182336206</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-6.21</t>
+          <t>-6.11</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6875,22 +6875,22 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6900,7 +6900,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>31.29</t>
+          <t>32.19</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>25809</t>
+          <t>26546</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6940,22 +6940,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>95.8</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>96.6</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>95.1</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>95.3</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>-3.53</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>4255.671</t>
+          <t>7327.598</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7012,17 +7012,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>14.67</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-11.57</t>
+          <t>-14.62</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7097,17 +7097,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>7.02</t>
+          <t>12.09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>-4.94</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7118,17 +7118,17 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>1536</t>
+          <t>1655</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>38.64</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
@@ -7138,57 +7138,57 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-5.63</t>
+          <t>-6.09</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>97.24000000000001</t>
+          <t>96.56</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>103.04</t>
+          <t>102.82</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>102.79</t>
+          <t>102.56</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>104.13</t>
+          <t>104.04</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-260.17</t>
+          <t>-159.05</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-102.92</t>
+          <t>-104.84</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7208,46 +7208,46 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>1674868559.974212</t>
+          <t>1672815479.585837</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>417505501.0</t>
+          <t>714004012.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>313755822.4</t>
+          <t>384535008.4</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>306400241.3</t>
+          <t>335344540.6</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>420660383.62</t>
+          <t>431976435.3</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>7355581</t>
+          <t>49190467</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-14266850.85435314</t>
+          <t>-21269455.67571436</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-92647688.78753585</t>
+          <t>-59783782.19320107</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>417505501</v>
+        <v>714004012</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-2.86</t>
+          <t>-6.21</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7311,22 +7311,22 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>31.29</t>
+          <t>32.19</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>25809</t>
+          <t>26546</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>98.4</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>95.1</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2950.547</t>
+          <t>4255.671</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7448,17 +7448,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-19.47</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-14.62</t>
+          <t>-11.57</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7533,17 +7533,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>7.02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7554,77 +7554,77 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>1536</t>
+          <t>1655</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>38.64</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.88</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-5.20</t>
+          <t>-5.63</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>97.82</t>
+          <t>97.24000000000001</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>103.19</t>
+          <t>103.04</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>102.95</t>
+          <t>102.79</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>104.19</t>
+          <t>104.13</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-887.49</t>
+          <t>-260.17</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-101.02</t>
+          <t>-102.92</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7644,46 +7644,46 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>1674868559.974212</t>
+          <t>1672815479.585837</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>281468682.0</t>
+          <t>417505501.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>283145846.4</t>
+          <t>313755822.4</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>351622846.6</t>
+          <t>306400241.3</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>414970230.06</t>
+          <t>420660383.62</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-68477000</t>
+          <t>7355581</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-15789.41195628047</t>
+          <t>-14266850.85435314</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-104519583.1441735</t>
+          <t>-92647688.78753585</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>281468682</v>
+        <v>417505501</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-6.21</t>
+          <t>-2.86</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7747,22 +7747,22 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>31.29</t>
+          <t>32.19</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>25809</t>
+          <t>26546</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7812,22 +7812,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>98.4</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>97.9</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>94.1</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>3012.776</t>
+          <t>2950.547</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-1.9</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-37.86</t>
+          <t>-19.47</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7959,7 +7959,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-13.63</t>
+          <t>-14.62</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7969,17 +7969,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7990,12 +7990,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>1536</t>
+          <t>1655</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -8010,57 +8010,57 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-5.20</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>99.08000000000001</t>
+          <t>97.82</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>103.19</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>103.2</t>
+          <t>102.95</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>104.3</t>
+          <t>104.19</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-667.15</t>
+          <t>-887.49</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-98.76</t>
+          <t>-101.02</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -8080,46 +8080,46 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1674868559.974212</t>
+          <t>1672815479.585837</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>289264312.0</t>
+          <t>281468682.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>275009623.6</t>
+          <t>283145846.4</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>442557432.7</t>
+          <t>351622846.6</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>412480726.12</t>
+          <t>414970230.06</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-167547809</t>
+          <t>-68477000</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>18984900.35753776</t>
+          <t>-15789.41195628047</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-103171216.5056498</t>
+          <t>-104519583.1441735</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>289264312</v>
+        <v>281468682</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-5.12</t>
+          <t>-6.21</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8183,7 +8183,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>31.29</t>
+          <t>32.19</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>25809</t>
+          <t>26546</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8248,22 +8248,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>97.2</t>
+          <t>97.9</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>94.1</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2248.507</t>
+          <t>3012.776</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>96.3</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8320,17 +8320,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-53.51</t>
+          <t>-37.86</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-12.56</t>
+          <t>-13.63</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8426,12 +8426,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>1536</t>
+          <t>1655</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -8461,42 +8461,42 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>100.42</t>
+          <t>99.08000000000001</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>103.72</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>103.4</t>
+          <t>103.2</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>104.41</t>
+          <t>104.3</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-215.80</t>
+          <t>-667.15</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-96.68</t>
+          <t>-98.76</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8516,46 +8516,46 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>1674868559.974212</t>
+          <t>1672815479.585837</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>220432535.0</t>
+          <t>289264312.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>268507044.2</t>
+          <t>275009623.6</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>577618774.1</t>
+          <t>442557432.7</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>409190484.56</t>
+          <t>412480726.12</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-309111729</t>
+          <t>-167547809</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>41195103.42357187</t>
+          <t>18984900.35753776</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-98395538.21827114</t>
+          <t>-103171216.5056498</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>220432535</v>
+        <v>289264312</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-3.94</t>
+          <t>-5.12</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8619,7 +8619,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>4.40</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>31.29</t>
+          <t>32.19</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>25809</t>
+          <t>26546</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8684,22 +8684,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>99.2</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>97.2</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>97.2</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>96.3</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-2.9</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3626.375</t>
+          <t>2248.507</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8756,17 +8756,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-75.12</t>
+          <t>-53.51</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-11.57</t>
+          <t>-12.56</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8841,33 +8841,33 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>5.98</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>1536</t>
+          <t>1655</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8882,57 +8882,57 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>101.72</t>
+          <t>100.42</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>103.96</t>
+          <t>103.72</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>103.6</t>
+          <t>103.4</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>104.44</t>
+          <t>104.41</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-109.91</t>
+          <t>-215.80</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-94.89</t>
+          <t>-96.68</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8952,46 +8952,46 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>1674868559.974212</t>
+          <t>1672815479.585837</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>360108082.0</t>
+          <t>220432535.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>286154072.8</t>
+          <t>268507044.2</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>1150276311.8</t>
+          <t>577618774.1</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>408529389.62</t>
+          <t>409190484.56</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-864122239</t>
+          <t>-309111729</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>66575220.08572514</t>
+          <t>41195103.42357187</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-80684181.04993486</t>
+          <t>-98395538.21827114</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>360108082</v>
+        <v>220432535</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-2.86</t>
+          <t>-3.94</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -9055,7 +9055,7 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -9065,12 +9065,12 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>4.40</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -9080,7 +9080,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>31.29</t>
+          <t>32.19</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -9095,12 +9095,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>25809</t>
+          <t>26546</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9120,22 +9120,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>99.2</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>99.6</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>97.2</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2607.704</t>
+          <t>3626.375</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9192,17 +9192,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-7.41</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-77.08</t>
+          <t>-75.12</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-8.97</t>
+          <t>-11.57</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9277,33 +9277,33 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>5.98</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>1536</t>
+          <t>1655</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9313,62 +9313,62 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>5.21</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>103.1</t>
+          <t>101.72</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>104.18</t>
+          <t>103.96</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>103.79</t>
+          <t>103.6</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>104.52</t>
+          <t>104.44</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-53.80</t>
+          <t>-109.91</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-93.49</t>
+          <t>-94.89</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9388,46 +9388,46 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>1674868559.974212</t>
+          <t>1672815479.585837</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>264455621.0</t>
+          <t>360108082.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>299044660.2</t>
+          <t>286154072.8</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>1304605197.0</t>
+          <t>1150276311.8</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>411510598.5</t>
+          <t>408529389.62</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-1005560536</t>
+          <t>-864122239</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>93349656.65584514</t>
+          <t>66575220.08572514</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-67465901.52195692</t>
+          <t>-80684181.04993486</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>264455621</v>
+        <v>360108082</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.86</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9491,22 +9491,22 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>31.29</t>
+          <t>32.19</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9531,12 +9531,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>25809</t>
+          <t>26546</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9556,22 +9556,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2354.931</t>
+          <t>2607.704</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9628,17 +9628,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-7.41</t>
+          <t>-4.42</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-67.98</t>
+          <t>-77.08</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9713,17 +9713,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>3.89</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9734,12 +9734,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>1536</t>
+          <t>1655</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9749,32 +9749,32 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>16.14</t>
+          <t>5.21</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>104.9</t>
+          <t>103.1</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
@@ -9784,27 +9784,27 @@
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>104.03</t>
+          <t>103.79</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>104.57</t>
+          <t>104.52</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-25.93</t>
+          <t>-53.80</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-92.62</t>
+          <t>-93.49</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9824,46 +9824,46 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>1674868559.974212</t>
+          <t>1672815479.585837</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>240787568.0</t>
+          <t>264455621.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>420099846.8</t>
+          <t>299044660.2</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>1311901908.4</t>
+          <t>1304605197.0</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>422014478.54</t>
+          <t>411510598.5</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-891802061</t>
+          <t>-1005560536</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>122588849.0518091</t>
+          <t>93349656.65584514</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-35924670.60620415</t>
+          <t>-67465901.52195692</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>240787568</v>
+        <v>264455621</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -9927,7 +9927,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9942,7 +9942,7 @@
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>31.29</t>
+          <t>32.19</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>25809</t>
+          <t>26546</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9992,17 +9992,17 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2468.394</t>
+          <t>2354.931</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -10064,17 +10064,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-8.99</t>
+          <t>-4.42</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-52.97</t>
+          <t>-67.98</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-7.62</t>
+          <t>-8.97</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10149,17 +10149,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10170,77 +10170,77 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>1536</t>
+          <t>1655</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>15.62</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>30.28</t>
+          <t>16.14</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-4.45</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>107.8</t>
+          <t>104.9</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>104.1</t>
+          <t>104.18</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>104.21</t>
+          <t>104.03</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>104.62</t>
+          <t>104.57</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>8.52</t>
+          <t>-25.93</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-92.14</t>
+          <t>-92.62</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10260,46 +10260,46 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>1674868559.974212</t>
+          <t>1672815479.585837</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>256751415.0</t>
+          <t>240787568.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>610105241.8</t>
+          <t>420099846.8</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>1297204898.4</t>
+          <t>1311901908.4</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>427732003.84</t>
+          <t>422014478.54</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-687099656</t>
+          <t>-891802061</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>151409488.9896297</t>
+          <t>122588849.0518091</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>12953117.47366416</t>
+          <t>-35924670.60620415</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>256751415</v>
+        <v>240787568</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>31.29</t>
+          <t>32.19</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>25809</t>
+          <t>26546</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10428,22 +10428,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/配電系統.xlsx
+++ b/Result/checksun_type/配電系統.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>價_量;【c】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>701.8</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>734.15</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>644.12</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>734.15</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>644.12</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>2145406818.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>4705713538.6</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>4705713538.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>2697328683.0</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>2381458909.08</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>2381458909.08</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>47833880.16900253</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>2145406818</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>2145406818.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>712.8</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>729.6</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>642.32</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>729.6</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>642.3200000000001</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>2917531202.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>4446393537.2</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>4446393537.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>2537135784.1</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>2394527724.36</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>2394527724.36</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>171300840.0050039</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>2917531202</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>2917531202.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>718.0</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>726.45</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>641.18</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>726.45</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>641.1799999999999</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>3308931687.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>3977678243.4</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>3977678243.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>2336901368.1</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>2356977274.04</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>2356977274.04</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>258836711.484827</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>3308931687</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>3308931687.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>724.4</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>720.75</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>639.48</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>720.75</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>639.48</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>9396894111.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>3406595539.2</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>3406595539.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>2092972596.2</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>2319670873.56</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>2319670873.56</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>332708021.9386873</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>9396894111</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>9396894111.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>731.2</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>715.55</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>638.3</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>715.55</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>638.3</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>5759803875.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>1689450518.2</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>1689450518.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>1272693479.4</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>2149905312.46</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>2149905312.46</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-225925652.1964645</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>5759803875</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>5759803875.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>732.4</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>708.6</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>635.96</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>708.6</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>635.96</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>848806811.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>688943827.4</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>688943827.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>860708905.5</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>2069337538.82</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>2069337538.82</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-626216745.2396646</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>848806811</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>848806811.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>735.4</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>701.1</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>633.54</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>701.1</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>633.54</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>573954733.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>627878031.0</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>627878031</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>1516353585.7</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>2106062606.14</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>2106062606.14</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-649518023.2571056</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>573954733</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>573954733.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>745.6</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>695.2</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>631.48</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>695.2</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>631.48</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>453518166.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>696124492.8</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>696124492.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>2883970531.7</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>2126707687.18</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>2126707687.18</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-630160054.0942674</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>453518166</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>453518166.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>752.0</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>688.05</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>628.72</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>688.05</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>628.72</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>811169006.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>779349653.2</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>779349653.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>4079717323.9</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>2168937186.34</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>2168937186.34</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-567096178.3225608</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>811169006</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>811169006.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>756.8</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>681.7</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>626.7</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>681.7</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>626.7</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>757270421.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>855936440.6</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>855936440.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>4864530439.2</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>2227082877.5</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>2227082877.5</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-495071225.1371737</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>757270421</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>757270421.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>760.8</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>673.0</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>624.74</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>673</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>624.74</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>543477829.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>1032473983.6</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>1032473983.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>5522062366.6</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>2292721646.52</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>2292721646.52</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-368722471.2960072</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>543477829</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>543477829.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>96.16</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>102.5</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>101.88</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>101.88</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>159843579.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>323909709.6</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>323909709.6</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>303527778.0</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>427891465.06</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>427891465.06</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-91694911.4967857</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>159843579</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>159843579.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>95.75999999999999</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>102.53</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>102.08</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>102.53</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>102.08</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>145859250.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>348234730.2</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>348234730.2</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>311622176.9</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>429640696.94</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>429640696.94</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-86779351.10592324</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>145859250</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>145859250.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>96.12</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>102.68</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>102.33</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>102.68</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>102.33</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>182336206.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>376915742.6</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>376915742.6</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>322711393.4</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>429470961.98</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>429470961.98</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-75159538.47233671</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>182336206</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>182336206.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>96.56</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>102.82</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>102.56</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>102.82</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>102.56</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>714004012.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>384535008.4</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>384535008.4</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>335344540.6</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>431976435.3</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>431976435.3</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-59783782.19320107</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>714004012</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>714004012.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>97.24000000000001</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>103.04</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>102.79</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>103.04</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>102.79</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>417505501.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>313755822.4</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>313755822.4</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>306400241.3</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>420660383.62</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>420660383.62</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-92647688.78753585</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>417505501</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>417505501.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>97.82</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>103.19</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>102.95</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>103.19</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>102.95</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>281468682.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>283145846.4</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>283145846.4</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>351622846.6</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>414970230.06</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>414970230.06</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-104519583.1441735</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>281468682</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>281468682.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>99.08000000000001</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>103.5</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>103.2</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>103.2</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>289264312.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>275009623.6</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>275009623.6</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>442557432.7</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>412480726.12</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>412480726.12</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-103171216.5056498</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>289264312</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>289264312.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>100.42</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>103.72</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>103.4</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>103.72</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>103.4</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>220432535.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>268507044.2</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>268507044.2</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>577618774.1</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>409190484.56</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>409190484.56</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-98395538.21827114</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>220432535</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>220432535.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>101.72</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>103.96</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>103.6</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>103.96</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>103.6</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>360108082.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>286154072.8</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>286154072.8</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>1150276311.8</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>408529389.62</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>408529389.62</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-80684181.04993486</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>360108082</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>360108082.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>103.1</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>104.18</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>103.79</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>104.18</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>103.79</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>264455621.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>299044660.2</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>299044660.2</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>1304605197.0</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>411510598.5</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>411510598.5</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-67465901.52195692</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>264455621</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>264455621.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>104.9</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>104.18</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>104.03</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>104.18</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>104.03</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>240787568.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>420099846.8</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>420099846.8</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>1311901908.4</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>422014478.54</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>422014478.54</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-35924670.60620415</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>240787568</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>240787568.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>

--- a/Result/checksun_type/配電系統.xlsx
+++ b/Result/checksun_type/配電系統.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3102.28</t>
+          <t>5678.126</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>695.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>74.46</t>
+          <t>44.32</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11.06</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>238</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>3102</t>
+          <t>5678</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>20.29</t>
+          <t>69.57</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>14.56</t>
+          <t>29.95</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-5.19</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>13.98</t>
+          <t>14.16</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>701.8</t>
+          <t>699.8</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>734.15</v>
+        <v>738.1</v>
       </c>
       <c r="AN2" t="n">
-        <v>644.12</v>
+        <v>646.54</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>638.67</t>
+          <t>639.58</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-43.51</t>
+          <t>-37.42</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>15.15</t>
+          <t>15.35</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>26.82</t>
+          <t>24.53</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-66.78</t>
+          <t>-69.62</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>4933726257.051502</t>
+          <t>4935523146.353572</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>2145406818.0</t>
+          <t>4127699179.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>4705713538.6</v>
+        <v>4379292599.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>2697328683.0</t>
+          <t>3034371558.8</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>2381458909.08</v>
+        <v>2446536212.66</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>2008384855</t>
+          <t>1344921040</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>2064955.740049592</t>
+          <t>18498514.60382305</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>47833880.16900253</t>
+          <t>108883088.3545771</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>2145406818.0</t>
+          <t>4127699179.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-9.97</t>
+          <t>-5.57</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>26.28</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>50.99</t>
+          <t>53.49</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>219537</t>
+          <t>230277</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>689.0</t>
+          <t>704.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
+          <t>743.0</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
           <t>704.0</t>
         </is>
       </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>677.0</t>
-        </is>
-      </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>695.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4210.877</t>
+          <t>3102.28</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>681.0</t>
+          <t>695.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>4.66</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>75.25</t>
+          <t>74.46</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-7.72</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15.02</t>
+          <t>11.06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-5.28</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>238</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>3102</t>
+          <t>5678</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.29</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>14.56</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-4.46</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-2.30</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>13.59</t>
+          <t>13.98</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>712.8</t>
+          <t>701.8</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>729.6</v>
+        <v>734.15</v>
       </c>
       <c r="AN3" t="n">
-        <v>642.3200000000001</v>
+        <v>644.12</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>638.33</t>
+          <t>638.67</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-38.99</t>
+          <t>-43.51</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>15.15</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>29.74</t>
+          <t>26.82</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-63.17</t>
+          <t>-66.78</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>4933726257.051502</t>
+          <t>4935523146.353572</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>2917531202.0</t>
+          <t>2145406818.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>4446393537.2</v>
+        <v>4705713538.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>2537135784.1</t>
+          <t>2697328683.0</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>2394527724.36</v>
+        <v>2381458909.08</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>1909257753</t>
+          <t>2008384855</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-6256666.883396398</t>
+          <t>2064955.740049592</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>171300840.0050039</t>
+          <t>47833880.16900253</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>2917531202.0</t>
+          <t>2145406818.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-11.79</t>
+          <t>-9.97</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1636,17 +1636,17 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>50.99</t>
+          <t>53.49</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>219537</t>
+          <t>230277</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,12 +1696,12 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>720.0</t>
+          <t>689.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>721.0</t>
+          <t>704.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>681.0</t>
+          <t>695.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4656.178</t>
+          <t>4210.877</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>681.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>6.58</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>70.21</t>
+          <t>75.25</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>-7.72</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16.60</t>
+          <t>15.02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-5.28</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>238</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>3102</t>
+          <t>5678</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-4.46</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-2.30</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>13.59</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>718.0</t>
+          <t>712.8</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>726.45</v>
+        <v>729.6</v>
       </c>
       <c r="AN4" t="n">
-        <v>641.1799999999999</v>
+        <v>642.3200000000001</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>638.1</t>
+          <t>638.33</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-29.15</t>
+          <t>-38.99</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>23.12</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>32.64</t>
+          <t>29.74</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-59.58</t>
+          <t>-63.17</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>4933726257.051502</t>
+          <t>4935523146.353572</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>3308931687.0</t>
+          <t>2917531202.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>3977678243.4</v>
+        <v>4446393537.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>2336901368.1</t>
+          <t>2537135784.1</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>2356977274.04</v>
+        <v>2394527724.36</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>1640776875</t>
+          <t>1909257753</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-38539849.95401464</t>
+          <t>-6256666.883396398</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>258836711.484827</t>
+          <t>171300840.0050039</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>3308931687.0</t>
+          <t>2917531202.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-8.55</t>
+          <t>-11.79</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2066,17 +2066,17 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>50.99</t>
+          <t>53.49</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>219537</t>
+          <t>230277</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>701.0</t>
+          <t>720.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>721.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>698.0</t>
+          <t>677.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>681.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-7.07</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>12908.308</t>
+          <t>4656.178</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>688.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>62.76</t>
+          <t>70.21</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-6.78</t>
+          <t>-4.34</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>46.03</t>
+          <t>16.60</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-13.23</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>238</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>3102</t>
+          <t>5678</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>39.68</t>
+          <t>24.72</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-5.02</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>12.71</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>724.4</t>
+          <t>718.0</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>720.75</v>
+        <v>726.45</v>
       </c>
       <c r="AN5" t="n">
-        <v>639.48</v>
+        <v>641.1799999999999</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>637.48</t>
+          <t>638.1</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-24.05</t>
+          <t>-29.15</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>26.60</t>
+          <t>23.12</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>35.02</t>
+          <t>32.64</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-56.63</t>
+          <t>-59.58</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>4933726257.051502</t>
+          <t>4935523146.353572</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>9396894111.0</t>
+          <t>3308931687.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>3406595539.2</v>
+        <v>3977678243.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>2092972596.2</t>
+          <t>2336901368.1</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>2319670873.56</v>
+        <v>2356977274.04</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>1313622943</t>
+          <t>1640776875</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-92608315.67016768</t>
+          <t>-38539849.95401464</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>332708021.9386873</t>
+          <t>258836711.484827</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>9396894111.0</t>
+          <t>3308931687.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-10.88</t>
+          <t>-8.55</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,12 +2501,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>24.80</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>50.99</t>
+          <t>53.49</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>219537</t>
+          <t>230277</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>721.0</t>
+          <t>701.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>780.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>687.0</t>
+          <t>698.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>688.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-7.07</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7500.722</t>
+          <t>12908.308</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>739.0</t>
+          <t>688.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-6.33</t>
+          <t>5.62</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>32.75</t>
+          <t>62.76</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-6.78</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>26.75</t>
+          <t>46.03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-7.70</t>
+          <t>-13.23</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,17 +2734,17 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>238</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>3102</t>
+          <t>5678</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>50.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -2754,53 +2754,53 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>-5.02</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>12.71</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>731.2</t>
+          <t>724.4</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>715.55</v>
+        <v>720.75</v>
       </c>
       <c r="AN6" t="n">
-        <v>638.3</v>
+        <v>639.48</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>636.88</t>
+          <t>637.48</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-12.52</t>
+          <t>-24.05</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>32.48</t>
+          <t>26.60</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>37.13</t>
+          <t>35.02</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-54.03</t>
+          <t>-56.63</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>4933726257.051502</t>
+          <t>4935523146.353572</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>5759803875.0</t>
+          <t>9396894111.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>1689450518.2</v>
+        <v>3406595539.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>1272693479.4</t>
+          <t>2092972596.2</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>2149905312.46</v>
+        <v>2319670873.56</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>416757038</t>
+          <t>1313622943</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-169938558.8717777</t>
+          <t>-92608315.67016768</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-225925652.1964645</t>
+          <t>332708021.9386873</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>5759803875.0</t>
+          <t>9396894111.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-10.88</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>26.64</t>
+          <t>24.80</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>50.99</t>
+          <t>53.49</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>219537</t>
+          <t>230277</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>789.0</t>
+          <t>721.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>803.0</t>
+          <t>780.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>732.0</t>
+          <t>687.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>739.0</t>
+          <t>688.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1152.161</t>
+          <t>7500.722</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>739.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-7.91</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-19.96</t>
+          <t>32.75</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>26.75</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>-7.70</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>238</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>3102</t>
+          <t>5678</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>68.25</t>
+          <t>50.79</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>31.22</t>
+          <t>39.68</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>732.4</t>
+          <t>731.2</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>708.6</v>
+        <v>715.55</v>
       </c>
       <c r="AN7" t="n">
-        <v>635.96</v>
+        <v>638.3</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>635.39</t>
+          <t>636.88</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-10.37</t>
+          <t>-12.52</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>34.32</t>
+          <t>32.48</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>38.29</t>
+          <t>37.13</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-52.59</t>
+          <t>-54.03</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>4933726257.051502</t>
+          <t>4935523146.353572</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>848806811.0</t>
+          <t>5759803875.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>688943827.4</v>
+        <v>1689450518.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>860708905.5</t>
+          <t>1272693479.4</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>2069337538.82</v>
+        <v>2149905312.46</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-171765078</t>
+          <t>416757038</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-159759087.3581983</t>
+          <t>-169938558.8717777</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-626216745.2396646</t>
+          <t>-225925652.1964645</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>848806811.0</t>
+          <t>5759803875.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>27.04</t>
+          <t>26.64</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>50.99</t>
+          <t>53.49</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>219537</t>
+          <t>230277</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>789.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>803.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>732.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>739.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>799.533</t>
+          <t>1152.161</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-58.59</t>
+          <t>-19.96</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-4.20</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-4.53</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>238</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>3102</t>
+          <t>5678</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>68.25</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>8.47</t>
+          <t>31.22</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>10.66</t>
+          <t>11.42</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>735.4</t>
+          <t>732.4</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>701.1</v>
+        <v>708.6</v>
       </c>
       <c r="AN8" t="n">
-        <v>633.54</v>
+        <v>635.96</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>634.25</t>
+          <t>635.39</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-10.78</t>
+          <t>-10.37</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>34.32</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>39.28</t>
+          <t>38.29</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-51.36</t>
+          <t>-52.59</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>4933726257.051502</t>
+          <t>4935523146.353572</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>573954733.0</t>
+          <t>848806811.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>627878031</v>
+        <v>688943827.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>1516353585.7</t>
+          <t>860708905.5</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>2106062606.14</v>
+        <v>2069337538.82</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-888475554</t>
+          <t>-171765078</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-74948604.10702263</t>
+          <t>-159759087.3581983</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-649518023.2571056</t>
+          <t>-626216745.2396646</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>573954733.0</t>
+          <t>848806811.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-8.42</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>25.49</t>
+          <t>27.04</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>50.99</t>
+          <t>53.49</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>219537</t>
+          <t>230277</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>740.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>740.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>617.266</t>
+          <t>799.533</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,72 +3908,72 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>707.0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>3.02</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>-1.87</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>-58.59</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2025-11-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2025-09-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>785.0</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
           <t>738.0</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>-6.19</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>-4.01</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>-75.86</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>2025-11-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2025-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2025-09-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>785.0</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>738.0</t>
-        </is>
-      </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>785.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>-5.99</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>-4.53</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,17 +4024,17 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>238</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>3102</t>
+          <t>5678</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -4044,53 +4044,53 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>10.09</t>
+          <t>10.66</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>745.6</t>
+          <t>735.4</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>695.2</v>
+        <v>701.1</v>
       </c>
       <c r="AN9" t="n">
-        <v>631.48</v>
+        <v>633.54</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>633.66</t>
+          <t>634.25</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-10.78</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>35.05</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>40.34</t>
+          <t>39.28</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-50.05</t>
+          <t>-51.36</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,48 +4110,48 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>4933726257.051502</t>
+          <t>4935523146.353572</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>453518166.0</t>
+          <t>573954733.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>696124492.8</v>
+        <v>627878031</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2883970531.7</t>
+          <t>1516353585.7</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>2126707687.18</v>
+        <v>2106062606.14</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-2147483648</t>
+          <t>-888475554</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>29518563.01117429</t>
+          <t>-74948604.10702263</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-630160054.0942674</t>
+          <t>-649518023.2571056</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>453518166.0</t>
+          <t>573954733.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-4.40</t>
+          <t>-8.42</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>26.60</t>
+          <t>25.49</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>50.99</t>
+          <t>53.49</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>219537</t>
+          <t>230277</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>737.0</t>
+          <t>740.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>739.0</t>
+          <t>740.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>730.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>738.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4313,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1116.653</t>
+          <t>617.266</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-3.88</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-80.90</t>
+          <t>-75.86</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>-8.03</t>
+          <t>-5.99</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>238</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>3102</t>
+          <t>5678</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>23.47</t>
+          <t>8.47</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-3.99</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>9.29</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>10.09</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>752.0</t>
+          <t>745.6</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>688.05</v>
+        <v>695.2</v>
       </c>
       <c r="AN10" t="n">
-        <v>628.72</v>
+        <v>631.48</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>632.04</t>
+          <t>633.66</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>42.23</t>
+          <t>39.85</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>40.46</t>
+          <t>40.34</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-49.89</t>
+          <t>-50.05</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,24 +4540,24 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>4933726257.051502</t>
+          <t>4935523146.353572</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>811169006.0</t>
+          <t>453518166.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>779349653.2</v>
+        <v>696124492.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>4079717323.9</t>
+          <t>2883970531.7</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>2168937186.34</v>
+        <v>2126707687.18</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4566,17 +4566,17 @@
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>149460129.7576182</t>
+          <t>29518563.01117429</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-567096178.3225608</t>
+          <t>-630160054.0942674</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>811169006.0</t>
+          <t>453518166.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-6.48</t>
+          <t>-4.40</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,22 +4641,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>26.03</t>
+          <t>26.60</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>50.99</t>
+          <t>53.49</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>219537</t>
+          <t>230277</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>725.0</t>
+          <t>737.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>736.0</t>
+          <t>739.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>730.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1008.586</t>
+          <t>1116.653</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>745.0</t>
+          <t>722.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-7.19</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-82.40</t>
+          <t>-80.90</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4848,12 +4848,12 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>-5.10</t>
+          <t>-8.03</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,12 +4884,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>238</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>3102</t>
+          <t>5678</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4899,58 +4899,58 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>49.94</t>
+          <t>23.47</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-3.99</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>11.02</t>
+          <t>9.29</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>8.78</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>756.8</t>
+          <t>752.0</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>681.7</v>
+        <v>688.05</v>
       </c>
       <c r="AN11" t="n">
-        <v>626.7</v>
+        <v>628.72</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>630.91</t>
+          <t>632.04</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>15.69</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>46.30</t>
+          <t>42.23</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>40.02</t>
+          <t>40.46</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-50.44</t>
+          <t>-49.89</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,24 +4970,24 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>4933726257.051502</t>
+          <t>4935523146.353572</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>757270421.0</t>
+          <t>811169006.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>855936440.6</v>
+        <v>779349653.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>4864530439.2</t>
+          <t>4079717323.9</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>2227082877.5</v>
+        <v>2168937186.34</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -4996,17 +4996,17 @@
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>279743094.8631054</t>
+          <t>149460129.7576182</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-495071225.1371737</t>
+          <t>-567096178.3225608</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>757270421.0</t>
+          <t>811169006.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-3.50</t>
+          <t>-6.48</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>26.86</t>
+          <t>26.03</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>50.99</t>
+          <t>53.49</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>219537</t>
+          <t>230277</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>769.0</t>
+          <t>725.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>769.0</t>
+          <t>736.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>737.0</t>
+          <t>722.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>745.0</t>
+          <t>722.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>711.087</t>
+          <t>1008.586</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>765.0</t>
+          <t>745.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-10.07</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-81.30</t>
+          <t>-82.40</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5278,12 +5278,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-5.10</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>238</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>3102</t>
+          <t>5678</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>70.42</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>80.35</t>
+          <t>49.94</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>13.05</t>
+          <t>11.02</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>8.78</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>760.8</t>
+          <t>756.8</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>673</v>
+        <v>681.7</v>
       </c>
       <c r="AN12" t="n">
-        <v>624.74</v>
+        <v>626.7</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>629.5</t>
+          <t>630.91</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>26.07</t>
+          <t>15.69</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>48.47</t>
+          <t>46.30</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>38.45</t>
+          <t>40.02</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-52.39</t>
+          <t>-50.44</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,24 +5400,24 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>4933726257.051502</t>
+          <t>4935523146.353572</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>543477829.0</t>
+          <t>757270421.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>1032473983.6</v>
+        <v>855936440.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>5522062366.6</t>
+          <t>4864530439.2</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>2292721646.52</v>
+        <v>2227082877.5</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5426,17 +5426,17 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>420618425.772247</t>
+          <t>279743094.8631054</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-368722471.2960072</t>
+          <t>-495071225.1371737</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>543477829.0</t>
+          <t>757270421.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-3.50</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>27.58</t>
+          <t>26.86</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>50.99</t>
+          <t>53.49</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>219537</t>
+          <t>230277</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>765.0</t>
+          <t>769.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>770.0</t>
+          <t>769.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>759.0</t>
+          <t>737.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>765.0</t>
+          <t>745.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1654.541</t>
+          <t>2251.93</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>97.2</t>
+          <t>97.1</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-12.83</t>
+          <t>-12.91</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,73 +5744,73 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>1655</t>
+          <t>2252</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>65.85</t>
+          <t>63.41</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>22.48</t>
+          <t>43.09</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-6.18</t>
+          <t>-6.32</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>96.16</t>
+          <t>95.86</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>102.5</v>
+        <v>102.32</v>
       </c>
       <c r="AN13" t="n">
-        <v>101.88</v>
+        <v>101.67</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>103.75</t>
+          <t>103.67</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-52.73</t>
+          <t>-34.44</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-109.67</t>
+          <t>-110.58</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>1672815479.585837</t>
+          <t>1670896773.625714</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>159843579.0</t>
+          <t>219814205.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>323909709.6</v>
+        <v>284371450.4</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>303527778.0</t>
+          <t>299063636.4</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>427891465.06</v>
+        <v>422852603.5</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>20381931</t>
+          <t>-14692186</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-46568060.22616701</t>
+          <t>-52995379.27336744</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-91694911.4967857</t>
+          <t>-88345634.03296983</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>159843579.0</t>
+          <t>219814205.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-4.24</t>
+          <t>-4.33</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -5931,12 +5931,12 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>32.19</t>
+          <t>32.15</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>26546</t>
+          <t>26519</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>97.6</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>97.2</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>96.7</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>97.2</t>
+          <t>97.1</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1536.151</t>
+          <t>1654.541</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>97.2</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>11.75</t>
+          <t>6.72</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-15.25</t>
+          <t>-12.83</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,73 +6174,73 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>1655</t>
+          <t>2252</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>65.85</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>22.48</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-6.60</t>
+          <t>-6.18</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>95.75999999999999</t>
+          <t>96.16</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>102.53</v>
+        <v>102.5</v>
       </c>
       <c r="AN14" t="n">
-        <v>102.08</v>
+        <v>101.88</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>103.82</t>
+          <t>103.75</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-82.43</t>
+          <t>-52.73</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-108.39</t>
+          <t>-109.67</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>1672815479.585837</t>
+          <t>1670896773.625714</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>145859250.0</t>
+          <t>159843579.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>348234730.2</v>
+        <v>323909709.6</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>311622176.9</t>
+          <t>303527778.0</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>429640696.94</v>
+        <v>427891465.06</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>36612553</t>
+          <t>20381931</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-38363178.1769636</t>
+          <t>-46568060.22616701</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-86779351.10592324</t>
+          <t>-91694911.4967857</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>145859250.0</t>
+          <t>159843579.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-6.90</t>
+          <t>-4.24</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
@@ -6361,22 +6361,22 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>32.19</t>
+          <t>32.15</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>26546</t>
+          <t>26519</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>97.2</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>97.2</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1914.684</t>
+          <t>1536.151</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>95.3</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>16.80</t>
+          <t>11.75</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-14.53</t>
+          <t>-15.25</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,73 +6604,73 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>1655</t>
+          <t>2252</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>13.41</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-6.38</t>
+          <t>-6.60</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>96.12</t>
+          <t>95.75999999999999</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>102.68</v>
+        <v>102.53</v>
       </c>
       <c r="AN15" t="n">
-        <v>102.33</v>
+        <v>102.08</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>103.93</t>
+          <t>103.82</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-109.29</t>
+          <t>-82.43</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-106.66</t>
+          <t>-108.39</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>1672815479.585837</t>
+          <t>1670896773.625714</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>182336206.0</t>
+          <t>145859250.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>376915742.6</v>
+        <v>348234730.2</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>322711393.4</t>
+          <t>311622176.9</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>429470961.98</v>
+        <v>429640696.94</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>54204349</t>
+          <t>36612553</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-29560237.64442549</t>
+          <t>-38363178.1769636</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-75159538.47233671</t>
+          <t>-86779351.10592324</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>182336206.0</t>
+          <t>145859250.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-6.11</t>
+          <t>-6.90</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
@@ -6791,22 +6791,22 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>32.19</t>
+          <t>32.15</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>26546</t>
+          <t>26519</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>95.8</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>96.3</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>95.3</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-3.53</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>7327.598</t>
+          <t>1914.684</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>95.3</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>14.67</t>
+          <t>16.80</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-14.62</t>
+          <t>-14.53</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12.09</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-4.94</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,73 +7034,73 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>1655</t>
+          <t>2252</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>12.88</t>
+          <t>13.41</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-6.09</t>
+          <t>-6.38</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>96.56</t>
+          <t>96.12</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>102.82</v>
+        <v>102.68</v>
       </c>
       <c r="AN16" t="n">
-        <v>102.56</v>
+        <v>102.33</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>104.04</t>
+          <t>103.93</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-159.05</t>
+          <t>-109.29</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-104.84</t>
+          <t>-106.66</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>1672815479.585837</t>
+          <t>1670896773.625714</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>714004012.0</t>
+          <t>182336206.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>384535008.4</v>
+        <v>376915742.6</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>335344540.6</t>
+          <t>322711393.4</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>431976435.3</v>
+        <v>429470961.98</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>49190467</t>
+          <t>54204349</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-21269455.67571436</t>
+          <t>-29560237.64442549</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-59783782.19320107</t>
+          <t>-75159538.47233671</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>714004012.0</t>
+          <t>182336206.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-6.21</t>
+          <t>-6.11</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7201,7 +7201,7 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
@@ -7221,22 +7221,22 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>32.19</t>
+          <t>32.15</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>26546</t>
+          <t>26519</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>95.8</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>96.6</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>95.1</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>95.3</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>-3.53</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>4255.671</t>
+          <t>7327.598</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>14.67</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-11.57</t>
+          <t>-14.62</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>7.02</t>
+          <t>12.09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>-4.94</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,17 +7464,17 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>1655</t>
+          <t>2252</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>38.64</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
@@ -7484,53 +7484,53 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-5.63</t>
+          <t>-6.09</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>97.24000000000001</t>
+          <t>96.56</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>103.04</v>
+        <v>102.82</v>
       </c>
       <c r="AN17" t="n">
-        <v>102.79</v>
+        <v>102.56</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>104.13</t>
+          <t>104.04</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-260.17</t>
+          <t>-159.05</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-102.92</t>
+          <t>-104.84</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>1672815479.585837</t>
+          <t>1670896773.625714</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>417505501.0</t>
+          <t>714004012.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>313755822.4</v>
+        <v>384535008.4</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>306400241.3</t>
+          <t>335344540.6</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>420660383.62</v>
+        <v>431976435.3</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>7355581</t>
+          <t>49190467</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-14266850.85435314</t>
+          <t>-21269455.67571436</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-92647688.78753585</t>
+          <t>-59783782.19320107</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>417505501.0</t>
+          <t>714004012.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-2.86</t>
+          <t>-6.21</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
@@ -7651,22 +7651,22 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>32.19</t>
+          <t>32.15</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>26546</t>
+          <t>26519</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,7 +7716,7 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>98.4</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
@@ -7726,12 +7726,12 @@
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>95.1</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2950.547</t>
+          <t>4255.671</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-19.47</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-14.62</t>
+          <t>-11.57</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>7.02</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,73 +7894,73 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>1655</t>
+          <t>2252</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>38.64</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.88</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-5.20</t>
+          <t>-5.63</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>97.82</t>
+          <t>97.24000000000001</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>103.19</v>
+        <v>103.04</v>
       </c>
       <c r="AN18" t="n">
-        <v>102.95</v>
+        <v>102.79</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>104.19</t>
+          <t>104.13</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-887.49</t>
+          <t>-260.17</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-101.02</t>
+          <t>-102.92</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1672815479.585837</t>
+          <t>1670896773.625714</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>281468682.0</t>
+          <t>417505501.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>283145846.4</v>
+        <v>313755822.4</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>351622846.6</t>
+          <t>306400241.3</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>414970230.06</v>
+        <v>420660383.62</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-68477000</t>
+          <t>7355581</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-15789.41195628047</t>
+          <t>-14266850.85435314</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-104519583.1441735</t>
+          <t>-92647688.78753585</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>281468682.0</t>
+          <t>417505501.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-6.21</t>
+          <t>-2.86</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
@@ -8081,22 +8081,22 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>32.19</t>
+          <t>32.15</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>26546</t>
+          <t>26519</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>98.4</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>97.9</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>94.1</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>3012.776</t>
+          <t>2950.547</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-37.86</t>
+          <t>-19.47</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-13.63</t>
+          <t>-14.62</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,12 +8324,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>1655</t>
+          <t>2252</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8344,53 +8344,53 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-5.20</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>99.08000000000001</t>
+          <t>97.82</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>103.5</v>
+        <v>103.19</v>
       </c>
       <c r="AN19" t="n">
-        <v>103.2</v>
+        <v>102.95</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>104.3</t>
+          <t>104.19</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-667.15</t>
+          <t>-887.49</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-98.76</t>
+          <t>-101.02</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>1672815479.585837</t>
+          <t>1670896773.625714</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>289264312.0</t>
+          <t>281468682.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>275009623.6</v>
+        <v>283145846.4</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>442557432.7</t>
+          <t>351622846.6</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>412480726.12</v>
+        <v>414970230.06</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-167547809</t>
+          <t>-68477000</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>18984900.35753776</t>
+          <t>-15789.41195628047</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-103171216.5056498</t>
+          <t>-104519583.1441735</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>289264312.0</t>
+          <t>281468682.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-5.12</t>
+          <t>-6.21</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8521,12 +8521,12 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>32.19</t>
+          <t>32.15</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>26546</t>
+          <t>26519</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>97.2</t>
+          <t>97.9</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>94.1</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2248.507</t>
+          <t>3012.776</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>96.3</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-53.51</t>
+          <t>-37.86</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-12.56</t>
+          <t>-13.63</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,12 +8754,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>1655</t>
+          <t>2252</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8774,12 +8774,12 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -8789,38 +8789,38 @@
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>100.42</t>
+          <t>99.08000000000001</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>103.72</v>
+        <v>103.5</v>
       </c>
       <c r="AN20" t="n">
-        <v>103.4</v>
+        <v>103.2</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>104.41</t>
+          <t>104.3</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-215.80</t>
+          <t>-667.15</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-96.68</t>
+          <t>-98.76</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>1672815479.585837</t>
+          <t>1670896773.625714</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>220432535.0</t>
+          <t>289264312.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>268507044.2</v>
+        <v>275009623.6</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>577618774.1</t>
+          <t>442557432.7</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>409190484.56</v>
+        <v>412480726.12</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-309111729</t>
+          <t>-167547809</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>41195103.42357187</t>
+          <t>18984900.35753776</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-98395538.21827114</t>
+          <t>-103171216.5056498</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>220432535.0</t>
+          <t>289264312.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-3.94</t>
+          <t>-5.12</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -8951,12 +8951,12 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>4.40</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>32.19</t>
+          <t>32.15</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>26546</t>
+          <t>26519</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>99.2</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>97.2</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>97.2</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>96.3</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-2.9</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>3626.375</t>
+          <t>2248.507</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-75.12</t>
+          <t>-53.51</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-11.57</t>
+          <t>-12.56</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,33 +9163,33 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>5.98</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>1655</t>
+          <t>2252</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9204,53 +9204,53 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>101.72</t>
+          <t>100.42</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>103.96</v>
+        <v>103.72</v>
       </c>
       <c r="AN21" t="n">
-        <v>103.6</v>
+        <v>103.4</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>104.44</t>
+          <t>104.41</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-109.91</t>
+          <t>-215.80</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-94.89</t>
+          <t>-96.68</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>1672815479.585837</t>
+          <t>1670896773.625714</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>360108082.0</t>
+          <t>220432535.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>286154072.8</v>
+        <v>268507044.2</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>1150276311.8</t>
+          <t>577618774.1</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>408529389.62</v>
+        <v>409190484.56</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-864122239</t>
+          <t>-309111729</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>66575220.08572514</t>
+          <t>41195103.42357187</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-80684181.04993486</t>
+          <t>-98395538.21827114</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>360108082.0</t>
+          <t>220432535.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-2.86</t>
+          <t>-3.94</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9381,12 +9381,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>4.40</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>32.19</t>
+          <t>32.15</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>26546</t>
+          <t>26519</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>99.2</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>99.6</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>97.2</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2607.704</t>
+          <t>3626.375</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-4.42</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-77.08</t>
+          <t>-75.12</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-8.97</t>
+          <t>-11.57</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,33 +9593,33 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>5.98</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>1655</t>
+          <t>2252</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9629,58 +9629,58 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>5.21</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>103.1</t>
+          <t>101.72</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>104.18</v>
+        <v>103.96</v>
       </c>
       <c r="AN22" t="n">
-        <v>103.79</v>
+        <v>103.6</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>104.52</t>
+          <t>104.44</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-53.80</t>
+          <t>-109.91</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-93.49</t>
+          <t>-94.89</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>1672815479.585837</t>
+          <t>1670896773.625714</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>264455621.0</t>
+          <t>360108082.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>299044660.2</v>
+        <v>286154072.8</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>1304605197.0</t>
+          <t>1150276311.8</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>411510598.5</v>
+        <v>408529389.62</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-1005560536</t>
+          <t>-864122239</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>93349656.65584514</t>
+          <t>66575220.08572514</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-67465901.52195692</t>
+          <t>-80684181.04993486</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>264455621.0</t>
+          <t>360108082.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.86</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9781,7 +9781,7 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>32.19</t>
+          <t>32.15</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>26546</t>
+          <t>26519</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2354.931</t>
+          <t>2607.704</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-4.42</t>
+          <t>-4.53</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-67.98</t>
+          <t>-77.08</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>3.89</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,12 +10044,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>1655</t>
+          <t>2252</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10059,58 +10059,58 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>16.14</t>
+          <t>5.21</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>104.9</t>
+          <t>103.1</t>
         </is>
       </c>
       <c r="AM23" t="n">
         <v>104.18</v>
       </c>
       <c r="AN23" t="n">
-        <v>104.03</v>
+        <v>103.79</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>104.57</t>
+          <t>104.52</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-25.93</t>
+          <t>-53.80</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-92.62</t>
+          <t>-93.49</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>1672815479.585837</t>
+          <t>1670896773.625714</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>240787568.0</t>
+          <t>264455621.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>420099846.8</v>
+        <v>299044660.2</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>1311901908.4</t>
+          <t>1304605197.0</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>422014478.54</v>
+        <v>411510598.5</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-891802061</t>
+          <t>-1005560536</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>122588849.0518091</t>
+          <t>93349656.65584514</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-35924670.60620415</t>
+          <t>-67465901.52195692</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>240787568.0</t>
+          <t>264455621.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10211,7 +10211,7 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10246,7 +10246,7 @@
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>32.19</t>
+          <t>32.15</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>26546</t>
+          <t>26519</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,17 +10296,17 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/配電系統.xlsx
+++ b/Result/checksun_type/配電系統.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5678.126</t>
+          <t>4456.494</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>700.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-4.65</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>44.32</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-5.15</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>15.89</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>-5.14</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>267</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>5678</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>69.57</t>
+          <t>27.54</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>29.95</t>
+          <t>39.13</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-5.19</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>14.16</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>699.8</t>
+          <t>702.2</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>738.1</v>
+        <v>737.35</v>
       </c>
       <c r="AN2" t="n">
-        <v>646.54</v>
+        <v>648.52</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>639.58</t>
+          <t>640.28</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-37.42</t>
+          <t>-41.44</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>15.35</t>
+          <t>13.01</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>24.53</t>
+          <t>22.23</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-69.62</t>
+          <t>-72.48</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>4935523146.353572</t>
+          <t>4935251699.197575</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>4127699179.0</t>
+          <t>3163492460.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>4379292599.4</v>
+        <v>3132612269.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>3034371558.8</t>
+          <t>3269603904.2</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>2446536212.66</v>
+        <v>2494838192.4</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>1344921040</t>
+          <t>-136991635</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>18498514.60382305</t>
+          <t>27434120.50332935</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>108883088.3545771</t>
+          <t>76579952.95061398</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>4127699179.0</t>
+          <t>3163492460.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-5.57</t>
+          <t>-9.33</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>26.28</t>
+          <t>25.23</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>53.49</t>
+          <t>51.36</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>230277</t>
+          <t>221116</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>704.0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>743.0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>704.0</t>
+          <t>698.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>700.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3102.28</t>
+          <t>5678.126</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>695.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4.66</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-4.65</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>74.46</t>
+          <t>44.32</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11.06</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>267</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>5678</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>20.29</t>
+          <t>69.57</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>14.56</t>
+          <t>29.95</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-5.19</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>13.98</t>
+          <t>14.16</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>701.8</t>
+          <t>699.8</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>734.15</v>
+        <v>738.1</v>
       </c>
       <c r="AN3" t="n">
-        <v>644.12</v>
+        <v>646.54</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>638.67</t>
+          <t>639.58</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-43.51</t>
+          <t>-37.42</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>15.15</t>
+          <t>15.35</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>26.82</t>
+          <t>24.53</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-66.78</t>
+          <t>-69.62</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>4935523146.353572</t>
+          <t>4935251699.197575</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>2145406818.0</t>
+          <t>4127699179.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>4705713538.6</v>
+        <v>4379292599.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>2697328683.0</t>
+          <t>3034371558.8</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>2381458909.08</v>
+        <v>2446536212.66</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>2008384855</t>
+          <t>1344921040</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>2064955.740049592</t>
+          <t>18498514.60382305</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>47833880.16900253</t>
+          <t>108883088.3545771</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>2145406818.0</t>
+          <t>4127699179.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-9.97</t>
+          <t>-5.57</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>26.28</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>53.49</t>
+          <t>51.36</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>230277</t>
+          <t>221116</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>689.0</t>
+          <t>704.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
+          <t>743.0</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
           <t>704.0</t>
         </is>
       </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>677.0</t>
-        </is>
-      </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>695.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4210.877</t>
+          <t>3102.28</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>681.0</t>
+          <t>695.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6.58</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-4.65</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>75.25</t>
+          <t>74.46</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-7.72</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15.02</t>
+          <t>11.06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-5.28</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>267</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>5678</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.29</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>14.56</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-4.46</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-2.30</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>13.59</t>
+          <t>13.98</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>712.8</t>
+          <t>701.8</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>729.6</v>
+        <v>734.15</v>
       </c>
       <c r="AN4" t="n">
-        <v>642.3200000000001</v>
+        <v>644.12</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>638.33</t>
+          <t>638.67</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-38.99</t>
+          <t>-43.51</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>15.15</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>29.74</t>
+          <t>26.82</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-63.17</t>
+          <t>-66.78</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>4935523146.353572</t>
+          <t>4935251699.197575</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>2917531202.0</t>
+          <t>2145406818.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>4446393537.2</v>
+        <v>4705713538.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>2537135784.1</t>
+          <t>2697328683.0</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>2394527724.36</v>
+        <v>2381458909.08</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>1909257753</t>
+          <t>2008384855</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-6256666.883396398</t>
+          <t>2064955.740049592</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>171300840.0050039</t>
+          <t>47833880.16900253</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>2917531202.0</t>
+          <t>2145406818.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-11.79</t>
+          <t>-9.97</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2066,17 +2066,17 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>53.49</t>
+          <t>51.36</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>230277</t>
+          <t>221116</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,12 +2126,12 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>720.0</t>
+          <t>689.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>721.0</t>
+          <t>704.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>681.0</t>
+          <t>695.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4656.178</t>
+          <t>4210.877</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>681.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-4.65</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>70.21</t>
+          <t>75.25</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>-7.72</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16.60</t>
+          <t>15.02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-5.28</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>267</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>5678</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-4.46</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-2.30</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>13.59</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>718.0</t>
+          <t>712.8</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>726.45</v>
+        <v>729.6</v>
       </c>
       <c r="AN5" t="n">
-        <v>641.1799999999999</v>
+        <v>642.3200000000001</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>638.1</t>
+          <t>638.33</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-29.15</t>
+          <t>-38.99</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>23.12</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>32.64</t>
+          <t>29.74</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-59.58</t>
+          <t>-63.17</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>4935523146.353572</t>
+          <t>4935251699.197575</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>3308931687.0</t>
+          <t>2917531202.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>3977678243.4</v>
+        <v>4446393537.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>2336901368.1</t>
+          <t>2537135784.1</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>2356977274.04</v>
+        <v>2394527724.36</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>1640776875</t>
+          <t>1909257753</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-38539849.95401464</t>
+          <t>-6256666.883396398</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>258836711.484827</t>
+          <t>171300840.0050039</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>3308931687.0</t>
+          <t>2917531202.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-8.55</t>
+          <t>-11.79</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2496,17 +2496,17 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>53.49</t>
+          <t>51.36</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>230277</t>
+          <t>221116</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>701.0</t>
+          <t>720.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>721.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>698.0</t>
+          <t>677.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>681.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-7.07</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>12908.308</t>
+          <t>4656.178</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>688.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-4.65</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>62.76</t>
+          <t>70.21</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-6.78</t>
+          <t>-4.34</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>46.03</t>
+          <t>16.60</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-13.23</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>267</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>5678</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>39.68</t>
+          <t>24.72</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-5.02</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>12.71</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>724.4</t>
+          <t>718.0</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>720.75</v>
+        <v>726.45</v>
       </c>
       <c r="AN6" t="n">
-        <v>639.48</v>
+        <v>641.1799999999999</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>637.48</t>
+          <t>638.1</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-24.05</t>
+          <t>-29.15</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>26.60</t>
+          <t>23.12</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>35.02</t>
+          <t>32.64</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-56.63</t>
+          <t>-59.58</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>4935523146.353572</t>
+          <t>4935251699.197575</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>9396894111.0</t>
+          <t>3308931687.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>3406595539.2</v>
+        <v>3977678243.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>2092972596.2</t>
+          <t>2336901368.1</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>2319670873.56</v>
+        <v>2356977274.04</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>1313622943</t>
+          <t>1640776875</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-92608315.67016768</t>
+          <t>-38539849.95401464</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>332708021.9386873</t>
+          <t>258836711.484827</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>9396894111.0</t>
+          <t>3308931687.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-10.88</t>
+          <t>-8.55</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>24.80</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>53.49</t>
+          <t>51.36</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>230277</t>
+          <t>221116</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>721.0</t>
+          <t>701.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>780.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>687.0</t>
+          <t>698.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>688.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-7.07</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>7500.722</t>
+          <t>12908.308</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>739.0</t>
+          <t>688.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-4.65</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>32.75</t>
+          <t>62.76</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-6.78</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>26.75</t>
+          <t>46.03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-7.70</t>
+          <t>-13.23</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,17 +3164,17 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>267</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>5678</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>50.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
@@ -3184,53 +3184,53 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>-5.02</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>12.71</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>731.2</t>
+          <t>724.4</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>715.55</v>
+        <v>720.75</v>
       </c>
       <c r="AN7" t="n">
-        <v>638.3</v>
+        <v>639.48</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>636.88</t>
+          <t>637.48</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-12.52</t>
+          <t>-24.05</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>32.48</t>
+          <t>26.60</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>37.13</t>
+          <t>35.02</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-54.03</t>
+          <t>-56.63</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>4935523146.353572</t>
+          <t>4935251699.197575</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>5759803875.0</t>
+          <t>9396894111.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>1689450518.2</v>
+        <v>3406595539.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>1272693479.4</t>
+          <t>2092972596.2</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>2149905312.46</v>
+        <v>2319670873.56</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>416757038</t>
+          <t>1313622943</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-169938558.8717777</t>
+          <t>-92608315.67016768</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-225925652.1964645</t>
+          <t>332708021.9386873</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>5759803875.0</t>
+          <t>9396894111.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-10.88</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3361,12 +3361,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>26.64</t>
+          <t>24.80</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>53.49</t>
+          <t>51.36</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>230277</t>
+          <t>221116</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>789.0</t>
+          <t>721.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>803.0</t>
+          <t>780.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>732.0</t>
+          <t>687.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>739.0</t>
+          <t>688.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1152.161</t>
+          <t>7500.722</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>739.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-5.57</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-4.65</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-19.96</t>
+          <t>32.75</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>26.75</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>-7.70</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>267</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>5678</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>68.25</t>
+          <t>50.79</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>31.22</t>
+          <t>39.68</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>732.4</t>
+          <t>731.2</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>708.6</v>
+        <v>715.55</v>
       </c>
       <c r="AN8" t="n">
-        <v>635.96</v>
+        <v>638.3</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>635.39</t>
+          <t>636.88</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-10.37</t>
+          <t>-12.52</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>34.32</t>
+          <t>32.48</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>38.29</t>
+          <t>37.13</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-52.59</t>
+          <t>-54.03</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>4935523146.353572</t>
+          <t>4935251699.197575</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>848806811.0</t>
+          <t>5759803875.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>688943827.4</v>
+        <v>1689450518.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>860708905.5</t>
+          <t>1272693479.4</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>2069337538.82</v>
+        <v>2149905312.46</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-171765078</t>
+          <t>416757038</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-159759087.3581983</t>
+          <t>-169938558.8717777</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-626216745.2396646</t>
+          <t>-225925652.1964645</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>848806811.0</t>
+          <t>5759803875.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>27.04</t>
+          <t>26.64</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>53.49</t>
+          <t>51.36</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>230277</t>
+          <t>221116</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>789.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>803.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>732.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>739.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>799.533</t>
+          <t>1152.161</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>-7.14</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-4.65</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-58.59</t>
+          <t>-19.96</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-4.20</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-4.53</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>267</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>5678</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>68.25</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>8.47</t>
+          <t>31.22</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>10.66</t>
+          <t>11.42</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>735.4</t>
+          <t>732.4</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>701.1</v>
+        <v>708.6</v>
       </c>
       <c r="AN9" t="n">
-        <v>633.54</v>
+        <v>635.96</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>634.25</t>
+          <t>635.39</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-10.78</t>
+          <t>-10.37</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>34.32</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>39.28</t>
+          <t>38.29</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-51.36</t>
+          <t>-52.59</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>4935523146.353572</t>
+          <t>4935251699.197575</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>573954733.0</t>
+          <t>848806811.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>627878031</v>
+        <v>688943827.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>1516353585.7</t>
+          <t>860708905.5</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>2106062606.14</v>
+        <v>2069337538.82</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-888475554</t>
+          <t>-171765078</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-74948604.10702263</t>
+          <t>-159759087.3581983</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-649518023.2571056</t>
+          <t>-626216745.2396646</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>573954733.0</t>
+          <t>848806811.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-8.42</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>25.49</t>
+          <t>27.04</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>53.49</t>
+          <t>51.36</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>230277</t>
+          <t>221116</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>740.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>740.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>617.266</t>
+          <t>799.533</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,72 +4338,72 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>707.0</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>-4.65</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>-58.59</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2025-11-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2025-09-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>785.0</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
           <t>738.0</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>-1.23</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>-1.87</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>-75.86</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2025-11-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2025-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2025-09-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>785.0</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>738.0</t>
-        </is>
-      </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>785.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>-5.99</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>-4.53</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,17 +4454,17 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>267</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>5678</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -4474,53 +4474,53 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>10.09</t>
+          <t>10.66</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>745.6</t>
+          <t>735.4</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>695.2</v>
+        <v>701.1</v>
       </c>
       <c r="AN10" t="n">
-        <v>631.48</v>
+        <v>633.54</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>633.66</t>
+          <t>634.25</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-10.78</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>35.05</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>40.34</t>
+          <t>39.28</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-50.05</t>
+          <t>-51.36</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,48 +4540,48 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>4935523146.353572</t>
+          <t>4935251699.197575</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>453518166.0</t>
+          <t>573954733.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>696124492.8</v>
+        <v>627878031</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>2883970531.7</t>
+          <t>1516353585.7</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>2126707687.18</v>
+        <v>2106062606.14</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-2147483648</t>
+          <t>-888475554</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>29518563.01117429</t>
+          <t>-74948604.10702263</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-630160054.0942674</t>
+          <t>-649518023.2571056</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>453518166.0</t>
+          <t>573954733.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-4.40</t>
+          <t>-8.42</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,22 +4641,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>26.60</t>
+          <t>25.49</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>53.49</t>
+          <t>51.36</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>230277</t>
+          <t>221116</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>737.0</t>
+          <t>740.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>739.0</t>
+          <t>740.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>730.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>738.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4743,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1116.653</t>
+          <t>617.266</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,102 +4778,102 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
+          <t>-5.43</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>-4.65</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>-75.86</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2025-11-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-09-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>785.0</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>738.0</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>785.0</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>624.0</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>605.0</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>-5.99</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>29.75</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
           <t>0.96</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>-1.87</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>-80.90</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2025-11-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-09-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>785.0</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>738.0</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>785.0</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>624.0</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>605.0</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>-8.03</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>-2.17</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>29.75</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>3.98</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>-1.94</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>267</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>5678</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>23.47</t>
+          <t>8.47</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-3.99</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>9.29</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>10.09</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>752.0</t>
+          <t>745.6</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>688.05</v>
+        <v>695.2</v>
       </c>
       <c r="AN11" t="n">
-        <v>628.72</v>
+        <v>631.48</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>632.04</t>
+          <t>633.66</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>42.23</t>
+          <t>39.85</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>40.46</t>
+          <t>40.34</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-49.89</t>
+          <t>-50.05</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,24 +4970,24 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>4935523146.353572</t>
+          <t>4935251699.197575</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>811169006.0</t>
+          <t>453518166.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>779349653.2</v>
+        <v>696124492.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>4079717323.9</t>
+          <t>2883970531.7</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>2168937186.34</v>
+        <v>2126707687.18</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -4996,17 +4996,17 @@
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>149460129.7576182</t>
+          <t>29518563.01117429</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-567096178.3225608</t>
+          <t>-630160054.0942674</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>811169006.0</t>
+          <t>453518166.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-6.48</t>
+          <t>-4.40</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>26.03</t>
+          <t>26.60</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>53.49</t>
+          <t>51.36</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>230277</t>
+          <t>221116</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>725.0</t>
+          <t>737.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>736.0</t>
+          <t>739.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>730.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1008.586</t>
+          <t>1116.653</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>745.0</t>
+          <t>722.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-4.65</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-82.40</t>
+          <t>-80.90</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5278,12 +5278,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>-5.10</t>
+          <t>-8.03</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,12 +5314,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>267</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>5678</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5329,58 +5329,58 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>49.94</t>
+          <t>23.47</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-3.99</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>11.02</t>
+          <t>9.29</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>8.78</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>756.8</t>
+          <t>752.0</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>681.7</v>
+        <v>688.05</v>
       </c>
       <c r="AN12" t="n">
-        <v>626.7</v>
+        <v>628.72</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>630.91</t>
+          <t>632.04</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>15.69</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>46.30</t>
+          <t>42.23</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>40.02</t>
+          <t>40.46</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-50.44</t>
+          <t>-49.89</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,24 +5400,24 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>4935523146.353572</t>
+          <t>4935251699.197575</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>757270421.0</t>
+          <t>811169006.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>855936440.6</v>
+        <v>779349653.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>4864530439.2</t>
+          <t>4079717323.9</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>2227082877.5</v>
+        <v>2168937186.34</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5426,17 +5426,17 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>279743094.8631054</t>
+          <t>149460129.7576182</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-495071225.1371737</t>
+          <t>-567096178.3225608</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>757270421.0</t>
+          <t>811169006.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-3.50</t>
+          <t>-6.48</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>26.86</t>
+          <t>26.03</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>53.49</t>
+          <t>51.36</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>230277</t>
+          <t>221116</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>769.0</t>
+          <t>725.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>769.0</t>
+          <t>736.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>737.0</t>
+          <t>722.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>745.0</t>
+          <t>722.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2251.93</t>
+          <t>1934.14</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>97.1</t>
+          <t>96.9</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>-36.48</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-12.91</t>
+          <t>-13.09</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5749,68 +5749,68 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>2252</t>
+          <t>1934</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>63.41</t>
+          <t>58.54</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>43.09</t>
+          <t>62.6</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-6.32</t>
+          <t>-5.36</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>95.86</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>102.32</v>
+        <v>101.64</v>
       </c>
       <c r="AN13" t="n">
-        <v>101.67</v>
+        <v>101.52</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>103.67</t>
+          <t>103.55</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-34.44</t>
+          <t>-22.57</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-110.58</t>
+          <t>-111.21</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>1670896773.625714</t>
+          <t>1668913450.726819</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>219814205.0</t>
+          <t>187058281.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>284371450.4</v>
+        <v>178982304.2</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>299063636.4</t>
+          <t>281758656.3</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>422852603.5</v>
+        <v>421804108.64</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-14692186</t>
+          <t>-102776352</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-52995379.27336744</t>
+          <t>-58111350.65553775</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-88345634.03296983</t>
+          <t>-86249193.25747448</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>219814205.0</t>
+          <t>187058281.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-4.33</t>
+          <t>-4.53</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5941,7 +5941,7 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>32.15</t>
+          <t>32.09</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>26519</t>
+          <t>26464</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
+          <t>97.5</t>
+        </is>
+      </c>
+      <c r="CE13" t="inlineStr">
+        <is>
           <t>97.6</t>
         </is>
       </c>
-      <c r="CE13" t="inlineStr">
-        <is>
-          <t>98.6</t>
-        </is>
-      </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>96.7</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>97.1</t>
+          <t>96.9</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1654.541</t>
+          <t>2251.93</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>97.2</t>
+          <t>97.1</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-12.83</t>
+          <t>-12.91</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6179,68 +6179,68 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>2252</t>
+          <t>1934</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>65.85</t>
+          <t>63.41</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>22.48</t>
+          <t>43.09</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-6.18</t>
+          <t>-6.32</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>96.16</t>
+          <t>95.86</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>102.5</v>
+        <v>102.32</v>
       </c>
       <c r="AN14" t="n">
-        <v>101.88</v>
+        <v>101.67</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>103.75</t>
+          <t>103.67</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-52.73</t>
+          <t>-34.44</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-109.67</t>
+          <t>-110.58</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>1670896773.625714</t>
+          <t>1668913450.726819</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>159843579.0</t>
+          <t>219814205.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>323909709.6</v>
+        <v>284371450.4</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>303527778.0</t>
+          <t>299063636.4</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>427891465.06</v>
+        <v>422852603.5</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>20381931</t>
+          <t>-14692186</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-46568060.22616701</t>
+          <t>-52995379.27336744</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-91694911.4967857</t>
+          <t>-88345634.03296983</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>159843579.0</t>
+          <t>219814205.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-4.24</t>
+          <t>-4.33</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>32.15</t>
+          <t>32.09</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>26519</t>
+          <t>26464</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>97.6</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>97.2</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>96.7</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>97.2</t>
+          <t>97.1</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1536.151</t>
+          <t>1654.541</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>97.2</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>11.75</t>
+          <t>6.72</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-15.25</t>
+          <t>-12.83</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6609,68 +6609,68 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>2252</t>
+          <t>1934</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>65.85</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>22.48</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-6.60</t>
+          <t>-6.18</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>95.75999999999999</t>
+          <t>96.16</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>102.53</v>
+        <v>102.5</v>
       </c>
       <c r="AN15" t="n">
-        <v>102.08</v>
+        <v>101.88</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>103.82</t>
+          <t>103.75</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-82.43</t>
+          <t>-52.73</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-108.39</t>
+          <t>-109.67</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>1670896773.625714</t>
+          <t>1668913450.726819</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>145859250.0</t>
+          <t>159843579.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>348234730.2</v>
+        <v>323909709.6</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>311622176.9</t>
+          <t>303527778.0</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>429640696.94</v>
+        <v>427891465.06</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>36612553</t>
+          <t>20381931</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-38363178.1769636</t>
+          <t>-46568060.22616701</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-86779351.10592324</t>
+          <t>-91694911.4967857</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>145859250.0</t>
+          <t>159843579.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-6.90</t>
+          <t>-4.24</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
@@ -6791,17 +6791,17 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>32.15</t>
+          <t>32.09</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>26519</t>
+          <t>26464</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>97.2</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>97.2</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1914.684</t>
+          <t>1536.151</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>95.3</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>16.80</t>
+          <t>11.75</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-14.53</t>
+          <t>-15.25</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7039,68 +7039,68 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>2252</t>
+          <t>1934</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>13.41</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-6.38</t>
+          <t>-6.60</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>96.12</t>
+          <t>95.75999999999999</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>102.68</v>
+        <v>102.53</v>
       </c>
       <c r="AN16" t="n">
-        <v>102.33</v>
+        <v>102.08</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>103.93</t>
+          <t>103.82</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-109.29</t>
+          <t>-82.43</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-106.66</t>
+          <t>-108.39</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>1670896773.625714</t>
+          <t>1668913450.726819</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>182336206.0</t>
+          <t>145859250.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>376915742.6</v>
+        <v>348234730.2</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>322711393.4</t>
+          <t>311622176.9</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>429470961.98</v>
+        <v>429640696.94</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>54204349</t>
+          <t>36612553</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-29560237.64442549</t>
+          <t>-38363178.1769636</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-75159538.47233671</t>
+          <t>-86779351.10592324</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>182336206.0</t>
+          <t>145859250.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-6.11</t>
+          <t>-6.90</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7201,7 +7201,7 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
@@ -7221,17 +7221,17 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>32.15</t>
+          <t>32.09</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>26519</t>
+          <t>26464</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>95.8</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>96.3</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>95.3</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-3.53</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>7327.598</t>
+          <t>1914.684</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>95.3</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>14.67</t>
+          <t>16.80</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-14.62</t>
+          <t>-14.53</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12.09</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-4.94</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7469,68 +7469,68 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>2252</t>
+          <t>1934</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>12.88</t>
+          <t>13.41</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-6.09</t>
+          <t>-6.38</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>96.56</t>
+          <t>96.12</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>102.82</v>
+        <v>102.68</v>
       </c>
       <c r="AN17" t="n">
-        <v>102.56</v>
+        <v>102.33</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>104.04</t>
+          <t>103.93</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-159.05</t>
+          <t>-109.29</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-104.84</t>
+          <t>-106.66</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>1670896773.625714</t>
+          <t>1668913450.726819</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>714004012.0</t>
+          <t>182336206.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>384535008.4</v>
+        <v>376915742.6</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>335344540.6</t>
+          <t>322711393.4</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>431976435.3</v>
+        <v>429470961.98</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>49190467</t>
+          <t>54204349</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-21269455.67571436</t>
+          <t>-29560237.64442549</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-59783782.19320107</t>
+          <t>-75159538.47233671</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>714004012.0</t>
+          <t>182336206.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-6.21</t>
+          <t>-6.11</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
@@ -7651,17 +7651,17 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>32.15</t>
+          <t>32.09</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>26519</t>
+          <t>26464</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>95.8</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>96.6</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>95.1</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>95.3</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>-3.53</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>4255.671</t>
+          <t>7327.598</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>14.67</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-11.57</t>
+          <t>-14.62</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>7.02</t>
+          <t>12.09</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>-4.94</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7899,12 +7899,12 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>2252</t>
+          <t>1934</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>38.64</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
@@ -7914,53 +7914,53 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-5.63</t>
+          <t>-6.09</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>97.24000000000001</t>
+          <t>96.56</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>103.04</v>
+        <v>102.82</v>
       </c>
       <c r="AN18" t="n">
-        <v>102.79</v>
+        <v>102.56</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>104.13</t>
+          <t>104.04</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-260.17</t>
+          <t>-159.05</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-102.92</t>
+          <t>-104.84</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1670896773.625714</t>
+          <t>1668913450.726819</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>417505501.0</t>
+          <t>714004012.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>313755822.4</v>
+        <v>384535008.4</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>306400241.3</t>
+          <t>335344540.6</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>420660383.62</v>
+        <v>431976435.3</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>7355581</t>
+          <t>49190467</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-14266850.85435314</t>
+          <t>-21269455.67571436</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-92647688.78753585</t>
+          <t>-59783782.19320107</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>417505501.0</t>
+          <t>714004012.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-2.86</t>
+          <t>-6.21</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
@@ -8081,17 +8081,17 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>32.15</t>
+          <t>32.09</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>26519</t>
+          <t>26464</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,7 +8146,7 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>98.4</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
@@ -8156,12 +8156,12 @@
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>95.1</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2950.547</t>
+          <t>4255.671</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-19.47</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-14.62</t>
+          <t>-11.57</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>7.02</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8329,68 +8329,68 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>2252</t>
+          <t>1934</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>38.64</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.88</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-5.20</t>
+          <t>-5.63</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>97.82</t>
+          <t>97.24000000000001</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>103.19</v>
+        <v>103.04</v>
       </c>
       <c r="AN19" t="n">
-        <v>102.95</v>
+        <v>102.79</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>104.19</t>
+          <t>104.13</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-887.49</t>
+          <t>-260.17</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-101.02</t>
+          <t>-102.92</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>1670896773.625714</t>
+          <t>1668913450.726819</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>281468682.0</t>
+          <t>417505501.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>283145846.4</v>
+        <v>313755822.4</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>351622846.6</t>
+          <t>306400241.3</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>414970230.06</v>
+        <v>420660383.62</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-68477000</t>
+          <t>7355581</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-15789.41195628047</t>
+          <t>-14266850.85435314</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-104519583.1441735</t>
+          <t>-92647688.78753585</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>281468682.0</t>
+          <t>417505501.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-6.21</t>
+          <t>-2.86</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
@@ -8511,17 +8511,17 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>32.15</t>
+          <t>32.09</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>26519</t>
+          <t>26464</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>98.4</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>97.9</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>94.1</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3012.776</t>
+          <t>2950.547</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-37.86</t>
+          <t>-19.47</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-13.63</t>
+          <t>-14.62</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8759,7 +8759,7 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>2252</t>
+          <t>1934</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8774,53 +8774,53 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-5.20</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>99.08000000000001</t>
+          <t>97.82</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>103.5</v>
+        <v>103.19</v>
       </c>
       <c r="AN20" t="n">
-        <v>103.2</v>
+        <v>102.95</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>104.3</t>
+          <t>104.19</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-667.15</t>
+          <t>-887.49</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-98.76</t>
+          <t>-101.02</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>1670896773.625714</t>
+          <t>1668913450.726819</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>289264312.0</t>
+          <t>281468682.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>275009623.6</v>
+        <v>283145846.4</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>442557432.7</t>
+          <t>351622846.6</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>412480726.12</v>
+        <v>414970230.06</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-167547809</t>
+          <t>-68477000</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>18984900.35753776</t>
+          <t>-15789.41195628047</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-103171216.5056498</t>
+          <t>-104519583.1441735</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>289264312.0</t>
+          <t>281468682.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-5.12</t>
+          <t>-6.21</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -8951,7 +8951,7 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>32.15</t>
+          <t>32.09</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>26519</t>
+          <t>26464</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>97.2</t>
+          <t>97.9</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>94.1</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2248.507</t>
+          <t>3012.776</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>96.3</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-53.51</t>
+          <t>-37.86</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-12.56</t>
+          <t>-13.63</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9189,7 +9189,7 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>2252</t>
+          <t>1934</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9204,12 +9204,12 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -9219,38 +9219,38 @@
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>100.42</t>
+          <t>99.08000000000001</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>103.72</v>
+        <v>103.5</v>
       </c>
       <c r="AN21" t="n">
-        <v>103.4</v>
+        <v>103.2</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>104.41</t>
+          <t>104.3</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-215.80</t>
+          <t>-667.15</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-96.68</t>
+          <t>-98.76</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>1670896773.625714</t>
+          <t>1668913450.726819</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>220432535.0</t>
+          <t>289264312.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>268507044.2</v>
+        <v>275009623.6</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>577618774.1</t>
+          <t>442557432.7</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>409190484.56</v>
+        <v>412480726.12</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-309111729</t>
+          <t>-167547809</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>41195103.42357187</t>
+          <t>18984900.35753776</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-98395538.21827114</t>
+          <t>-103171216.5056498</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>220432535.0</t>
+          <t>289264312.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-3.94</t>
+          <t>-5.12</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9381,7 +9381,7 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>4.40</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>32.15</t>
+          <t>32.09</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>26519</t>
+          <t>26464</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>99.2</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>97.2</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>97.2</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>96.3</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-2.9</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>3626.375</t>
+          <t>2248.507</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-75.12</t>
+          <t>-53.51</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-11.57</t>
+          <t>-12.56</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,22 +9593,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>5.98</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr"/>
@@ -9619,7 +9619,7 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>2252</t>
+          <t>1934</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9634,53 +9634,53 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>101.72</t>
+          <t>100.42</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>103.96</v>
+        <v>103.72</v>
       </c>
       <c r="AN22" t="n">
-        <v>103.6</v>
+        <v>103.4</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>104.44</t>
+          <t>104.41</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-109.91</t>
+          <t>-215.80</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-94.89</t>
+          <t>-96.68</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>1670896773.625714</t>
+          <t>1668913450.726819</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>360108082.0</t>
+          <t>220432535.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>286154072.8</v>
+        <v>268507044.2</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>1150276311.8</t>
+          <t>577618774.1</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>408529389.62</v>
+        <v>409190484.56</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-864122239</t>
+          <t>-309111729</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>66575220.08572514</t>
+          <t>41195103.42357187</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-80684181.04993486</t>
+          <t>-98395538.21827114</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>360108082.0</t>
+          <t>220432535.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-2.86</t>
+          <t>-3.94</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9781,7 +9781,7 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>4.40</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>32.15</t>
+          <t>32.09</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>26519</t>
+          <t>26464</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>99.2</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>99.6</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>97.2</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2607.704</t>
+          <t>3626.375</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-4.53</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-77.08</t>
+          <t>-75.12</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-8.97</t>
+          <t>-11.57</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,22 +10023,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>5.98</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr"/>
@@ -10049,7 +10049,7 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>2252</t>
+          <t>1934</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10059,58 +10059,58 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>5.21</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>103.1</t>
+          <t>101.72</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>104.18</v>
+        <v>103.96</v>
       </c>
       <c r="AN23" t="n">
-        <v>103.79</v>
+        <v>103.6</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>104.52</t>
+          <t>104.44</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-53.80</t>
+          <t>-109.91</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-93.49</t>
+          <t>-94.89</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>1670896773.625714</t>
+          <t>1668913450.726819</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>264455621.0</t>
+          <t>360108082.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>299044660.2</v>
+        <v>286154072.8</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>1304605197.0</t>
+          <t>1150276311.8</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>411510598.5</v>
+        <v>408529389.62</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-1005560536</t>
+          <t>-864122239</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>93349656.65584514</t>
+          <t>66575220.08572514</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-67465901.52195692</t>
+          <t>-80684181.04993486</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>264455621.0</t>
+          <t>360108082.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.86</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10211,7 +10211,7 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>32.15</t>
+          <t>32.09</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>26519</t>
+          <t>26464</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/配電系統.xlsx
+++ b/Result/checksun_type/配電系統.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4456.494</t>
+          <t>3523.66</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>700.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-4.65</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>-14.40</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-5.15</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15.89</t>
+          <t>12.57</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-5.14</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>108</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>3524</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>27.54</t>
+          <t>37.68</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>39.13</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-4.23</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>12.69</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>702.2</t>
+          <t>702.4</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>737.35</v>
+        <v>733.4</v>
       </c>
       <c r="AN2" t="n">
-        <v>648.52</v>
+        <v>650.8200000000001</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>640.28</t>
+          <t>641.01</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-41.44</t>
+          <t>-42.31</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>13.01</t>
+          <t>11.60</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>22.23</t>
+          <t>20.10</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-72.48</t>
+          <t>-75.11</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>4935251699.197575</t>
+          <t>4933619914.912393</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>3163492460.0</t>
+          <t>2526492754.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>3132612269.2</v>
+        <v>2976124482.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>3269603904.2</t>
+          <t>3476901363.0</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>2494838192.4</v>
+        <v>2522196255.28</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-136991635</t>
+          <t>-500776880</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>27434120.50332935</t>
+          <t>23871683.71729021</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>76579952.95061398</t>
+          <t>4278281.394074917</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>3163492460.0</t>
+          <t>2526492754.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-9.33</t>
+          <t>-8.42</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>25.23</t>
+          <t>25.49</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>51.36</t>
+          <t>51.87</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>221116</t>
+          <t>223327</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>738.0</t>
+          <t>717.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>738.0</t>
+          <t>727.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>698.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>700.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5678.126</t>
+          <t>4456.494</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>700.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-4.65</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>44.32</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-5.15</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>15.89</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>-5.14</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>108</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>3524</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>69.57</t>
+          <t>27.54</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>29.95</t>
+          <t>39.13</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-5.19</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>14.16</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>699.8</t>
+          <t>702.2</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>738.1</v>
+        <v>737.35</v>
       </c>
       <c r="AN3" t="n">
-        <v>646.54</v>
+        <v>648.52</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>639.58</t>
+          <t>640.28</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-37.42</t>
+          <t>-41.44</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>15.35</t>
+          <t>13.01</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>24.53</t>
+          <t>22.23</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-69.62</t>
+          <t>-72.48</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>4935251699.197575</t>
+          <t>4933619914.912393</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>4127699179.0</t>
+          <t>3163492460.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>4379292599.4</v>
+        <v>3132612269.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>3034371558.8</t>
+          <t>3269603904.2</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>2446536212.66</v>
+        <v>2494838192.4</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>1344921040</t>
+          <t>-136991635</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>18498514.60382305</t>
+          <t>27434120.50332935</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>108883088.3545771</t>
+          <t>76579952.95061398</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>4127699179.0</t>
+          <t>3163492460.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-5.57</t>
+          <t>-9.33</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>26.28</t>
+          <t>25.23</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>51.36</t>
+          <t>51.87</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>221116</t>
+          <t>223327</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>704.0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>743.0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>704.0</t>
+          <t>698.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>700.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3102.28</t>
+          <t>5678.126</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>695.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>-3.11</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-4.65</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>74.46</t>
+          <t>44.32</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11.06</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>108</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>3524</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>20.29</t>
+          <t>69.57</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>14.56</t>
+          <t>29.95</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-5.19</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>13.98</t>
+          <t>14.16</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>701.8</t>
+          <t>699.8</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>734.15</v>
+        <v>738.1</v>
       </c>
       <c r="AN4" t="n">
-        <v>644.12</v>
+        <v>646.54</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>638.67</t>
+          <t>639.58</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-43.51</t>
+          <t>-37.42</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>15.15</t>
+          <t>15.35</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>26.82</t>
+          <t>24.53</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-66.78</t>
+          <t>-69.62</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>4935251699.197575</t>
+          <t>4933619914.912393</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>2145406818.0</t>
+          <t>4127699179.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>4705713538.6</v>
+        <v>4379292599.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>2697328683.0</t>
+          <t>3034371558.8</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>2381458909.08</v>
+        <v>2446536212.66</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>2008384855</t>
+          <t>1344921040</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>2064955.740049592</t>
+          <t>18498514.60382305</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>47833880.16900253</t>
+          <t>108883088.3545771</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>2145406818.0</t>
+          <t>4127699179.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-9.97</t>
+          <t>-5.57</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>26.28</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>51.36</t>
+          <t>51.87</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>221116</t>
+          <t>223327</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>689.0</t>
+          <t>704.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
+          <t>743.0</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
           <t>704.0</t>
         </is>
       </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>677.0</t>
-        </is>
-      </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>695.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4210.877</t>
+          <t>3102.28</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>681.0</t>
+          <t>695.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-4.65</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>75.25</t>
+          <t>74.46</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-7.72</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15.02</t>
+          <t>11.06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-5.28</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>108</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>3524</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.29</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>14.56</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-4.46</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-2.30</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>13.59</t>
+          <t>13.98</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>712.8</t>
+          <t>701.8</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>729.6</v>
+        <v>734.15</v>
       </c>
       <c r="AN5" t="n">
-        <v>642.3200000000001</v>
+        <v>644.12</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>638.33</t>
+          <t>638.67</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-38.99</t>
+          <t>-43.51</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>15.15</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>29.74</t>
+          <t>26.82</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-63.17</t>
+          <t>-66.78</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>4935251699.197575</t>
+          <t>4933619914.912393</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>2917531202.0</t>
+          <t>2145406818.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>4446393537.2</v>
+        <v>4705713538.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>2537135784.1</t>
+          <t>2697328683.0</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>2394527724.36</v>
+        <v>2381458909.08</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>1909257753</t>
+          <t>2008384855</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-6256666.883396398</t>
+          <t>2064955.740049592</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>171300840.0050039</t>
+          <t>47833880.16900253</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>2917531202.0</t>
+          <t>2145406818.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-11.79</t>
+          <t>-9.97</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2496,17 +2496,17 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>51.36</t>
+          <t>51.87</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>221116</t>
+          <t>223327</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,12 +2556,12 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>720.0</t>
+          <t>689.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>721.0</t>
+          <t>704.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
@@ -2571,7 +2571,7 @@
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>681.0</t>
+          <t>695.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4656.178</t>
+          <t>4210.877</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>681.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-4.65</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>70.21</t>
+          <t>75.25</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>-7.72</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16.60</t>
+          <t>15.02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-5.28</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>108</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>3524</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-4.46</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-2.30</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>13.59</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>718.0</t>
+          <t>712.8</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>726.45</v>
+        <v>729.6</v>
       </c>
       <c r="AN6" t="n">
-        <v>641.1799999999999</v>
+        <v>642.3200000000001</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>638.1</t>
+          <t>638.33</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-29.15</t>
+          <t>-38.99</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>23.12</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>32.64</t>
+          <t>29.74</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-59.58</t>
+          <t>-63.17</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>4935251699.197575</t>
+          <t>4933619914.912393</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>3308931687.0</t>
+          <t>2917531202.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>3977678243.4</v>
+        <v>4446393537.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>2336901368.1</t>
+          <t>2537135784.1</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>2356977274.04</v>
+        <v>2394527724.36</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>1640776875</t>
+          <t>1909257753</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-38539849.95401464</t>
+          <t>-6256666.883396398</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>258836711.484827</t>
+          <t>171300840.0050039</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>3308931687.0</t>
+          <t>2917531202.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-8.55</t>
+          <t>-11.79</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2926,17 +2926,17 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>51.36</t>
+          <t>51.87</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>221116</t>
+          <t>223327</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>701.0</t>
+          <t>720.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>721.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>698.0</t>
+          <t>677.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>681.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-7.07</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>12908.308</t>
+          <t>4656.178</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>688.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-4.65</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>62.76</t>
+          <t>70.21</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-6.78</t>
+          <t>-4.34</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>46.03</t>
+          <t>16.60</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-13.23</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>108</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>3524</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>39.68</t>
+          <t>24.72</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-5.02</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>12.71</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>724.4</t>
+          <t>718.0</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>720.75</v>
+        <v>726.45</v>
       </c>
       <c r="AN7" t="n">
-        <v>639.48</v>
+        <v>641.1799999999999</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>637.48</t>
+          <t>638.1</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-24.05</t>
+          <t>-29.15</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>26.60</t>
+          <t>23.12</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>35.02</t>
+          <t>32.64</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-56.63</t>
+          <t>-59.58</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>4935251699.197575</t>
+          <t>4933619914.912393</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>9396894111.0</t>
+          <t>3308931687.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>3406595539.2</v>
+        <v>3977678243.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>2092972596.2</t>
+          <t>2336901368.1</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>2319670873.56</v>
+        <v>2356977274.04</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>1313622943</t>
+          <t>1640776875</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-92608315.67016768</t>
+          <t>-38539849.95401464</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>332708021.9386873</t>
+          <t>258836711.484827</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>9396894111.0</t>
+          <t>3308931687.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-10.88</t>
+          <t>-8.55</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3361,12 +3361,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>24.80</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>51.36</t>
+          <t>51.87</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>221116</t>
+          <t>223327</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>721.0</t>
+          <t>701.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>780.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>687.0</t>
+          <t>698.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>688.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-7.07</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>7500.722</t>
+          <t>12908.308</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>739.0</t>
+          <t>688.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-5.57</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-4.65</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>32.75</t>
+          <t>62.76</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-6.78</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>26.75</t>
+          <t>46.03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-7.70</t>
+          <t>-13.23</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,17 +3594,17 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>108</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>3524</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>50.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -3614,53 +3614,53 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>-5.02</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>12.71</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>731.2</t>
+          <t>724.4</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>715.55</v>
+        <v>720.75</v>
       </c>
       <c r="AN8" t="n">
-        <v>638.3</v>
+        <v>639.48</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>636.88</t>
+          <t>637.48</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-12.52</t>
+          <t>-24.05</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>32.48</t>
+          <t>26.60</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>37.13</t>
+          <t>35.02</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-54.03</t>
+          <t>-56.63</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>4935251699.197575</t>
+          <t>4933619914.912393</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>5759803875.0</t>
+          <t>9396894111.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>1689450518.2</v>
+        <v>3406595539.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>1272693479.4</t>
+          <t>2092972596.2</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>2149905312.46</v>
+        <v>2319670873.56</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>416757038</t>
+          <t>1313622943</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-169938558.8717777</t>
+          <t>-92608315.67016768</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-225925652.1964645</t>
+          <t>332708021.9386873</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>5759803875.0</t>
+          <t>9396894111.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-10.88</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3791,12 +3791,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>26.64</t>
+          <t>24.80</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>51.36</t>
+          <t>51.87</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>221116</t>
+          <t>223327</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>789.0</t>
+          <t>721.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>803.0</t>
+          <t>780.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>732.0</t>
+          <t>687.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>739.0</t>
+          <t>688.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1152.161</t>
+          <t>7500.722</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>739.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-7.14</t>
+          <t>-4.53</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-4.65</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-19.96</t>
+          <t>32.75</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>26.75</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>-7.70</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>108</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>3524</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>68.25</t>
+          <t>50.79</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>31.22</t>
+          <t>39.68</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>732.4</t>
+          <t>731.2</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>708.6</v>
+        <v>715.55</v>
       </c>
       <c r="AN9" t="n">
-        <v>635.96</v>
+        <v>638.3</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>635.39</t>
+          <t>636.88</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-10.37</t>
+          <t>-12.52</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>34.32</t>
+          <t>32.48</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>38.29</t>
+          <t>37.13</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-52.59</t>
+          <t>-54.03</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>4935251699.197575</t>
+          <t>4933619914.912393</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>848806811.0</t>
+          <t>5759803875.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>688943827.4</v>
+        <v>1689450518.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>860708905.5</t>
+          <t>1272693479.4</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>2069337538.82</v>
+        <v>2149905312.46</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-171765078</t>
+          <t>416757038</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-159759087.3581983</t>
+          <t>-169938558.8717777</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-626216745.2396646</t>
+          <t>-225925652.1964645</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>848806811.0</t>
+          <t>5759803875.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>27.04</t>
+          <t>26.64</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>51.36</t>
+          <t>51.87</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>221116</t>
+          <t>223327</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>789.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>803.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>732.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>739.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>799.533</t>
+          <t>1152.161</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-6.08</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-4.65</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-58.59</t>
+          <t>-19.96</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-4.20</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-4.53</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>108</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>3524</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>68.25</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>8.47</t>
+          <t>31.22</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>10.66</t>
+          <t>11.42</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>735.4</t>
+          <t>732.4</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>701.1</v>
+        <v>708.6</v>
       </c>
       <c r="AN10" t="n">
-        <v>633.54</v>
+        <v>635.96</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>634.25</t>
+          <t>635.39</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-10.78</t>
+          <t>-10.37</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>34.32</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>39.28</t>
+          <t>38.29</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-51.36</t>
+          <t>-52.59</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>4935251699.197575</t>
+          <t>4933619914.912393</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>573954733.0</t>
+          <t>848806811.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>627878031</v>
+        <v>688943827.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>1516353585.7</t>
+          <t>860708905.5</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>2106062606.14</v>
+        <v>2069337538.82</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-888475554</t>
+          <t>-171765078</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-74948604.10702263</t>
+          <t>-159759087.3581983</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-649518023.2571056</t>
+          <t>-626216745.2396646</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>573954733.0</t>
+          <t>848806811.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-8.42</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,22 +4641,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>25.49</t>
+          <t>27.04</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>51.36</t>
+          <t>51.87</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>221116</t>
+          <t>223327</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>740.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>740.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>617.266</t>
+          <t>799.533</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,72 +4768,72 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>707.0</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>-1.86</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>-58.59</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2025-11-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-09-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>785.0</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
           <t>738.0</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>-5.43</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>-4.65</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>-75.86</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2025-11-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-09-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>785.0</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>738.0</t>
-        </is>
-      </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>785.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
@@ -4848,12 +4848,12 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>-5.99</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>-4.53</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,17 +4884,17 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>108</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>3524</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -4904,53 +4904,53 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>10.09</t>
+          <t>10.66</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>745.6</t>
+          <t>735.4</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>695.2</v>
+        <v>701.1</v>
       </c>
       <c r="AN11" t="n">
-        <v>631.48</v>
+        <v>633.54</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>633.66</t>
+          <t>634.25</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-10.78</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>35.05</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>40.34</t>
+          <t>39.28</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-50.05</t>
+          <t>-51.36</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,48 +4970,48 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>4935251699.197575</t>
+          <t>4933619914.912393</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>453518166.0</t>
+          <t>573954733.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>696124492.8</v>
+        <v>627878031</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>2883970531.7</t>
+          <t>1516353585.7</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>2126707687.18</v>
+        <v>2106062606.14</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-2147483648</t>
+          <t>-888475554</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>29518563.01117429</t>
+          <t>-74948604.10702263</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-630160054.0942674</t>
+          <t>-649518023.2571056</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>453518166.0</t>
+          <t>573954733.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-4.40</t>
+          <t>-8.42</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>26.60</t>
+          <t>25.49</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>51.36</t>
+          <t>51.87</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>221116</t>
+          <t>223327</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>737.0</t>
+          <t>740.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>739.0</t>
+          <t>740.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>730.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>738.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5173,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1116.653</t>
+          <t>617.266</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-4.38</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-4.65</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-80.90</t>
+          <t>-75.86</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5278,12 +5278,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>-8.03</t>
+          <t>-5.99</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>108</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>3524</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>23.47</t>
+          <t>8.47</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-3.99</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>9.29</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>10.09</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>752.0</t>
+          <t>745.6</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>688.05</v>
+        <v>695.2</v>
       </c>
       <c r="AN12" t="n">
-        <v>628.72</v>
+        <v>631.48</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>632.04</t>
+          <t>633.66</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>42.23</t>
+          <t>39.85</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>40.46</t>
+          <t>40.34</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-49.89</t>
+          <t>-50.05</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,24 +5400,24 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>4935251699.197575</t>
+          <t>4933619914.912393</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>811169006.0</t>
+          <t>453518166.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>779349653.2</v>
+        <v>696124492.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>4079717323.9</t>
+          <t>2883970531.7</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>2168937186.34</v>
+        <v>2126707687.18</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5426,17 +5426,17 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>149460129.7576182</t>
+          <t>29518563.01117429</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-567096178.3225608</t>
+          <t>-630160054.0942674</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>811169006.0</t>
+          <t>453518166.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-6.48</t>
+          <t>-4.40</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>26.03</t>
+          <t>26.60</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>51.36</t>
+          <t>51.87</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>221116</t>
+          <t>223327</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>725.0</t>
+          <t>737.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>736.0</t>
+          <t>739.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>730.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5603,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1934.14</t>
+          <t>1237.634</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>96.9</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-36.48</t>
+          <t>-38.77</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-13.09</t>
+          <t>-14.62</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,73 +5744,73 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>1238</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>58.54</t>
+          <t>17.07</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>62.6</t>
+          <t>46.34</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-5.36</t>
+          <t>-4.37</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>96.18</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>101.64</v>
+        <v>100.58</v>
       </c>
       <c r="AN13" t="n">
-        <v>101.52</v>
+        <v>101.32</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>103.55</t>
+          <t>103.42</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-22.57</t>
+          <t>-19.71</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-111.21</t>
+          <t>-111.79</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>1668913450.726819</t>
+          <t>1666790472.826923</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>187058281.0</t>
+          <t>119055310.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>178982304.2</v>
+        <v>166326125</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>281758656.3</t>
+          <t>271620933.8</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>421804108.64</v>
+        <v>421729365.34</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-102776352</t>
+          <t>-105294808</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-58111350.65553775</t>
+          <t>-62667400.97133053</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-86249193.25747448</t>
+          <t>-87725677.7081908</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>187058281.0</t>
+          <t>119055310.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-4.53</t>
+          <t>-6.21</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -5931,22 +5931,22 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>2</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>32.09</t>
+          <t>31.52</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>26464</t>
+          <t>26000</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>96.8</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>97.6</t>
+          <t>97.7</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>96.9</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2251.93</t>
+          <t>1934.14</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>97.1</t>
+          <t>96.9</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>-36.48</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-12.91</t>
+          <t>-13.09</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,73 +6174,73 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>1238</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>63.41</t>
+          <t>58.54</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>43.09</t>
+          <t>62.6</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-6.32</t>
+          <t>-5.36</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>95.86</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>102.32</v>
+        <v>101.64</v>
       </c>
       <c r="AN14" t="n">
-        <v>101.67</v>
+        <v>101.52</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>103.67</t>
+          <t>103.55</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-34.44</t>
+          <t>-22.57</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-110.58</t>
+          <t>-111.21</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>1668913450.726819</t>
+          <t>1666790472.826923</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>219814205.0</t>
+          <t>187058281.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>284371450.4</v>
+        <v>178982304.2</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>299063636.4</t>
+          <t>281758656.3</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>422852603.5</v>
+        <v>421804108.64</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-14692186</t>
+          <t>-102776352</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-52995379.27336744</t>
+          <t>-58111350.65553775</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-88345634.03296983</t>
+          <t>-86249193.25747448</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>219814205.0</t>
+          <t>187058281.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-4.33</t>
+          <t>-4.53</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6371,12 +6371,12 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>2</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>32.09</t>
+          <t>31.52</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>26464</t>
+          <t>26000</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
+          <t>97.5</t>
+        </is>
+      </c>
+      <c r="CE14" t="inlineStr">
+        <is>
           <t>97.6</t>
         </is>
       </c>
-      <c r="CE14" t="inlineStr">
-        <is>
-          <t>98.6</t>
-        </is>
-      </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>96.7</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>97.1</t>
+          <t>96.9</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1654.541</t>
+          <t>2251.93</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>97.2</t>
+          <t>97.1</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-12.83</t>
+          <t>-12.91</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,73 +6604,73 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>1238</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>65.85</t>
+          <t>63.41</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>22.48</t>
+          <t>43.09</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-6.18</t>
+          <t>-6.32</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>96.16</t>
+          <t>95.86</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>102.5</v>
+        <v>102.32</v>
       </c>
       <c r="AN15" t="n">
-        <v>101.88</v>
+        <v>101.67</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>103.75</t>
+          <t>103.67</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-52.73</t>
+          <t>-34.44</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-109.67</t>
+          <t>-110.58</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>1668913450.726819</t>
+          <t>1666790472.826923</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>159843579.0</t>
+          <t>219814205.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>323909709.6</v>
+        <v>284371450.4</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>303527778.0</t>
+          <t>299063636.4</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>427891465.06</v>
+        <v>422852603.5</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>20381931</t>
+          <t>-14692186</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-46568060.22616701</t>
+          <t>-52995379.27336744</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-91694911.4967857</t>
+          <t>-88345634.03296983</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>159843579.0</t>
+          <t>219814205.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-4.24</t>
+          <t>-4.33</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
@@ -6791,12 +6791,12 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
@@ -6806,7 +6806,7 @@
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>2</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>32.09</t>
+          <t>31.52</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>26464</t>
+          <t>26000</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>97.6</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>97.2</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>96.7</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>97.2</t>
+          <t>97.1</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1536.151</t>
+          <t>1654.541</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>97.2</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>-2.1</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>11.75</t>
+          <t>6.72</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-15.25</t>
+          <t>-12.83</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,73 +7034,73 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>1238</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>65.85</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>22.48</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-6.60</t>
+          <t>-6.18</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>95.75999999999999</t>
+          <t>96.16</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>102.53</v>
+        <v>102.5</v>
       </c>
       <c r="AN16" t="n">
-        <v>102.08</v>
+        <v>101.88</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>103.82</t>
+          <t>103.75</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-82.43</t>
+          <t>-52.73</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-108.39</t>
+          <t>-109.67</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>1668913450.726819</t>
+          <t>1666790472.826923</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>145859250.0</t>
+          <t>159843579.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>348234730.2</v>
+        <v>323909709.6</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>311622176.9</t>
+          <t>303527778.0</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>429640696.94</v>
+        <v>427891465.06</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>36612553</t>
+          <t>20381931</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-38363178.1769636</t>
+          <t>-46568060.22616701</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-86779351.10592324</t>
+          <t>-91694911.4967857</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>145859250.0</t>
+          <t>159843579.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-6.90</t>
+          <t>-4.24</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7201,7 +7201,7 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
@@ -7221,22 +7221,22 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>2</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>32.09</t>
+          <t>31.52</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>26464</t>
+          <t>26000</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>97.2</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>97.2</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1914.684</t>
+          <t>1536.151</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>95.3</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>16.80</t>
+          <t>11.75</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-14.53</t>
+          <t>-15.25</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,73 +7464,73 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>1238</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>13.41</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-6.38</t>
+          <t>-6.60</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>96.12</t>
+          <t>95.75999999999999</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>102.68</v>
+        <v>102.53</v>
       </c>
       <c r="AN17" t="n">
-        <v>102.33</v>
+        <v>102.08</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>103.93</t>
+          <t>103.82</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-109.29</t>
+          <t>-82.43</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-106.66</t>
+          <t>-108.39</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>1668913450.726819</t>
+          <t>1666790472.826923</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>182336206.0</t>
+          <t>145859250.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>376915742.6</v>
+        <v>348234730.2</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>322711393.4</t>
+          <t>311622176.9</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>429470961.98</v>
+        <v>429640696.94</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>54204349</t>
+          <t>36612553</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-29560237.64442549</t>
+          <t>-38363178.1769636</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-75159538.47233671</t>
+          <t>-86779351.10592324</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>182336206.0</t>
+          <t>145859250.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-6.11</t>
+          <t>-6.90</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
@@ -7651,22 +7651,22 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>2</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>32.09</t>
+          <t>31.52</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>26464</t>
+          <t>26000</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>95.8</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>96.3</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>95.3</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-3.53</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>7327.598</t>
+          <t>1914.684</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>95.3</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>14.67</t>
+          <t>16.80</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-14.62</t>
+          <t>-14.53</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12.09</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-4.94</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,73 +7894,73 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>1238</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>12.88</t>
+          <t>13.41</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-6.09</t>
+          <t>-6.38</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>96.56</t>
+          <t>96.12</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>102.82</v>
+        <v>102.68</v>
       </c>
       <c r="AN18" t="n">
-        <v>102.56</v>
+        <v>102.33</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>104.04</t>
+          <t>103.93</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-159.05</t>
+          <t>-109.29</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-104.84</t>
+          <t>-106.66</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1668913450.726819</t>
+          <t>1666790472.826923</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>714004012.0</t>
+          <t>182336206.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>384535008.4</v>
+        <v>376915742.6</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>335344540.6</t>
+          <t>322711393.4</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>431976435.3</v>
+        <v>429470961.98</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>49190467</t>
+          <t>54204349</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-21269455.67571436</t>
+          <t>-29560237.64442549</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-59783782.19320107</t>
+          <t>-75159538.47233671</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>714004012.0</t>
+          <t>182336206.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-6.21</t>
+          <t>-6.11</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
@@ -8081,22 +8081,22 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>2</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>32.09</t>
+          <t>31.52</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>26464</t>
+          <t>26000</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>95.8</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>96.6</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>95.1</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>95.3</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>-3.53</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>4255.671</t>
+          <t>7327.598</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>14.67</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-11.57</t>
+          <t>-14.62</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>7.02</t>
+          <t>12.09</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>-4.94</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,17 +8324,17 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>1238</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>38.64</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
@@ -8344,53 +8344,53 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-5.63</t>
+          <t>-6.09</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>97.24000000000001</t>
+          <t>96.56</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>103.04</v>
+        <v>102.82</v>
       </c>
       <c r="AN19" t="n">
-        <v>102.79</v>
+        <v>102.56</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>104.13</t>
+          <t>104.04</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-260.17</t>
+          <t>-159.05</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-102.92</t>
+          <t>-104.84</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>1668913450.726819</t>
+          <t>1666790472.826923</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>417505501.0</t>
+          <t>714004012.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>313755822.4</v>
+        <v>384535008.4</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>306400241.3</t>
+          <t>335344540.6</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>420660383.62</v>
+        <v>431976435.3</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>7355581</t>
+          <t>49190467</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-14266850.85435314</t>
+          <t>-21269455.67571436</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-92647688.78753585</t>
+          <t>-59783782.19320107</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>417505501.0</t>
+          <t>714004012.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-2.86</t>
+          <t>-6.21</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
@@ -8511,22 +8511,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>2</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>32.09</t>
+          <t>31.52</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>26464</t>
+          <t>26000</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,7 +8576,7 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>98.4</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
@@ -8586,12 +8586,12 @@
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>95.1</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2950.547</t>
+          <t>4255.671</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>-3.57</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-19.47</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-14.62</t>
+          <t>-11.57</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>7.02</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,73 +8754,73 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>1238</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>38.64</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.88</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-5.20</t>
+          <t>-5.63</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>97.82</t>
+          <t>97.24000000000001</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>103.19</v>
+        <v>103.04</v>
       </c>
       <c r="AN20" t="n">
-        <v>102.95</v>
+        <v>102.79</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>104.19</t>
+          <t>104.13</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-887.49</t>
+          <t>-260.17</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-101.02</t>
+          <t>-102.92</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>1668913450.726819</t>
+          <t>1666790472.826923</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>281468682.0</t>
+          <t>417505501.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>283145846.4</v>
+        <v>313755822.4</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>351622846.6</t>
+          <t>306400241.3</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>414970230.06</v>
+        <v>420660383.62</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-68477000</t>
+          <t>7355581</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-15789.41195628047</t>
+          <t>-14266850.85435314</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-104519583.1441735</t>
+          <t>-92647688.78753585</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>281468682.0</t>
+          <t>417505501.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-6.21</t>
+          <t>-2.86</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
@@ -8941,22 +8941,22 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>2</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>32.09</t>
+          <t>31.52</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>26464</t>
+          <t>26000</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>98.4</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>97.9</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>94.1</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>3012.776</t>
+          <t>2950.547</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-37.86</t>
+          <t>-19.47</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-13.63</t>
+          <t>-14.62</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,12 +9184,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>1238</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9204,53 +9204,53 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-5.20</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>99.08000000000001</t>
+          <t>97.82</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>103.5</v>
+        <v>103.19</v>
       </c>
       <c r="AN21" t="n">
-        <v>103.2</v>
+        <v>102.95</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>104.3</t>
+          <t>104.19</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-667.15</t>
+          <t>-887.49</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-98.76</t>
+          <t>-101.02</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>1668913450.726819</t>
+          <t>1666790472.826923</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>289264312.0</t>
+          <t>281468682.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>275009623.6</v>
+        <v>283145846.4</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>442557432.7</t>
+          <t>351622846.6</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>412480726.12</v>
+        <v>414970230.06</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-167547809</t>
+          <t>-68477000</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>18984900.35753776</t>
+          <t>-15789.41195628047</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-103171216.5056498</t>
+          <t>-104519583.1441735</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>289264312.0</t>
+          <t>281468682.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-5.12</t>
+          <t>-6.21</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
@@ -9371,22 +9371,22 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>2</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>32.09</t>
+          <t>31.52</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>26464</t>
+          <t>26000</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>97.2</t>
+          <t>97.9</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>94.1</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2248.507</t>
+          <t>3012.776</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>96.3</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-53.51</t>
+          <t>-37.86</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-12.56</t>
+          <t>-13.63</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,12 +9614,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>1238</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9634,12 +9634,12 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
@@ -9649,38 +9649,38 @@
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>100.42</t>
+          <t>99.08000000000001</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>103.72</v>
+        <v>103.5</v>
       </c>
       <c r="AN22" t="n">
-        <v>103.4</v>
+        <v>103.2</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>104.41</t>
+          <t>104.3</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-215.80</t>
+          <t>-667.15</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-96.68</t>
+          <t>-98.76</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>1668913450.726819</t>
+          <t>1666790472.826923</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>220432535.0</t>
+          <t>289264312.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>268507044.2</v>
+        <v>275009623.6</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>577618774.1</t>
+          <t>442557432.7</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>409190484.56</v>
+        <v>412480726.12</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-309111729</t>
+          <t>-167547809</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>41195103.42357187</t>
+          <t>18984900.35753776</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-98395538.21827114</t>
+          <t>-103171216.5056498</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>220432535.0</t>
+          <t>289264312.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-3.94</t>
+          <t>-5.12</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9781,7 +9781,7 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>4.40</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>2</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>32.09</t>
+          <t>31.52</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>26464</t>
+          <t>26000</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>99.2</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>97.2</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>97.2</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>96.3</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-2.9</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>3626.375</t>
+          <t>2248.507</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-75.12</t>
+          <t>-53.51</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-11.57</t>
+          <t>-12.56</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,33 +10023,33 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>5.98</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>1238</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10064,53 +10064,53 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>101.72</t>
+          <t>100.42</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>103.96</v>
+        <v>103.72</v>
       </c>
       <c r="AN23" t="n">
-        <v>103.6</v>
+        <v>103.4</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>104.44</t>
+          <t>104.41</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-109.91</t>
+          <t>-215.80</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-94.89</t>
+          <t>-96.68</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>1668913450.726819</t>
+          <t>1666790472.826923</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>360108082.0</t>
+          <t>220432535.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>286154072.8</v>
+        <v>268507044.2</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>1150276311.8</t>
+          <t>577618774.1</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>408529389.62</v>
+        <v>409190484.56</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-864122239</t>
+          <t>-309111729</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>66575220.08572514</t>
+          <t>41195103.42357187</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-80684181.04993486</t>
+          <t>-98395538.21827114</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>360108082.0</t>
+          <t>220432535.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-2.86</t>
+          <t>-3.94</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10211,7 +10211,7 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>4.40</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>2</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>32.09</t>
+          <t>31.52</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>26464</t>
+          <t>26000</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>99.2</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>99.6</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>97.2</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/配電系統.xlsx
+++ b/Result/checksun_type/配電系統.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3523.66</t>
+          <t>3516.568</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>691.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-3.62</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-14.40</t>
+          <t>-21.29</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-4.20</t>
+          <t>-6.37</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>12.54</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>188</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>3524</t>
+          <t>3517</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>37.68</t>
+          <t>17.24</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>27.49</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-4.23</t>
+          <t>-3.42</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>12.69</t>
+          <t>11.69</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>702.4</t>
+          <t>704.4</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>733.4</v>
+        <v>729.35</v>
       </c>
       <c r="AN2" t="n">
-        <v>650.8200000000001</v>
+        <v>653</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>641.01</t>
+          <t>641.5</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-42.31</t>
+          <t>-49.29</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>11.60</t>
+          <t>9.08</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>20.10</t>
+          <t>17.90</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-75.11</t>
+          <t>-77.84</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>4933619914.912393</t>
+          <t>4931859360.209104</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>2526492754.0</t>
+          <t>2463966639.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>2976124482.6</v>
+        <v>2885411570</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>3476901363.0</t>
+          <t>3665902553.6</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>2522196255.28</v>
+        <v>2552773254.62</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-500776880</t>
+          <t>-780490983</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>23871683.71729021</t>
+          <t>12333070.16765259</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>4278281.394074917</t>
+          <t>-51129304.35535431</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>2526492754.0</t>
+          <t>2463966639.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-8.42</t>
+          <t>-10.49</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>25.49</t>
+          <t>24.91</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>51.87</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>223327</t>
+          <t>218273</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>717.0</t>
+          <t>711.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>727.0</t>
+          <t>718.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>691.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>691.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4456.494</t>
+          <t>3523.66</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>700.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-3.62</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>-14.40</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-5.15</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15.89</t>
+          <t>12.57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-5.14</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>188</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>3524</t>
+          <t>3517</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>27.54</t>
+          <t>37.68</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>39.13</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-4.23</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>12.69</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>702.2</t>
+          <t>702.4</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>737.35</v>
+        <v>733.4</v>
       </c>
       <c r="AN3" t="n">
-        <v>648.52</v>
+        <v>650.8200000000001</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>640.28</t>
+          <t>641.01</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-41.44</t>
+          <t>-42.31</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>13.01</t>
+          <t>11.60</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>22.23</t>
+          <t>20.10</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-72.48</t>
+          <t>-75.11</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>4933619914.912393</t>
+          <t>4931859360.209104</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>3163492460.0</t>
+          <t>2526492754.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>3132612269.2</v>
+        <v>2976124482.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>3269603904.2</t>
+          <t>3476901363.0</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>2494838192.4</v>
+        <v>2522196255.28</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-136991635</t>
+          <t>-500776880</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>27434120.50332935</t>
+          <t>23871683.71729021</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>76579952.95061398</t>
+          <t>4278281.394074917</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>3163492460.0</t>
+          <t>2526492754.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-9.33</t>
+          <t>-8.42</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>25.23</t>
+          <t>25.49</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>51.87</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>223327</t>
+          <t>218273</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>738.0</t>
+          <t>717.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>738.0</t>
+          <t>727.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>698.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>700.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5678.126</t>
+          <t>4456.494</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>700.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-3.11</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-3.62</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>44.32</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-5.15</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>15.89</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>-5.14</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>188</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>3524</t>
+          <t>3517</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>69.57</t>
+          <t>27.54</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>29.95</t>
+          <t>39.13</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-5.19</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>14.16</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>699.8</t>
+          <t>702.2</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>738.1</v>
+        <v>737.35</v>
       </c>
       <c r="AN4" t="n">
-        <v>646.54</v>
+        <v>648.52</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>639.58</t>
+          <t>640.28</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-37.42</t>
+          <t>-41.44</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>15.35</t>
+          <t>13.01</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>24.53</t>
+          <t>22.23</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-69.62</t>
+          <t>-72.48</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>4933619914.912393</t>
+          <t>4931859360.209104</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>4127699179.0</t>
+          <t>3163492460.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>4379292599.4</v>
+        <v>3132612269.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>3034371558.8</t>
+          <t>3269603904.2</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>2446536212.66</v>
+        <v>2494838192.4</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>1344921040</t>
+          <t>-136991635</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>18498514.60382305</t>
+          <t>27434120.50332935</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>108883088.3545771</t>
+          <t>76579952.95061398</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>4127699179.0</t>
+          <t>3163492460.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-5.57</t>
+          <t>-9.33</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>26.28</t>
+          <t>25.23</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>51.87</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>223327</t>
+          <t>218273</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>704.0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>743.0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>704.0</t>
+          <t>698.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>700.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3102.28</t>
+          <t>5678.126</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>695.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>-5.5</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-3.62</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>74.46</t>
+          <t>44.32</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11.06</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>188</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>3524</t>
+          <t>3517</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>20.29</t>
+          <t>69.57</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>14.56</t>
+          <t>29.95</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-5.19</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>13.98</t>
+          <t>14.16</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>701.8</t>
+          <t>699.8</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>734.15</v>
+        <v>738.1</v>
       </c>
       <c r="AN5" t="n">
-        <v>644.12</v>
+        <v>646.54</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>638.67</t>
+          <t>639.58</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-43.51</t>
+          <t>-37.42</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>15.15</t>
+          <t>15.35</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>26.82</t>
+          <t>24.53</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-66.78</t>
+          <t>-69.62</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>4933619914.912393</t>
+          <t>4931859360.209104</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>2145406818.0</t>
+          <t>4127699179.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>4705713538.6</v>
+        <v>4379292599.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>2697328683.0</t>
+          <t>3034371558.8</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>2381458909.08</v>
+        <v>2446536212.66</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>2008384855</t>
+          <t>1344921040</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>2064955.740049592</t>
+          <t>18498514.60382305</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>47833880.16900253</t>
+          <t>108883088.3545771</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>2145406818.0</t>
+          <t>4127699179.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-9.97</t>
+          <t>-5.57</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>26.28</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>51.87</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>223327</t>
+          <t>218273</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>689.0</t>
+          <t>704.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
+          <t>743.0</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
           <t>704.0</t>
         </is>
       </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>677.0</t>
-        </is>
-      </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>695.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4210.877</t>
+          <t>3102.28</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>681.0</t>
+          <t>695.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-3.62</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>75.25</t>
+          <t>74.46</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-7.72</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15.02</t>
+          <t>11.06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-5.28</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>188</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>3524</t>
+          <t>3517</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.29</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>14.56</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-4.46</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-2.30</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>13.59</t>
+          <t>13.98</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>712.8</t>
+          <t>701.8</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>729.6</v>
+        <v>734.15</v>
       </c>
       <c r="AN6" t="n">
-        <v>642.3200000000001</v>
+        <v>644.12</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>638.33</t>
+          <t>638.67</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-38.99</t>
+          <t>-43.51</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>15.15</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>29.74</t>
+          <t>26.82</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-63.17</t>
+          <t>-66.78</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>4933619914.912393</t>
+          <t>4931859360.209104</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>2917531202.0</t>
+          <t>2145406818.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>4446393537.2</v>
+        <v>4705713538.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>2537135784.1</t>
+          <t>2697328683.0</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>2394527724.36</v>
+        <v>2381458909.08</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>1909257753</t>
+          <t>2008384855</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-6256666.883396398</t>
+          <t>2064955.740049592</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>171300840.0050039</t>
+          <t>47833880.16900253</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>2917531202.0</t>
+          <t>2145406818.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-11.79</t>
+          <t>-9.97</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2926,17 +2926,17 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>51.87</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>223327</t>
+          <t>218273</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>720.0</t>
+          <t>689.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>721.0</t>
+          <t>704.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>681.0</t>
+          <t>695.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4656.178</t>
+          <t>4210.877</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>681.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-3.62</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>70.21</t>
+          <t>75.25</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>-7.72</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16.60</t>
+          <t>15.02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-5.28</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>188</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>3524</t>
+          <t>3517</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-4.46</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-2.30</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>13.59</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>718.0</t>
+          <t>712.8</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>726.45</v>
+        <v>729.6</v>
       </c>
       <c r="AN7" t="n">
-        <v>641.1799999999999</v>
+        <v>642.3200000000001</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>638.1</t>
+          <t>638.33</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-29.15</t>
+          <t>-38.99</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>23.12</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>32.64</t>
+          <t>29.74</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-59.58</t>
+          <t>-63.17</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>4933619914.912393</t>
+          <t>4931859360.209104</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>3308931687.0</t>
+          <t>2917531202.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>3977678243.4</v>
+        <v>4446393537.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>2336901368.1</t>
+          <t>2537135784.1</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>2356977274.04</v>
+        <v>2394527724.36</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>1640776875</t>
+          <t>1909257753</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-38539849.95401464</t>
+          <t>-6256666.883396398</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>258836711.484827</t>
+          <t>171300840.0050039</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>3308931687.0</t>
+          <t>2917531202.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-8.55</t>
+          <t>-11.79</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3356,17 +3356,17 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>51.87</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>223327</t>
+          <t>218273</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>701.0</t>
+          <t>720.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>721.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>698.0</t>
+          <t>677.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>681.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-7.07</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>12908.308</t>
+          <t>4656.178</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>688.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-3.62</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>62.76</t>
+          <t>70.21</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-6.78</t>
+          <t>-4.34</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>46.03</t>
+          <t>16.60</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-13.23</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>188</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>3524</t>
+          <t>3517</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>39.68</t>
+          <t>24.72</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-5.02</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>12.71</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>724.4</t>
+          <t>718.0</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>720.75</v>
+        <v>726.45</v>
       </c>
       <c r="AN8" t="n">
-        <v>639.48</v>
+        <v>641.1799999999999</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>637.48</t>
+          <t>638.1</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-24.05</t>
+          <t>-29.15</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>26.60</t>
+          <t>23.12</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>35.02</t>
+          <t>32.64</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-56.63</t>
+          <t>-59.58</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>4933619914.912393</t>
+          <t>4931859360.209104</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>9396894111.0</t>
+          <t>3308931687.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>3406595539.2</v>
+        <v>3977678243.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>2092972596.2</t>
+          <t>2336901368.1</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>2319670873.56</v>
+        <v>2356977274.04</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>1313622943</t>
+          <t>1640776875</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-92608315.67016768</t>
+          <t>-38539849.95401464</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>332708021.9386873</t>
+          <t>258836711.484827</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>9396894111.0</t>
+          <t>3308931687.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-10.88</t>
+          <t>-8.55</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3791,12 +3791,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>24.80</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>51.87</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>223327</t>
+          <t>218273</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>721.0</t>
+          <t>701.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>780.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>687.0</t>
+          <t>698.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>688.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-7.07</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>7500.722</t>
+          <t>12908.308</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>739.0</t>
+          <t>688.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-4.53</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-3.62</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>32.75</t>
+          <t>62.76</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-6.78</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>26.75</t>
+          <t>46.03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-7.70</t>
+          <t>-13.23</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,17 +4024,17 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>188</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>3524</t>
+          <t>3517</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>50.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -4044,53 +4044,53 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>-5.02</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>12.71</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>731.2</t>
+          <t>724.4</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>715.55</v>
+        <v>720.75</v>
       </c>
       <c r="AN9" t="n">
-        <v>638.3</v>
+        <v>639.48</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>636.88</t>
+          <t>637.48</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-12.52</t>
+          <t>-24.05</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>32.48</t>
+          <t>26.60</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>37.13</t>
+          <t>35.02</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-54.03</t>
+          <t>-56.63</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>4933619914.912393</t>
+          <t>4931859360.209104</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>5759803875.0</t>
+          <t>9396894111.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>1689450518.2</v>
+        <v>3406595539.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>1272693479.4</t>
+          <t>2092972596.2</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>2149905312.46</v>
+        <v>2319670873.56</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>416757038</t>
+          <t>1313622943</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-169938558.8717777</t>
+          <t>-92608315.67016768</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-225925652.1964645</t>
+          <t>332708021.9386873</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>5759803875.0</t>
+          <t>9396894111.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-10.88</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>26.64</t>
+          <t>24.80</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>51.87</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>223327</t>
+          <t>218273</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>789.0</t>
+          <t>721.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>803.0</t>
+          <t>780.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>732.0</t>
+          <t>687.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>739.0</t>
+          <t>688.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1152.161</t>
+          <t>7500.722</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>739.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-6.08</t>
+          <t>-6.95</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-3.62</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-19.96</t>
+          <t>32.75</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>26.75</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>-7.70</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>188</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>3524</t>
+          <t>3517</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>68.25</t>
+          <t>50.79</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>31.22</t>
+          <t>39.68</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>732.4</t>
+          <t>731.2</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>708.6</v>
+        <v>715.55</v>
       </c>
       <c r="AN10" t="n">
-        <v>635.96</v>
+        <v>638.3</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>635.39</t>
+          <t>636.88</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-10.37</t>
+          <t>-12.52</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>34.32</t>
+          <t>32.48</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>38.29</t>
+          <t>37.13</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-52.59</t>
+          <t>-54.03</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>4933619914.912393</t>
+          <t>4931859360.209104</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>848806811.0</t>
+          <t>5759803875.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>688943827.4</v>
+        <v>1689450518.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>860708905.5</t>
+          <t>1272693479.4</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>2069337538.82</v>
+        <v>2149905312.46</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-171765078</t>
+          <t>416757038</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-159759087.3581983</t>
+          <t>-169938558.8717777</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-626216745.2396646</t>
+          <t>-225925652.1964645</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>848806811.0</t>
+          <t>5759803875.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4641,22 +4641,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>27.04</t>
+          <t>26.64</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>51.87</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>223327</t>
+          <t>218273</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>789.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>803.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>732.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>739.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>799.533</t>
+          <t>1152.161</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-8.54</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-3.62</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-58.59</t>
+          <t>-19.96</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-4.20</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-4.53</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>188</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>3524</t>
+          <t>3517</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>68.25</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>8.47</t>
+          <t>31.22</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>10.66</t>
+          <t>11.42</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>735.4</t>
+          <t>732.4</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>701.1</v>
+        <v>708.6</v>
       </c>
       <c r="AN11" t="n">
-        <v>633.54</v>
+        <v>635.96</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>634.25</t>
+          <t>635.39</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-10.78</t>
+          <t>-10.37</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>34.32</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>39.28</t>
+          <t>38.29</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-51.36</t>
+          <t>-52.59</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>4933619914.912393</t>
+          <t>4931859360.209104</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>573954733.0</t>
+          <t>848806811.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>627878031</v>
+        <v>688943827.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>1516353585.7</t>
+          <t>860708905.5</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>2106062606.14</v>
+        <v>2069337538.82</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-888475554</t>
+          <t>-171765078</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-74948604.10702263</t>
+          <t>-159759087.3581983</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-649518023.2571056</t>
+          <t>-626216745.2396646</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>573954733.0</t>
+          <t>848806811.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-8.42</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>25.49</t>
+          <t>27.04</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>51.87</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>223327</t>
+          <t>218273</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>740.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>740.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>617.266</t>
+          <t>799.533</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,72 +5198,72 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>707.0</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-2.32</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>-3.62</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>-58.59</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2025-11-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2025-09-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>785.0</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
           <t>738.0</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>-4.38</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>-1.86</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>-75.86</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2025-11-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2025-09-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>785.0</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>738.0</t>
-        </is>
-      </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>785.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
@@ -5278,12 +5278,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>-5.99</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>-4.53</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,17 +5314,17 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>188</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>3524</t>
+          <t>3517</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -5334,53 +5334,53 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>10.09</t>
+          <t>10.66</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>745.6</t>
+          <t>735.4</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>695.2</v>
+        <v>701.1</v>
       </c>
       <c r="AN12" t="n">
-        <v>631.48</v>
+        <v>633.54</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>633.66</t>
+          <t>634.25</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-10.78</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>35.05</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>40.34</t>
+          <t>39.28</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-50.05</t>
+          <t>-51.36</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,48 +5400,48 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>4933619914.912393</t>
+          <t>4931859360.209104</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>453518166.0</t>
+          <t>573954733.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>696124492.8</v>
+        <v>627878031</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>2883970531.7</t>
+          <t>1516353585.7</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>2126707687.18</v>
+        <v>2106062606.14</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-2147483648</t>
+          <t>-888475554</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>29518563.01117429</t>
+          <t>-74948604.10702263</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-630160054.0942674</t>
+          <t>-649518023.2571056</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>453518166.0</t>
+          <t>573954733.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-4.40</t>
+          <t>-8.42</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>26.60</t>
+          <t>25.49</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>51.87</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>223327</t>
+          <t>218273</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>737.0</t>
+          <t>740.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>739.0</t>
+          <t>740.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>730.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>738.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1237.634</t>
+          <t>1061.208</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-38.77</t>
+          <t>-37.75</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-14.62</t>
+          <t>-14.98</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5749,32 +5749,32 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>1238</t>
+          <t>1061</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>17.07</t>
+          <t>7.32</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>46.34</t>
+          <t>27.64</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-4.37</t>
+          <t>-3.49</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -5784,33 +5784,33 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>96.18</t>
+          <t>96.24</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>100.58</v>
+        <v>99.72</v>
       </c>
       <c r="AN13" t="n">
-        <v>101.32</v>
+        <v>101.18</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>103.42</t>
+          <t>103.27</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-19.71</t>
+          <t>-17.33</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-111.79</t>
+          <t>-112.33</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>1666790472.826923</t>
+          <t>1664635030.48293</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>119055310.0</t>
+          <t>101009670.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>166326125</v>
+        <v>157356209</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>271620933.8</t>
+          <t>252795469.6</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>421729365.34</v>
+        <v>419248618.68</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-105294808</t>
+          <t>-95439260</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-62667400.97133053</t>
+          <t>-66552338.9574316</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-87725677.7081908</t>
+          <t>-87919497.88098752</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>119055310.0</t>
+          <t>101009670.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-6.21</t>
+          <t>-6.60</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5931,17 +5931,17 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>31.52</t>
+          <t>31.39</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>26000</t>
+          <t>25891</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>96.8</t>
+          <t>95.8</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>97.7</t>
+          <t>96.1</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6033,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1934.14</t>
+          <t>1237.634</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>96.9</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-36.48</t>
+          <t>-38.77</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-13.09</t>
+          <t>-14.62</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6179,68 +6179,68 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>1238</t>
+          <t>1061</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>58.54</t>
+          <t>17.07</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>62.6</t>
+          <t>46.34</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-5.36</t>
+          <t>-4.37</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>96.18</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>101.64</v>
+        <v>100.58</v>
       </c>
       <c r="AN14" t="n">
-        <v>101.52</v>
+        <v>101.32</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>103.55</t>
+          <t>103.42</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-22.57</t>
+          <t>-19.71</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-111.21</t>
+          <t>-111.79</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>1666790472.826923</t>
+          <t>1664635030.48293</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>187058281.0</t>
+          <t>119055310.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>178982304.2</v>
+        <v>166326125</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>281758656.3</t>
+          <t>271620933.8</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>421804108.64</v>
+        <v>421729365.34</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-102776352</t>
+          <t>-105294808</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-58111350.65553775</t>
+          <t>-62667400.97133053</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-86249193.25747448</t>
+          <t>-87725677.7081908</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>187058281.0</t>
+          <t>119055310.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-4.53</t>
+          <t>-6.21</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6361,17 +6361,17 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>31.52</t>
+          <t>31.39</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>26000</t>
+          <t>25891</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>96.8</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>97.6</t>
+          <t>97.7</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>96.9</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2251.93</t>
+          <t>1934.14</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>97.1</t>
+          <t>96.9</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>-36.48</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-12.91</t>
+          <t>-13.09</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6609,68 +6609,68 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>1238</t>
+          <t>1061</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>63.41</t>
+          <t>58.54</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>43.09</t>
+          <t>62.6</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-6.32</t>
+          <t>-5.36</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>95.86</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>102.32</v>
+        <v>101.64</v>
       </c>
       <c r="AN15" t="n">
-        <v>101.67</v>
+        <v>101.52</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>103.67</t>
+          <t>103.55</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-34.44</t>
+          <t>-22.57</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-110.58</t>
+          <t>-111.21</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>1666790472.826923</t>
+          <t>1664635030.48293</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>219814205.0</t>
+          <t>187058281.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>284371450.4</v>
+        <v>178982304.2</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>299063636.4</t>
+          <t>281758656.3</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>422852603.5</v>
+        <v>421804108.64</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-14692186</t>
+          <t>-102776352</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-52995379.27336744</t>
+          <t>-58111350.65553775</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-88345634.03296983</t>
+          <t>-86249193.25747448</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>219814205.0</t>
+          <t>187058281.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-4.33</t>
+          <t>-4.53</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>31.52</t>
+          <t>31.39</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>26000</t>
+          <t>25891</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
+          <t>97.5</t>
+        </is>
+      </c>
+      <c r="CE15" t="inlineStr">
+        <is>
           <t>97.6</t>
         </is>
       </c>
-      <c r="CE15" t="inlineStr">
-        <is>
-          <t>98.6</t>
-        </is>
-      </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>96.7</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>97.1</t>
+          <t>96.9</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1654.541</t>
+          <t>2251.93</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>97.2</t>
+          <t>97.1</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-2.1</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-12.83</t>
+          <t>-12.91</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7039,68 +7039,68 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>1238</t>
+          <t>1061</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>65.85</t>
+          <t>63.41</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>22.48</t>
+          <t>43.09</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-6.18</t>
+          <t>-6.32</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>96.16</t>
+          <t>95.86</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>102.5</v>
+        <v>102.32</v>
       </c>
       <c r="AN16" t="n">
-        <v>101.88</v>
+        <v>101.67</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>103.75</t>
+          <t>103.67</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-52.73</t>
+          <t>-34.44</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-109.67</t>
+          <t>-110.58</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>1666790472.826923</t>
+          <t>1664635030.48293</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>159843579.0</t>
+          <t>219814205.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>323909709.6</v>
+        <v>284371450.4</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>303527778.0</t>
+          <t>299063636.4</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>427891465.06</v>
+        <v>422852603.5</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>20381931</t>
+          <t>-14692186</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-46568060.22616701</t>
+          <t>-52995379.27336744</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-91694911.4967857</t>
+          <t>-88345634.03296983</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>159843579.0</t>
+          <t>219814205.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-4.24</t>
+          <t>-4.33</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,12 +7221,12 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>31.52</t>
+          <t>31.39</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>26000</t>
+          <t>25891</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>97.6</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>97.2</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>96.7</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>97.2</t>
+          <t>97.1</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1536.151</t>
+          <t>1654.541</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>97.2</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>11.75</t>
+          <t>6.72</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-15.25</t>
+          <t>-12.83</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7469,68 +7469,68 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>1238</t>
+          <t>1061</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>65.85</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>22.48</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-6.60</t>
+          <t>-6.18</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>95.75999999999999</t>
+          <t>96.16</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>102.53</v>
+        <v>102.5</v>
       </c>
       <c r="AN17" t="n">
-        <v>102.08</v>
+        <v>101.88</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>103.82</t>
+          <t>103.75</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-82.43</t>
+          <t>-52.73</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-108.39</t>
+          <t>-109.67</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>1666790472.826923</t>
+          <t>1664635030.48293</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>145859250.0</t>
+          <t>159843579.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>348234730.2</v>
+        <v>323909709.6</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>311622176.9</t>
+          <t>303527778.0</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>429640696.94</v>
+        <v>427891465.06</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>36612553</t>
+          <t>20381931</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-38363178.1769636</t>
+          <t>-46568060.22616701</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-86779351.10592324</t>
+          <t>-91694911.4967857</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>145859250.0</t>
+          <t>159843579.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-6.90</t>
+          <t>-4.24</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,17 +7651,17 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>31.52</t>
+          <t>31.39</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>26000</t>
+          <t>25891</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>97.2</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>97.2</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1914.684</t>
+          <t>1536.151</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>95.3</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>16.80</t>
+          <t>11.75</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-14.53</t>
+          <t>-15.25</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7899,68 +7899,68 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>1238</t>
+          <t>1061</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>13.41</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-6.38</t>
+          <t>-6.60</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>96.12</t>
+          <t>95.75999999999999</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>102.68</v>
+        <v>102.53</v>
       </c>
       <c r="AN18" t="n">
-        <v>102.33</v>
+        <v>102.08</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>103.93</t>
+          <t>103.82</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-109.29</t>
+          <t>-82.43</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-106.66</t>
+          <t>-108.39</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1666790472.826923</t>
+          <t>1664635030.48293</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>182336206.0</t>
+          <t>145859250.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>376915742.6</v>
+        <v>348234730.2</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>322711393.4</t>
+          <t>311622176.9</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>429470961.98</v>
+        <v>429640696.94</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>54204349</t>
+          <t>36612553</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-29560237.64442549</t>
+          <t>-38363178.1769636</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-75159538.47233671</t>
+          <t>-86779351.10592324</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>182336206.0</t>
+          <t>145859250.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-6.11</t>
+          <t>-6.90</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,17 +8081,17 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>31.52</t>
+          <t>31.39</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>26000</t>
+          <t>25891</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>95.8</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>96.3</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>95.3</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-3.53</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>7327.598</t>
+          <t>1914.684</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>95.3</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>14.67</t>
+          <t>16.80</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-14.62</t>
+          <t>-14.53</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12.09</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-4.94</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8329,68 +8329,68 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>1238</t>
+          <t>1061</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>12.88</t>
+          <t>13.41</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-6.09</t>
+          <t>-6.38</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>96.56</t>
+          <t>96.12</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>102.82</v>
+        <v>102.68</v>
       </c>
       <c r="AN19" t="n">
-        <v>102.56</v>
+        <v>102.33</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>104.04</t>
+          <t>103.93</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-159.05</t>
+          <t>-109.29</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-104.84</t>
+          <t>-106.66</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>1666790472.826923</t>
+          <t>1664635030.48293</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>714004012.0</t>
+          <t>182336206.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>384535008.4</v>
+        <v>376915742.6</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>335344540.6</t>
+          <t>322711393.4</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>431976435.3</v>
+        <v>429470961.98</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>49190467</t>
+          <t>54204349</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-21269455.67571436</t>
+          <t>-29560237.64442549</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-59783782.19320107</t>
+          <t>-75159538.47233671</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>714004012.0</t>
+          <t>182336206.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-6.21</t>
+          <t>-6.11</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,17 +8511,17 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>31.52</t>
+          <t>31.39</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>26000</t>
+          <t>25891</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>95.8</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>96.6</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>95.1</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>95.3</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>-3.53</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>4255.671</t>
+          <t>7327.598</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-3.57</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>14.67</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-11.57</t>
+          <t>-14.62</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>7.02</t>
+          <t>12.09</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>-4.94</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8759,12 +8759,12 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>1238</t>
+          <t>1061</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>38.64</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
@@ -8774,53 +8774,53 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-5.63</t>
+          <t>-6.09</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>97.24000000000001</t>
+          <t>96.56</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>103.04</v>
+        <v>102.82</v>
       </c>
       <c r="AN20" t="n">
-        <v>102.79</v>
+        <v>102.56</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>104.13</t>
+          <t>104.04</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-260.17</t>
+          <t>-159.05</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-102.92</t>
+          <t>-104.84</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>1666790472.826923</t>
+          <t>1664635030.48293</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>417505501.0</t>
+          <t>714004012.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>313755822.4</v>
+        <v>384535008.4</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>306400241.3</t>
+          <t>335344540.6</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>420660383.62</v>
+        <v>431976435.3</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>7355581</t>
+          <t>49190467</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-14266850.85435314</t>
+          <t>-21269455.67571436</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-92647688.78753585</t>
+          <t>-59783782.19320107</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>417505501.0</t>
+          <t>714004012.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-2.86</t>
+          <t>-6.21</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8941,17 +8941,17 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>31.52</t>
+          <t>31.39</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>26000</t>
+          <t>25891</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,7 +9006,7 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>98.4</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>95.1</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2950.547</t>
+          <t>4255.671</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-19.47</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-14.62</t>
+          <t>-11.57</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>7.02</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9189,68 +9189,68 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>1238</t>
+          <t>1061</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>38.64</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.88</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-5.20</t>
+          <t>-5.63</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>97.82</t>
+          <t>97.24000000000001</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>103.19</v>
+        <v>103.04</v>
       </c>
       <c r="AN21" t="n">
-        <v>102.95</v>
+        <v>102.79</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>104.19</t>
+          <t>104.13</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-887.49</t>
+          <t>-260.17</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-101.02</t>
+          <t>-102.92</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>1666790472.826923</t>
+          <t>1664635030.48293</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>281468682.0</t>
+          <t>417505501.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>283145846.4</v>
+        <v>313755822.4</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>351622846.6</t>
+          <t>306400241.3</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>414970230.06</v>
+        <v>420660383.62</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-68477000</t>
+          <t>7355581</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-15789.41195628047</t>
+          <t>-14266850.85435314</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-104519583.1441735</t>
+          <t>-92647688.78753585</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>281468682.0</t>
+          <t>417505501.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-6.21</t>
+          <t>-2.86</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9381,7 +9381,7 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>31.52</t>
+          <t>31.39</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>26000</t>
+          <t>25891</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>98.4</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>97.9</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>94.1</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>3012.776</t>
+          <t>2950.547</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-37.86</t>
+          <t>-19.47</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-13.63</t>
+          <t>-14.62</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9619,7 +9619,7 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>1238</t>
+          <t>1061</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9634,53 +9634,53 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-5.20</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>99.08000000000001</t>
+          <t>97.82</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>103.5</v>
+        <v>103.19</v>
       </c>
       <c r="AN22" t="n">
-        <v>103.2</v>
+        <v>102.95</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>104.3</t>
+          <t>104.19</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-667.15</t>
+          <t>-887.49</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-98.76</t>
+          <t>-101.02</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>1666790472.826923</t>
+          <t>1664635030.48293</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>289264312.0</t>
+          <t>281468682.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>275009623.6</v>
+        <v>283145846.4</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>442557432.7</t>
+          <t>351622846.6</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>412480726.12</v>
+        <v>414970230.06</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-167547809</t>
+          <t>-68477000</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>18984900.35753776</t>
+          <t>-15789.41195628047</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-103171216.5056498</t>
+          <t>-104519583.1441735</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>289264312.0</t>
+          <t>281468682.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-5.12</t>
+          <t>-6.21</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>31.52</t>
+          <t>31.39</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>26000</t>
+          <t>25891</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>97.2</t>
+          <t>97.9</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>94.1</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2248.507</t>
+          <t>3012.776</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>96.3</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-53.51</t>
+          <t>-37.86</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-12.56</t>
+          <t>-13.63</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10049,7 +10049,7 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>1238</t>
+          <t>1061</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10064,12 +10064,12 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
@@ -10079,38 +10079,38 @@
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>100.42</t>
+          <t>99.08000000000001</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>103.72</v>
+        <v>103.5</v>
       </c>
       <c r="AN23" t="n">
-        <v>103.4</v>
+        <v>103.2</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>104.41</t>
+          <t>104.3</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-215.80</t>
+          <t>-667.15</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-96.68</t>
+          <t>-98.76</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>1666790472.826923</t>
+          <t>1664635030.48293</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>220432535.0</t>
+          <t>289264312.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>268507044.2</v>
+        <v>275009623.6</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>577618774.1</t>
+          <t>442557432.7</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>409190484.56</v>
+        <v>412480726.12</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-309111729</t>
+          <t>-167547809</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>41195103.42357187</t>
+          <t>18984900.35753776</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-98395538.21827114</t>
+          <t>-103171216.5056498</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>220432535.0</t>
+          <t>289264312.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-3.94</t>
+          <t>-5.12</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>4.40</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>31.52</t>
+          <t>31.39</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>26000</t>
+          <t>25891</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>99.2</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>97.2</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>97.2</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>96.3</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/配電系統.xlsx
+++ b/Result/checksun_type/配電系統.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>價_量;【c】</t>
+          <t>價_量;【c】;【x】看好</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3516.568</t>
+          <t>1813.678</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>691.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-21.29</t>
+          <t>-26.91</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-6.37</t>
+          <t>-4.34</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12.54</t>
+          <t>6.47</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>66</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>3517</t>
+          <t>1814</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>17.24</t>
+          <t>52.08</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>27.49</t>
+          <t>35.67</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-3.42</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>11.69</t>
+          <t>10.71</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>704.4</t>
+          <t>706.6</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>729.35</v>
+        <v>725.4</v>
       </c>
       <c r="AN2" t="n">
-        <v>653</v>
+        <v>655.24</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>641.5</t>
+          <t>641.96</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-49.29</t>
+          <t>-48.64</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>9.08</t>
+          <t>8.19</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>17.90</t>
+          <t>15.96</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-77.84</t>
+          <t>-80.24</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>4931859360.209104</t>
+          <t>4927555242.950284</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>2463966639.0</t>
+          <t>1267840540.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>2885411570</v>
+        <v>2709898314.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>3665902553.6</t>
+          <t>3707805926.5</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>2552773254.62</v>
+        <v>2561747225.36</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-780490983</t>
+          <t>-997907612</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>12333070.16765259</t>
+          <t>-17002146.65753568</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-51129304.35535431</t>
+          <t>-178345839.1960711</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>2463966639.0</t>
+          <t>1267840540.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-10.49</t>
+          <t>-8.55</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>24.91</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>41.31</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>218273</t>
+          <t>223011</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>711.0</t>
+          <t>703.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>718.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>691.0</t>
+          <t>692.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>691.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3523.66</t>
+          <t>3516.568</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>691.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-14.40</t>
+          <t>-21.29</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-4.20</t>
+          <t>-6.37</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>12.54</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>66</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>3517</t>
+          <t>1814</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>37.68</t>
+          <t>17.24</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>27.49</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-4.23</t>
+          <t>-3.42</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>12.69</t>
+          <t>11.69</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>702.4</t>
+          <t>704.4</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>733.4</v>
+        <v>729.35</v>
       </c>
       <c r="AN3" t="n">
-        <v>650.8200000000001</v>
+        <v>653</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>641.01</t>
+          <t>641.5</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-42.31</t>
+          <t>-49.29</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>11.60</t>
+          <t>9.08</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>20.10</t>
+          <t>17.90</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-75.11</t>
+          <t>-77.84</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>4931859360.209104</t>
+          <t>4927555242.950284</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>2526492754.0</t>
+          <t>2463966639.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>2976124482.6</v>
+        <v>2885411570</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>3476901363.0</t>
+          <t>3665902553.6</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>2522196255.28</v>
+        <v>2552773254.62</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-500776880</t>
+          <t>-780490983</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>23871683.71729021</t>
+          <t>12333070.16765259</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>4278281.394074917</t>
+          <t>-51129304.35535431</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>2526492754.0</t>
+          <t>2463966639.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-8.42</t>
+          <t>-10.49</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>25.49</t>
+          <t>24.91</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>41.31</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>218273</t>
+          <t>223011</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>717.0</t>
+          <t>711.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>727.0</t>
+          <t>718.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>691.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>691.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4456.494</t>
+          <t>3523.66</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>700.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>-14.40</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-5.15</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15.89</t>
+          <t>12.57</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-5.14</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>66</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>3517</t>
+          <t>1814</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>27.54</t>
+          <t>37.68</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>39.13</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-4.23</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>12.69</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>702.2</t>
+          <t>702.4</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>737.35</v>
+        <v>733.4</v>
       </c>
       <c r="AN4" t="n">
-        <v>648.52</v>
+        <v>650.8200000000001</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>640.28</t>
+          <t>641.01</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-41.44</t>
+          <t>-42.31</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>13.01</t>
+          <t>11.60</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>22.23</t>
+          <t>20.10</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-72.48</t>
+          <t>-75.11</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>4931859360.209104</t>
+          <t>4927555242.950284</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>3163492460.0</t>
+          <t>2526492754.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>3132612269.2</v>
+        <v>2976124482.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>3269603904.2</t>
+          <t>3476901363.0</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>2494838192.4</v>
+        <v>2522196255.28</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-136991635</t>
+          <t>-500776880</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>27434120.50332935</t>
+          <t>23871683.71729021</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>76579952.95061398</t>
+          <t>4278281.394074917</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>3163492460.0</t>
+          <t>2526492754.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-9.33</t>
+          <t>-8.42</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,12 +2071,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>25.23</t>
+          <t>25.49</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>41.31</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>218273</t>
+          <t>223011</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>738.0</t>
+          <t>717.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>738.0</t>
+          <t>727.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>698.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>700.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5678.126</t>
+          <t>4456.494</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>700.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-5.5</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>44.32</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-5.15</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>15.89</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>-5.14</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>66</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>3517</t>
+          <t>1814</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>69.57</t>
+          <t>27.54</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>29.95</t>
+          <t>39.13</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-5.19</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>14.16</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>699.8</t>
+          <t>702.2</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>738.1</v>
+        <v>737.35</v>
       </c>
       <c r="AN5" t="n">
-        <v>646.54</v>
+        <v>648.52</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>639.58</t>
+          <t>640.28</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-37.42</t>
+          <t>-41.44</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>15.35</t>
+          <t>13.01</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>24.53</t>
+          <t>22.23</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-69.62</t>
+          <t>-72.48</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>4931859360.209104</t>
+          <t>4927555242.950284</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>4127699179.0</t>
+          <t>3163492460.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>4379292599.4</v>
+        <v>3132612269.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>3034371558.8</t>
+          <t>3269603904.2</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>2446536212.66</v>
+        <v>2494838192.4</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>1344921040</t>
+          <t>-136991635</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>18498514.60382305</t>
+          <t>27434120.50332935</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>108883088.3545771</t>
+          <t>76579952.95061398</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>4127699179.0</t>
+          <t>3163492460.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-5.57</t>
+          <t>-9.33</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>26.28</t>
+          <t>25.23</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>41.31</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>218273</t>
+          <t>223011</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>704.0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>743.0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>704.0</t>
+          <t>698.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>700.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3102.28</t>
+          <t>5678.126</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>695.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>74.46</t>
+          <t>44.32</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11.06</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>66</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>3517</t>
+          <t>1814</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>20.29</t>
+          <t>69.57</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>14.56</t>
+          <t>29.95</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-5.19</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>13.98</t>
+          <t>14.16</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>701.8</t>
+          <t>699.8</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>734.15</v>
+        <v>738.1</v>
       </c>
       <c r="AN6" t="n">
-        <v>644.12</v>
+        <v>646.54</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>638.67</t>
+          <t>639.58</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-43.51</t>
+          <t>-37.42</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>15.15</t>
+          <t>15.35</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>26.82</t>
+          <t>24.53</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-66.78</t>
+          <t>-69.62</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>4931859360.209104</t>
+          <t>4927555242.950284</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>2145406818.0</t>
+          <t>4127699179.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>4705713538.6</v>
+        <v>4379292599.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>2697328683.0</t>
+          <t>3034371558.8</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>2381458909.08</v>
+        <v>2446536212.66</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>2008384855</t>
+          <t>1344921040</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>2064955.740049592</t>
+          <t>18498514.60382305</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>47833880.16900253</t>
+          <t>108883088.3545771</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>2145406818.0</t>
+          <t>4127699179.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-9.97</t>
+          <t>-5.57</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>26.28</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>41.31</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>218273</t>
+          <t>223011</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>689.0</t>
+          <t>704.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
+          <t>743.0</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
           <t>704.0</t>
         </is>
       </c>
-      <c r="CF6" t="inlineStr">
-        <is>
-          <t>677.0</t>
-        </is>
-      </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>695.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4210.877</t>
+          <t>3102.28</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>681.0</t>
+          <t>695.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>75.25</t>
+          <t>74.46</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-7.72</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15.02</t>
+          <t>11.06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-5.28</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>66</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>3517</t>
+          <t>1814</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.29</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>14.56</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-4.46</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-2.30</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>13.59</t>
+          <t>13.98</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>712.8</t>
+          <t>701.8</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>729.6</v>
+        <v>734.15</v>
       </c>
       <c r="AN7" t="n">
-        <v>642.3200000000001</v>
+        <v>644.12</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>638.33</t>
+          <t>638.67</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-38.99</t>
+          <t>-43.51</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>15.15</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>29.74</t>
+          <t>26.82</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-63.17</t>
+          <t>-66.78</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>4931859360.209104</t>
+          <t>4927555242.950284</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>2917531202.0</t>
+          <t>2145406818.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>4446393537.2</v>
+        <v>4705713538.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>2537135784.1</t>
+          <t>2697328683.0</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>2394527724.36</v>
+        <v>2381458909.08</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>1909257753</t>
+          <t>2008384855</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-6256666.883396398</t>
+          <t>2064955.740049592</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>171300840.0050039</t>
+          <t>47833880.16900253</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>2917531202.0</t>
+          <t>2145406818.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-11.79</t>
+          <t>-9.97</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3356,17 +3356,17 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>41.31</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>218273</t>
+          <t>223011</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>720.0</t>
+          <t>689.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>721.0</t>
+          <t>704.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>681.0</t>
+          <t>695.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4656.178</t>
+          <t>4210.877</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>681.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>70.21</t>
+          <t>75.25</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>-7.72</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16.60</t>
+          <t>15.02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-5.28</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>66</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>3517</t>
+          <t>1814</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-4.46</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-2.30</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>13.59</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>718.0</t>
+          <t>712.8</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>726.45</v>
+        <v>729.6</v>
       </c>
       <c r="AN8" t="n">
-        <v>641.1799999999999</v>
+        <v>642.3200000000001</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>638.1</t>
+          <t>638.33</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-29.15</t>
+          <t>-38.99</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>23.12</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>32.64</t>
+          <t>29.74</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-59.58</t>
+          <t>-63.17</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>4931859360.209104</t>
+          <t>4927555242.950284</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>3308931687.0</t>
+          <t>2917531202.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>3977678243.4</v>
+        <v>4446393537.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>2336901368.1</t>
+          <t>2537135784.1</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>2356977274.04</v>
+        <v>2394527724.36</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>1640776875</t>
+          <t>1909257753</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-38539849.95401464</t>
+          <t>-6256666.883396398</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>258836711.484827</t>
+          <t>171300840.0050039</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>3308931687.0</t>
+          <t>2917531202.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-8.55</t>
+          <t>-11.79</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3786,17 +3786,17 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>41.31</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>218273</t>
+          <t>223011</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>701.0</t>
+          <t>720.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>721.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>698.0</t>
+          <t>677.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>681.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-7.07</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>12908.308</t>
+          <t>4656.178</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>688.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>62.76</t>
+          <t>70.21</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-6.78</t>
+          <t>-4.34</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>46.03</t>
+          <t>16.60</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-13.23</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>66</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>3517</t>
+          <t>1814</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>39.68</t>
+          <t>24.72</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-5.02</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>12.71</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>724.4</t>
+          <t>718.0</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>720.75</v>
+        <v>726.45</v>
       </c>
       <c r="AN9" t="n">
-        <v>639.48</v>
+        <v>641.1799999999999</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>637.48</t>
+          <t>638.1</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-24.05</t>
+          <t>-29.15</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>26.60</t>
+          <t>23.12</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>35.02</t>
+          <t>32.64</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-56.63</t>
+          <t>-59.58</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>4931859360.209104</t>
+          <t>4927555242.950284</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>9396894111.0</t>
+          <t>3308931687.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>3406595539.2</v>
+        <v>3977678243.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2092972596.2</t>
+          <t>2336901368.1</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>2319670873.56</v>
+        <v>2356977274.04</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>1313622943</t>
+          <t>1640776875</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-92608315.67016768</t>
+          <t>-38539849.95401464</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>332708021.9386873</t>
+          <t>258836711.484827</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>9396894111.0</t>
+          <t>3308931687.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-10.88</t>
+          <t>-8.55</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>24.80</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>41.31</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>218273</t>
+          <t>223011</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>721.0</t>
+          <t>701.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>780.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>687.0</t>
+          <t>698.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>688.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-7.07</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>7500.722</t>
+          <t>12908.308</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>739.0</t>
+          <t>688.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-6.95</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>32.75</t>
+          <t>62.76</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-6.78</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>26.75</t>
+          <t>46.03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-7.70</t>
+          <t>-13.23</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,17 +4454,17 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>66</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>3517</t>
+          <t>1814</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>50.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -4474,53 +4474,53 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>-5.02</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>12.71</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>731.2</t>
+          <t>724.4</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>715.55</v>
+        <v>720.75</v>
       </c>
       <c r="AN10" t="n">
-        <v>638.3</v>
+        <v>639.48</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>636.88</t>
+          <t>637.48</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-12.52</t>
+          <t>-24.05</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>32.48</t>
+          <t>26.60</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>37.13</t>
+          <t>35.02</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-54.03</t>
+          <t>-56.63</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>4931859360.209104</t>
+          <t>4927555242.950284</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>5759803875.0</t>
+          <t>9396894111.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>1689450518.2</v>
+        <v>3406595539.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>1272693479.4</t>
+          <t>2092972596.2</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>2149905312.46</v>
+        <v>2319670873.56</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>416757038</t>
+          <t>1313622943</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-169938558.8717777</t>
+          <t>-92608315.67016768</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-225925652.1964645</t>
+          <t>332708021.9386873</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>5759803875.0</t>
+          <t>9396894111.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-10.88</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>26.64</t>
+          <t>24.80</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>41.31</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>218273</t>
+          <t>223011</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>789.0</t>
+          <t>721.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>803.0</t>
+          <t>780.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>732.0</t>
+          <t>687.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>739.0</t>
+          <t>688.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1152.161</t>
+          <t>7500.722</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>739.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-8.54</t>
+          <t>-4.67</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-19.96</t>
+          <t>32.75</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>26.75</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>-7.70</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>66</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>3517</t>
+          <t>1814</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>68.25</t>
+          <t>50.79</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>31.22</t>
+          <t>39.68</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>732.4</t>
+          <t>731.2</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>708.6</v>
+        <v>715.55</v>
       </c>
       <c r="AN11" t="n">
-        <v>635.96</v>
+        <v>638.3</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>635.39</t>
+          <t>636.88</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-10.37</t>
+          <t>-12.52</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>34.32</t>
+          <t>32.48</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>38.29</t>
+          <t>37.13</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-52.59</t>
+          <t>-54.03</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>4931859360.209104</t>
+          <t>4927555242.950284</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>848806811.0</t>
+          <t>5759803875.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>688943827.4</v>
+        <v>1689450518.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>860708905.5</t>
+          <t>1272693479.4</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>2069337538.82</v>
+        <v>2149905312.46</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-171765078</t>
+          <t>416757038</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-159759087.3581983</t>
+          <t>-169938558.8717777</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-626216745.2396646</t>
+          <t>-225925652.1964645</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>848806811.0</t>
+          <t>5759803875.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>27.04</t>
+          <t>26.64</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>41.31</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>218273</t>
+          <t>223011</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>789.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>803.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>732.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>739.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>799.533</t>
+          <t>1152.161</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>-6.23</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-58.59</t>
+          <t>-19.96</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-4.20</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-4.53</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>66</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>3517</t>
+          <t>1814</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>68.25</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>8.47</t>
+          <t>31.22</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>10.66</t>
+          <t>11.42</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>735.4</t>
+          <t>732.4</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>701.1</v>
+        <v>708.6</v>
       </c>
       <c r="AN12" t="n">
-        <v>633.54</v>
+        <v>635.96</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>634.25</t>
+          <t>635.39</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-10.78</t>
+          <t>-10.37</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>34.32</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>39.28</t>
+          <t>38.29</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-51.36</t>
+          <t>-52.59</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>4931859360.209104</t>
+          <t>4927555242.950284</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>573954733.0</t>
+          <t>848806811.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>627878031</v>
+        <v>688943827.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>1516353585.7</t>
+          <t>860708905.5</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>2106062606.14</v>
+        <v>2069337538.82</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-888475554</t>
+          <t>-171765078</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-74948604.10702263</t>
+          <t>-159759087.3581983</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-649518023.2571056</t>
+          <t>-626216745.2396646</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>573954733.0</t>
+          <t>848806811.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-8.42</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>25.49</t>
+          <t>27.04</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>41.31</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>218273</t>
+          <t>223011</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>740.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>740.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1061.208</t>
+          <t>792.387</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>95.1</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-37.75</t>
+          <t>-39.51</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-14.98</t>
+          <t>-14.71</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,73 +5744,73 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t>792</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>7.32</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>27.64</t>
+          <t>15.54</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-3.49</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>96.24</t>
+          <t>95.82</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>99.72</v>
+        <v>98.68000000000001</v>
       </c>
       <c r="AN13" t="n">
-        <v>101.18</v>
+        <v>101.03</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>103.27</t>
+          <t>103.1</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-17.33</t>
+          <t>-13.08</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-112.33</t>
+          <t>-112.74</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>1664635030.48293</t>
+          <t>1662430966.46804</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>101009670.0</t>
+          <t>75315976.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>157356209</v>
+        <v>140450688.4</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>252795469.6</t>
+          <t>232180199.0</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>419248618.68</v>
+        <v>418404115.58</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-95439260</t>
+          <t>-91729510</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-66552338.9574316</t>
+          <t>-69818780.90319912</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-87919497.88098752</t>
+          <t>-87784211.6049205</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>101009670.0</t>
+          <t>75315976.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-6.60</t>
+          <t>-6.31</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5941,7 +5941,7 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>31.39</t>
+          <t>31.49</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>41.31</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>25891</t>
+          <t>25973</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
+          <t>95.7</t>
+        </is>
+      </c>
+      <c r="CE13" t="inlineStr">
+        <is>
           <t>95.8</t>
         </is>
       </c>
-      <c r="CE13" t="inlineStr">
-        <is>
-          <t>96.1</t>
-        </is>
-      </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>95.1</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1237.634</t>
+          <t>1061.208</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-38.77</t>
+          <t>-37.75</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-14.62</t>
+          <t>-14.98</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,37 +6174,37 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t>792</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>17.07</t>
+          <t>7.32</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>46.34</t>
+          <t>27.64</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-4.37</t>
+          <t>-3.49</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
@@ -6214,33 +6214,33 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>96.18</t>
+          <t>96.24</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>100.58</v>
+        <v>99.72</v>
       </c>
       <c r="AN14" t="n">
-        <v>101.32</v>
+        <v>101.18</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>103.42</t>
+          <t>103.27</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-19.71</t>
+          <t>-17.33</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-111.79</t>
+          <t>-112.33</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>1664635030.48293</t>
+          <t>1662430966.46804</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>119055310.0</t>
+          <t>101009670.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>166326125</v>
+        <v>157356209</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>271620933.8</t>
+          <t>252795469.6</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>421729365.34</v>
+        <v>419248618.68</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-105294808</t>
+          <t>-95439260</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-62667400.97133053</t>
+          <t>-66552338.9574316</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-87725677.7081908</t>
+          <t>-87919497.88098752</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>119055310.0</t>
+          <t>101009670.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-6.21</t>
+          <t>-6.60</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
@@ -6361,17 +6361,17 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>31.39</t>
+          <t>31.49</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>41.31</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>25891</t>
+          <t>25973</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>96.8</t>
+          <t>95.8</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>97.7</t>
+          <t>96.1</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6463,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1934.14</t>
+          <t>1237.634</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>96.9</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-36.48</t>
+          <t>-38.77</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-13.09</t>
+          <t>-14.62</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,73 +6604,73 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t>792</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>58.54</t>
+          <t>17.07</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>62.6</t>
+          <t>46.34</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-5.36</t>
+          <t>-4.37</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>96.18</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>101.64</v>
+        <v>100.58</v>
       </c>
       <c r="AN15" t="n">
-        <v>101.52</v>
+        <v>101.32</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>103.55</t>
+          <t>103.42</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-22.57</t>
+          <t>-19.71</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-111.21</t>
+          <t>-111.79</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>1664635030.48293</t>
+          <t>1662430966.46804</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>187058281.0</t>
+          <t>119055310.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>178982304.2</v>
+        <v>166326125</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>281758656.3</t>
+          <t>271620933.8</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>421804108.64</v>
+        <v>421729365.34</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-102776352</t>
+          <t>-105294808</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-58111350.65553775</t>
+          <t>-62667400.97133053</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-86249193.25747448</t>
+          <t>-87725677.7081908</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>187058281.0</t>
+          <t>119055310.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-4.53</t>
+          <t>-6.21</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
@@ -6791,17 +6791,17 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>31.39</t>
+          <t>31.49</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>41.31</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>25891</t>
+          <t>25973</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>96.8</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>97.6</t>
+          <t>97.7</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>96.9</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2251.93</t>
+          <t>1934.14</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>97.1</t>
+          <t>96.9</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>-36.48</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-12.91</t>
+          <t>-13.09</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,73 +7034,73 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t>792</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>63.41</t>
+          <t>58.54</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>43.09</t>
+          <t>62.6</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-6.32</t>
+          <t>-5.36</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>95.86</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>102.32</v>
+        <v>101.64</v>
       </c>
       <c r="AN16" t="n">
-        <v>101.67</v>
+        <v>101.52</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>103.67</t>
+          <t>103.55</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-34.44</t>
+          <t>-22.57</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-110.58</t>
+          <t>-111.21</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>1664635030.48293</t>
+          <t>1662430966.46804</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>219814205.0</t>
+          <t>187058281.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>284371450.4</v>
+        <v>178982304.2</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>299063636.4</t>
+          <t>281758656.3</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>422852603.5</v>
+        <v>421804108.64</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-14692186</t>
+          <t>-102776352</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-52995379.27336744</t>
+          <t>-58111350.65553775</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-88345634.03296983</t>
+          <t>-86249193.25747448</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>219814205.0</t>
+          <t>187058281.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-4.33</t>
+          <t>-4.53</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7201,7 +7201,7 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>31.39</t>
+          <t>31.49</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>41.31</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>25891</t>
+          <t>25973</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
+          <t>97.5</t>
+        </is>
+      </c>
+      <c r="CE16" t="inlineStr">
+        <is>
           <t>97.6</t>
         </is>
       </c>
-      <c r="CE16" t="inlineStr">
-        <is>
-          <t>98.6</t>
-        </is>
-      </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>96.7</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>97.1</t>
+          <t>96.9</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1654.541</t>
+          <t>2251.93</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>97.2</t>
+          <t>97.1</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-2.1</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-12.83</t>
+          <t>-12.91</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,73 +7464,73 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t>792</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>65.85</t>
+          <t>63.41</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>22.48</t>
+          <t>43.09</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-6.18</t>
+          <t>-6.32</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>96.16</t>
+          <t>95.86</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>102.5</v>
+        <v>102.32</v>
       </c>
       <c r="AN17" t="n">
-        <v>101.88</v>
+        <v>101.67</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>103.75</t>
+          <t>103.67</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-52.73</t>
+          <t>-34.44</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-109.67</t>
+          <t>-110.58</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>1664635030.48293</t>
+          <t>1662430966.46804</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>159843579.0</t>
+          <t>219814205.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>323909709.6</v>
+        <v>284371450.4</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>303527778.0</t>
+          <t>299063636.4</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>427891465.06</v>
+        <v>422852603.5</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>20381931</t>
+          <t>-14692186</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-46568060.22616701</t>
+          <t>-52995379.27336744</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-91694911.4967857</t>
+          <t>-88345634.03296983</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>159843579.0</t>
+          <t>219814205.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-4.24</t>
+          <t>-4.33</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>31.39</t>
+          <t>31.49</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>41.31</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>25891</t>
+          <t>25973</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>97.6</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>97.2</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>96.7</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>97.2</t>
+          <t>97.1</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1536.151</t>
+          <t>1654.541</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>97.2</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>11.75</t>
+          <t>6.72</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-15.25</t>
+          <t>-12.83</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,73 +7894,73 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t>792</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>65.85</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>22.48</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-6.60</t>
+          <t>-6.18</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>95.75999999999999</t>
+          <t>96.16</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>102.53</v>
+        <v>102.5</v>
       </c>
       <c r="AN18" t="n">
-        <v>102.08</v>
+        <v>101.88</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>103.82</t>
+          <t>103.75</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-82.43</t>
+          <t>-52.73</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-108.39</t>
+          <t>-109.67</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1664635030.48293</t>
+          <t>1662430966.46804</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>145859250.0</t>
+          <t>159843579.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>348234730.2</v>
+        <v>323909709.6</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>311622176.9</t>
+          <t>303527778.0</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>429640696.94</v>
+        <v>427891465.06</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>36612553</t>
+          <t>20381931</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-38363178.1769636</t>
+          <t>-46568060.22616701</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-86779351.10592324</t>
+          <t>-91694911.4967857</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>145859250.0</t>
+          <t>159843579.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-6.90</t>
+          <t>-4.24</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
@@ -8081,17 +8081,17 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>31.39</t>
+          <t>31.49</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>41.31</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>25891</t>
+          <t>25973</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>97.2</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>97.2</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1914.684</t>
+          <t>1536.151</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>95.3</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>16.80</t>
+          <t>11.75</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-14.53</t>
+          <t>-15.25</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,73 +8324,73 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t>792</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>13.41</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-6.38</t>
+          <t>-6.60</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>96.12</t>
+          <t>95.75999999999999</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>102.68</v>
+        <v>102.53</v>
       </c>
       <c r="AN19" t="n">
-        <v>102.33</v>
+        <v>102.08</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>103.93</t>
+          <t>103.82</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-109.29</t>
+          <t>-82.43</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-106.66</t>
+          <t>-108.39</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>1664635030.48293</t>
+          <t>1662430966.46804</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>182336206.0</t>
+          <t>145859250.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>376915742.6</v>
+        <v>348234730.2</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>322711393.4</t>
+          <t>311622176.9</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>429470961.98</v>
+        <v>429640696.94</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>54204349</t>
+          <t>36612553</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-29560237.64442549</t>
+          <t>-38363178.1769636</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-75159538.47233671</t>
+          <t>-86779351.10592324</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>182336206.0</t>
+          <t>145859250.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-6.11</t>
+          <t>-6.90</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
@@ -8511,17 +8511,17 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>31.39</t>
+          <t>31.49</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>41.31</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>25891</t>
+          <t>25973</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>95.8</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>96.3</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>95.3</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-3.53</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>7327.598</t>
+          <t>1914.684</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>95.3</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>14.67</t>
+          <t>16.80</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-14.62</t>
+          <t>-14.53</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12.09</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-4.94</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,73 +8754,73 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t>792</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>12.88</t>
+          <t>13.41</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-6.09</t>
+          <t>-6.38</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>96.56</t>
+          <t>96.12</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>102.82</v>
+        <v>102.68</v>
       </c>
       <c r="AN20" t="n">
-        <v>102.56</v>
+        <v>102.33</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>104.04</t>
+          <t>103.93</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-159.05</t>
+          <t>-109.29</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-104.84</t>
+          <t>-106.66</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>1664635030.48293</t>
+          <t>1662430966.46804</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>714004012.0</t>
+          <t>182336206.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>384535008.4</v>
+        <v>376915742.6</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>335344540.6</t>
+          <t>322711393.4</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>431976435.3</v>
+        <v>429470961.98</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>49190467</t>
+          <t>54204349</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-21269455.67571436</t>
+          <t>-29560237.64442549</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-59783782.19320107</t>
+          <t>-75159538.47233671</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>714004012.0</t>
+          <t>182336206.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-6.21</t>
+          <t>-6.11</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
@@ -8941,17 +8941,17 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>31.39</t>
+          <t>31.49</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>41.31</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>25891</t>
+          <t>25973</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>95.8</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>96.6</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>95.1</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>95.3</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>-3.53</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>4255.671</t>
+          <t>7327.598</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>14.67</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-11.57</t>
+          <t>-14.62</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>7.02</t>
+          <t>12.09</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>-4.94</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,17 +9184,17 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t>792</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>38.64</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
@@ -9204,53 +9204,53 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-5.63</t>
+          <t>-6.09</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>97.24000000000001</t>
+          <t>96.56</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>103.04</v>
+        <v>102.82</v>
       </c>
       <c r="AN21" t="n">
-        <v>102.79</v>
+        <v>102.56</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>104.13</t>
+          <t>104.04</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-260.17</t>
+          <t>-159.05</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-102.92</t>
+          <t>-104.84</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>1664635030.48293</t>
+          <t>1662430966.46804</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>417505501.0</t>
+          <t>714004012.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>313755822.4</v>
+        <v>384535008.4</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>306400241.3</t>
+          <t>335344540.6</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>420660383.62</v>
+        <v>431976435.3</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>7355581</t>
+          <t>49190467</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-14266850.85435314</t>
+          <t>-21269455.67571436</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-92647688.78753585</t>
+          <t>-59783782.19320107</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>417505501.0</t>
+          <t>714004012.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-2.86</t>
+          <t>-6.21</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9381,7 +9381,7 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>31.39</t>
+          <t>31.49</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>41.31</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>25891</t>
+          <t>25973</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,7 +9436,7 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>98.4</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>95.1</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2950.547</t>
+          <t>4255.671</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-3.68</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-19.47</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-14.62</t>
+          <t>-11.57</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>7.02</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,73 +9614,73 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t>792</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>38.64</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.88</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-5.20</t>
+          <t>-5.63</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>97.82</t>
+          <t>97.24000000000001</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>103.19</v>
+        <v>103.04</v>
       </c>
       <c r="AN22" t="n">
-        <v>102.95</v>
+        <v>102.79</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>104.19</t>
+          <t>104.13</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-887.49</t>
+          <t>-260.17</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-101.02</t>
+          <t>-102.92</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>1664635030.48293</t>
+          <t>1662430966.46804</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>281468682.0</t>
+          <t>417505501.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>283145846.4</v>
+        <v>313755822.4</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>351622846.6</t>
+          <t>306400241.3</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>414970230.06</v>
+        <v>420660383.62</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-68477000</t>
+          <t>7355581</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-15789.41195628047</t>
+          <t>-14266850.85435314</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-104519583.1441735</t>
+          <t>-92647688.78753585</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>281468682.0</t>
+          <t>417505501.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-6.21</t>
+          <t>-2.86</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9781,7 +9781,7 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>31.39</t>
+          <t>31.49</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>41.31</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>25891</t>
+          <t>25973</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>98.4</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>97.9</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>94.1</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>3012.776</t>
+          <t>2950.547</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-37.86</t>
+          <t>-19.47</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-13.63</t>
+          <t>-14.62</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,12 +10044,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t>792</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10064,53 +10064,53 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-5.20</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>99.08000000000001</t>
+          <t>97.82</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>103.5</v>
+        <v>103.19</v>
       </c>
       <c r="AN23" t="n">
-        <v>103.2</v>
+        <v>102.95</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>104.3</t>
+          <t>104.19</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-667.15</t>
+          <t>-887.49</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-98.76</t>
+          <t>-101.02</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>1664635030.48293</t>
+          <t>1662430966.46804</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>289264312.0</t>
+          <t>281468682.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>275009623.6</v>
+        <v>283145846.4</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>442557432.7</t>
+          <t>351622846.6</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>412480726.12</v>
+        <v>414970230.06</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-167547809</t>
+          <t>-68477000</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>18984900.35753776</t>
+          <t>-15789.41195628047</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-103171216.5056498</t>
+          <t>-104519583.1441735</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>289264312.0</t>
+          <t>281468682.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-5.12</t>
+          <t>-6.21</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10211,7 +10211,7 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>31.39</t>
+          <t>31.49</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>41.31</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>25891</t>
+          <t>25973</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>97.2</t>
+          <t>97.9</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>94.1</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/配電系統.xlsx
+++ b/Result/checksun_type/配電系統.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>價_量;【c】;【x】看好</t>
+          <t>【c】;【x】看好</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1813.678</t>
+          <t>2409.738</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>711.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-26.91</t>
+          <t>-32.61</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>6.47</t>
+          <t>8.59</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1814</t>
+          <t>2410</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>52.08</t>
+          <t>62.5</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>35.67</t>
+          <t>43.94</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>10.71</t>
+          <t>9.89</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>706.6</t>
+          <t>703.0</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>725.4</v>
+        <v>722.7</v>
       </c>
       <c r="AN2" t="n">
-        <v>655.24</v>
+        <v>657.66</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>641.96</t>
+          <t>642.4</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-48.64</t>
+          <t>-45.49</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>8.19</t>
+          <t>7.81</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>15.96</t>
+          <t>14.33</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-80.24</t>
+          <t>-82.26</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>4927555242.950284</t>
+          <t>4924195625.746809</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>1267840540.0</t>
+          <t>1706016743.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>2709898314.4</v>
+        <v>2225561827.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>3707805926.5</t>
+          <t>3302427213.3</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>2561747225.36</v>
+        <v>2578743388.1</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-997907612</t>
+          <t>-1076865386</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-17002146.65753568</t>
+          <t>-49782670.61478729</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-178345839.1960711</t>
+          <t>-230075552.3796711</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>1267840540.0</t>
+          <t>1706016743.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-8.55</t>
+          <t>-7.90</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>25.63</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>52.16</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>41.31</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>223011</t>
+          <t>224591</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>703.0</t>
+          <t>705.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>715.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>692.0</t>
+          <t>694.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>711.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3516.568</t>
+          <t>1813.678</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>691.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-21.29</t>
+          <t>-26.91</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-6.37</t>
+          <t>-4.34</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12.54</t>
+          <t>6.47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1814</t>
+          <t>2410</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>17.24</t>
+          <t>52.08</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>27.49</t>
+          <t>35.67</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-3.42</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>11.69</t>
+          <t>10.71</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>704.4</t>
+          <t>706.6</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>729.35</v>
+        <v>725.4</v>
       </c>
       <c r="AN3" t="n">
-        <v>653</v>
+        <v>655.24</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>641.5</t>
+          <t>641.96</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-49.29</t>
+          <t>-48.64</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>9.08</t>
+          <t>8.19</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>17.90</t>
+          <t>15.96</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-77.84</t>
+          <t>-80.24</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>4927555242.950284</t>
+          <t>4924195625.746809</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>2463966639.0</t>
+          <t>1267840540.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>2885411570</v>
+        <v>2709898314.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>3665902553.6</t>
+          <t>3707805926.5</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>2552773254.62</v>
+        <v>2561747225.36</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-780490983</t>
+          <t>-997907612</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>12333070.16765259</t>
+          <t>-17002146.65753568</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-51129304.35535431</t>
+          <t>-178345839.1960711</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>2463966639.0</t>
+          <t>1267840540.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-10.49</t>
+          <t>-8.55</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>24.91</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>52.16</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>41.31</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>223011</t>
+          <t>224591</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>711.0</t>
+          <t>703.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>718.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>691.0</t>
+          <t>692.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>691.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3523.66</t>
+          <t>3516.568</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>691.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-14.40</t>
+          <t>-21.29</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-4.20</t>
+          <t>-6.37</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>12.54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1814</t>
+          <t>2410</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>37.68</t>
+          <t>17.24</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>27.49</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-4.23</t>
+          <t>-3.42</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>12.69</t>
+          <t>11.69</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>702.4</t>
+          <t>704.4</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>733.4</v>
+        <v>729.35</v>
       </c>
       <c r="AN4" t="n">
-        <v>650.8200000000001</v>
+        <v>653</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>641.01</t>
+          <t>641.5</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-42.31</t>
+          <t>-49.29</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>11.60</t>
+          <t>9.08</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>20.10</t>
+          <t>17.90</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-75.11</t>
+          <t>-77.84</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>4927555242.950284</t>
+          <t>4924195625.746809</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>2526492754.0</t>
+          <t>2463966639.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>2976124482.6</v>
+        <v>2885411570</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>3476901363.0</t>
+          <t>3665902553.6</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>2522196255.28</v>
+        <v>2552773254.62</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-500776880</t>
+          <t>-780490983</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>23871683.71729021</t>
+          <t>12333070.16765259</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>4278281.394074917</t>
+          <t>-51129304.35535431</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>2526492754.0</t>
+          <t>2463966639.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-8.42</t>
+          <t>-10.49</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>25.49</t>
+          <t>24.91</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>52.16</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>41.31</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>223011</t>
+          <t>224591</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>717.0</t>
+          <t>711.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>727.0</t>
+          <t>718.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>691.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>691.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4456.494</t>
+          <t>3523.66</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>700.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>-14.40</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-5.15</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15.89</t>
+          <t>12.57</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-5.14</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1814</t>
+          <t>2410</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>27.54</t>
+          <t>37.68</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>39.13</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-4.23</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>12.69</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>702.2</t>
+          <t>702.4</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>737.35</v>
+        <v>733.4</v>
       </c>
       <c r="AN5" t="n">
-        <v>648.52</v>
+        <v>650.8200000000001</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>640.28</t>
+          <t>641.01</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-41.44</t>
+          <t>-42.31</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>13.01</t>
+          <t>11.60</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>22.23</t>
+          <t>20.10</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-72.48</t>
+          <t>-75.11</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>4927555242.950284</t>
+          <t>4924195625.746809</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>3163492460.0</t>
+          <t>2526492754.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>3132612269.2</v>
+        <v>2976124482.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>3269603904.2</t>
+          <t>3476901363.0</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>2494838192.4</v>
+        <v>2522196255.28</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-136991635</t>
+          <t>-500776880</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>27434120.50332935</t>
+          <t>23871683.71729021</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>76579952.95061398</t>
+          <t>4278281.394074917</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>3163492460.0</t>
+          <t>2526492754.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-9.33</t>
+          <t>-8.42</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,12 +2501,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>25.23</t>
+          <t>25.49</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>52.16</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>41.31</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>223011</t>
+          <t>224591</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>738.0</t>
+          <t>717.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>738.0</t>
+          <t>727.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>698.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>700.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5678.126</t>
+          <t>4456.494</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>700.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>44.32</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-5.15</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>15.89</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>-5.14</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1814</t>
+          <t>2410</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>69.57</t>
+          <t>27.54</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>29.95</t>
+          <t>39.13</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-5.19</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>14.16</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>699.8</t>
+          <t>702.2</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>738.1</v>
+        <v>737.35</v>
       </c>
       <c r="AN6" t="n">
-        <v>646.54</v>
+        <v>648.52</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>639.58</t>
+          <t>640.28</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-37.42</t>
+          <t>-41.44</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>15.35</t>
+          <t>13.01</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>24.53</t>
+          <t>22.23</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-69.62</t>
+          <t>-72.48</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>4927555242.950284</t>
+          <t>4924195625.746809</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>4127699179.0</t>
+          <t>3163492460.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>4379292599.4</v>
+        <v>3132612269.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>3034371558.8</t>
+          <t>3269603904.2</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>2446536212.66</v>
+        <v>2494838192.4</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>1344921040</t>
+          <t>-136991635</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>18498514.60382305</t>
+          <t>27434120.50332935</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>108883088.3545771</t>
+          <t>76579952.95061398</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>4127699179.0</t>
+          <t>3163492460.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-5.57</t>
+          <t>-9.33</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>26.28</t>
+          <t>25.23</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>52.16</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>41.31</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>223011</t>
+          <t>224591</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>704.0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>743.0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>704.0</t>
+          <t>698.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>700.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3102.28</t>
+          <t>5678.126</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>695.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>74.46</t>
+          <t>44.32</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11.06</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1814</t>
+          <t>2410</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>20.29</t>
+          <t>69.57</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>14.56</t>
+          <t>29.95</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-5.19</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>13.98</t>
+          <t>14.16</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>701.8</t>
+          <t>699.8</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>734.15</v>
+        <v>738.1</v>
       </c>
       <c r="AN7" t="n">
-        <v>644.12</v>
+        <v>646.54</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>638.67</t>
+          <t>639.58</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-43.51</t>
+          <t>-37.42</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>15.15</t>
+          <t>15.35</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>26.82</t>
+          <t>24.53</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-66.78</t>
+          <t>-69.62</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>4927555242.950284</t>
+          <t>4924195625.746809</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>2145406818.0</t>
+          <t>4127699179.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>4705713538.6</v>
+        <v>4379292599.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>2697328683.0</t>
+          <t>3034371558.8</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>2381458909.08</v>
+        <v>2446536212.66</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>2008384855</t>
+          <t>1344921040</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>2064955.740049592</t>
+          <t>18498514.60382305</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>47833880.16900253</t>
+          <t>108883088.3545771</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>2145406818.0</t>
+          <t>4127699179.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-9.97</t>
+          <t>-5.57</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>26.28</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>52.16</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>41.31</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>223011</t>
+          <t>224591</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>689.0</t>
+          <t>704.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
+          <t>743.0</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
           <t>704.0</t>
         </is>
       </c>
-      <c r="CF7" t="inlineStr">
-        <is>
-          <t>677.0</t>
-        </is>
-      </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>695.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4210.877</t>
+          <t>3102.28</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>681.0</t>
+          <t>695.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>75.25</t>
+          <t>74.46</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-7.72</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15.02</t>
+          <t>11.06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-5.28</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1814</t>
+          <t>2410</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.29</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>14.56</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-4.46</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-2.30</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>13.59</t>
+          <t>13.98</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>712.8</t>
+          <t>701.8</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>729.6</v>
+        <v>734.15</v>
       </c>
       <c r="AN8" t="n">
-        <v>642.3200000000001</v>
+        <v>644.12</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>638.33</t>
+          <t>638.67</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-38.99</t>
+          <t>-43.51</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>15.15</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>29.74</t>
+          <t>26.82</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-63.17</t>
+          <t>-66.78</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>4927555242.950284</t>
+          <t>4924195625.746809</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>2917531202.0</t>
+          <t>2145406818.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>4446393537.2</v>
+        <v>4705713538.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>2537135784.1</t>
+          <t>2697328683.0</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>2394527724.36</v>
+        <v>2381458909.08</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>1909257753</t>
+          <t>2008384855</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-6256666.883396398</t>
+          <t>2064955.740049592</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>171300840.0050039</t>
+          <t>47833880.16900253</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>2917531202.0</t>
+          <t>2145406818.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-11.79</t>
+          <t>-9.97</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3786,17 +3786,17 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>52.16</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>41.31</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>223011</t>
+          <t>224591</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>720.0</t>
+          <t>689.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>721.0</t>
+          <t>704.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
@@ -3861,7 +3861,7 @@
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>681.0</t>
+          <t>695.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>4656.178</t>
+          <t>4210.877</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>681.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>70.21</t>
+          <t>75.25</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>-7.72</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16.60</t>
+          <t>15.02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-5.28</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1814</t>
+          <t>2410</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-4.46</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-2.30</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>13.59</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>718.0</t>
+          <t>712.8</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>726.45</v>
+        <v>729.6</v>
       </c>
       <c r="AN9" t="n">
-        <v>641.1799999999999</v>
+        <v>642.3200000000001</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>638.1</t>
+          <t>638.33</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-29.15</t>
+          <t>-38.99</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>23.12</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>32.64</t>
+          <t>29.74</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-59.58</t>
+          <t>-63.17</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>4927555242.950284</t>
+          <t>4924195625.746809</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>3308931687.0</t>
+          <t>2917531202.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>3977678243.4</v>
+        <v>4446393537.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2336901368.1</t>
+          <t>2537135784.1</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>2356977274.04</v>
+        <v>2394527724.36</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>1640776875</t>
+          <t>1909257753</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-38539849.95401464</t>
+          <t>-6256666.883396398</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>258836711.484827</t>
+          <t>171300840.0050039</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>3308931687.0</t>
+          <t>2917531202.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-8.55</t>
+          <t>-11.79</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4216,17 +4216,17 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>52.16</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>41.31</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>223011</t>
+          <t>224591</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>701.0</t>
+          <t>720.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>721.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>698.0</t>
+          <t>677.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>681.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-7.07</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>12908.308</t>
+          <t>4656.178</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>688.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>62.76</t>
+          <t>70.21</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-6.78</t>
+          <t>-4.34</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>46.03</t>
+          <t>16.60</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-13.23</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1814</t>
+          <t>2410</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>39.68</t>
+          <t>24.72</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-5.02</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>12.71</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>724.4</t>
+          <t>718.0</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>720.75</v>
+        <v>726.45</v>
       </c>
       <c r="AN10" t="n">
-        <v>639.48</v>
+        <v>641.1799999999999</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>637.48</t>
+          <t>638.1</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-24.05</t>
+          <t>-29.15</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>26.60</t>
+          <t>23.12</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>35.02</t>
+          <t>32.64</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-56.63</t>
+          <t>-59.58</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>4927555242.950284</t>
+          <t>4924195625.746809</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>9396894111.0</t>
+          <t>3308931687.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>3406595539.2</v>
+        <v>3977678243.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>2092972596.2</t>
+          <t>2336901368.1</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>2319670873.56</v>
+        <v>2356977274.04</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>1313622943</t>
+          <t>1640776875</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-92608315.67016768</t>
+          <t>-38539849.95401464</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>332708021.9386873</t>
+          <t>258836711.484827</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>9396894111.0</t>
+          <t>3308931687.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-10.88</t>
+          <t>-8.55</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,22 +4641,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>24.80</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>52.16</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>41.31</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>223011</t>
+          <t>224591</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>721.0</t>
+          <t>701.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>780.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>687.0</t>
+          <t>698.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>688.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-7.07</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>7500.722</t>
+          <t>12908.308</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>739.0</t>
+          <t>688.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-4.67</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>32.75</t>
+          <t>62.76</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-6.78</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>26.75</t>
+          <t>46.03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-7.70</t>
+          <t>-13.23</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,17 +4884,17 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1814</t>
+          <t>2410</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>50.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -4904,53 +4904,53 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>-5.02</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>12.71</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>731.2</t>
+          <t>724.4</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>715.55</v>
+        <v>720.75</v>
       </c>
       <c r="AN11" t="n">
-        <v>638.3</v>
+        <v>639.48</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>636.88</t>
+          <t>637.48</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-12.52</t>
+          <t>-24.05</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>32.48</t>
+          <t>26.60</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>37.13</t>
+          <t>35.02</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-54.03</t>
+          <t>-56.63</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>4927555242.950284</t>
+          <t>4924195625.746809</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>5759803875.0</t>
+          <t>9396894111.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>1689450518.2</v>
+        <v>3406595539.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>1272693479.4</t>
+          <t>2092972596.2</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>2149905312.46</v>
+        <v>2319670873.56</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>416757038</t>
+          <t>1313622943</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-169938558.8717777</t>
+          <t>-92608315.67016768</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-225925652.1964645</t>
+          <t>332708021.9386873</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>5759803875.0</t>
+          <t>9396894111.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-10.88</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>26.64</t>
+          <t>24.80</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>52.16</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>41.31</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>223011</t>
+          <t>224591</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>789.0</t>
+          <t>721.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>803.0</t>
+          <t>780.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>732.0</t>
+          <t>687.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>739.0</t>
+          <t>688.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1152.161</t>
+          <t>7500.722</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>739.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-6.23</t>
+          <t>-3.94</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-19.96</t>
+          <t>32.75</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>26.75</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>-7.70</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1814</t>
+          <t>2410</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>68.25</t>
+          <t>50.79</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>31.22</t>
+          <t>39.68</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>732.4</t>
+          <t>731.2</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>708.6</v>
+        <v>715.55</v>
       </c>
       <c r="AN12" t="n">
-        <v>635.96</v>
+        <v>638.3</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>635.39</t>
+          <t>636.88</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-10.37</t>
+          <t>-12.52</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>34.32</t>
+          <t>32.48</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>38.29</t>
+          <t>37.13</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-52.59</t>
+          <t>-54.03</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>4927555242.950284</t>
+          <t>4924195625.746809</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>848806811.0</t>
+          <t>5759803875.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>688943827.4</v>
+        <v>1689450518.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>860708905.5</t>
+          <t>1272693479.4</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>2069337538.82</v>
+        <v>2149905312.46</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-171765078</t>
+          <t>416757038</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-159759087.3581983</t>
+          <t>-169938558.8717777</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-626216745.2396646</t>
+          <t>-225925652.1964645</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>848806811.0</t>
+          <t>5759803875.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>27.04</t>
+          <t>26.64</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>52.16</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>41.31</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>223011</t>
+          <t>224591</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>789.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>803.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>732.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>739.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>792.387</t>
+          <t>921.717</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>95.1</t>
+          <t>96.4</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-39.51</t>
+          <t>-42.70</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-14.71</t>
+          <t>-13.54</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,73 +5744,73 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>792</t>
+          <t>922</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>70.37</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>15.54</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>95.82</t>
+          <t>95.68</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>98.68000000000001</v>
+        <v>97.97</v>
       </c>
       <c r="AN13" t="n">
-        <v>101.03</v>
+        <v>100.91</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>103.1</t>
+          <t>102.96</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-13.08</t>
+          <t>-4.75</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-112.74</t>
+          <t>-112.90</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>1662430966.46804</t>
+          <t>1660261273.210638</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>75315976.0</t>
+          <t>88531480.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>140450688.4</v>
+        <v>114194143.4</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>232180199.0</t>
+          <t>199282796.9</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>418404115.58</v>
+        <v>417237806.8</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-91729510</t>
+          <t>-85088653</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-69818780.90319912</t>
+          <t>-72078005.85986857</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-87784211.6049205</t>
+          <t>-84503743.12155059</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>75315976.0</t>
+          <t>88531480.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-6.31</t>
+          <t>-5.02</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>31.49</t>
+          <t>31.92</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>41.31</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>25973</t>
+          <t>26328</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>95.7</t>
+          <t>95.3</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>95.8</t>
+          <t>96.6</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>94.7</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>95.1</t>
+          <t>96.4</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1061.208</t>
+          <t>792.387</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>95.1</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-37.75</t>
+          <t>-39.51</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-14.98</t>
+          <t>-14.71</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,73 +6174,73 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>792</t>
+          <t>922</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>7.32</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>27.64</t>
+          <t>15.54</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-3.49</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>96.24</t>
+          <t>95.82</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>99.72</v>
+        <v>98.68000000000001</v>
       </c>
       <c r="AN14" t="n">
-        <v>101.18</v>
+        <v>101.03</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>103.27</t>
+          <t>103.1</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-17.33</t>
+          <t>-13.08</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-112.33</t>
+          <t>-112.74</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>1662430966.46804</t>
+          <t>1660261273.210638</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>101009670.0</t>
+          <t>75315976.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>157356209</v>
+        <v>140450688.4</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>252795469.6</t>
+          <t>232180199.0</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>419248618.68</v>
+        <v>418404115.58</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-95439260</t>
+          <t>-91729510</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-66552338.9574316</t>
+          <t>-69818780.90319912</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-87919497.88098752</t>
+          <t>-87784211.6049205</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>101009670.0</t>
+          <t>75315976.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-6.60</t>
+          <t>-6.31</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6371,12 +6371,12 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>31.49</t>
+          <t>31.92</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>41.31</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>25973</t>
+          <t>26328</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
+          <t>95.7</t>
+        </is>
+      </c>
+      <c r="CE14" t="inlineStr">
+        <is>
           <t>95.8</t>
         </is>
       </c>
-      <c r="CE14" t="inlineStr">
-        <is>
-          <t>96.1</t>
-        </is>
-      </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>95.1</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1237.634</t>
+          <t>1061.208</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-38.77</t>
+          <t>-37.75</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-14.62</t>
+          <t>-14.98</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,37 +6604,37 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>792</t>
+          <t>922</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>17.07</t>
+          <t>7.32</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>46.34</t>
+          <t>27.64</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-4.37</t>
+          <t>-3.49</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -6644,33 +6644,33 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>96.18</t>
+          <t>96.24</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>100.58</v>
+        <v>99.72</v>
       </c>
       <c r="AN15" t="n">
-        <v>101.32</v>
+        <v>101.18</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>103.42</t>
+          <t>103.27</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-19.71</t>
+          <t>-17.33</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-111.79</t>
+          <t>-112.33</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>1662430966.46804</t>
+          <t>1660261273.210638</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>119055310.0</t>
+          <t>101009670.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>166326125</v>
+        <v>157356209</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>271620933.8</t>
+          <t>252795469.6</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>421729365.34</v>
+        <v>419248618.68</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-105294808</t>
+          <t>-95439260</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-62667400.97133053</t>
+          <t>-66552338.9574316</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-87725677.7081908</t>
+          <t>-87919497.88098752</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>119055310.0</t>
+          <t>101009670.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-6.21</t>
+          <t>-6.60</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
@@ -6791,22 +6791,22 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>31.49</t>
+          <t>31.92</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>41.31</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>25973</t>
+          <t>26328</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>96.8</t>
+          <t>95.8</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>97.7</t>
+          <t>96.1</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6893,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1934.14</t>
+          <t>1237.634</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>96.9</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-36.48</t>
+          <t>-38.77</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-13.09</t>
+          <t>-14.62</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,73 +7034,73 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>792</t>
+          <t>922</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>58.54</t>
+          <t>17.07</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>62.6</t>
+          <t>46.34</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-5.36</t>
+          <t>-4.37</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>96.18</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>101.64</v>
+        <v>100.58</v>
       </c>
       <c r="AN16" t="n">
-        <v>101.52</v>
+        <v>101.32</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>103.55</t>
+          <t>103.42</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-22.57</t>
+          <t>-19.71</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-111.21</t>
+          <t>-111.79</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>1662430966.46804</t>
+          <t>1660261273.210638</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>187058281.0</t>
+          <t>119055310.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>178982304.2</v>
+        <v>166326125</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>281758656.3</t>
+          <t>271620933.8</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>421804108.64</v>
+        <v>421729365.34</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-102776352</t>
+          <t>-105294808</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-58111350.65553775</t>
+          <t>-62667400.97133053</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-86249193.25747448</t>
+          <t>-87725677.7081908</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>187058281.0</t>
+          <t>119055310.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-4.53</t>
+          <t>-6.21</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7201,7 +7201,7 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
@@ -7221,22 +7221,22 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>31.49</t>
+          <t>31.92</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>41.31</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>25973</t>
+          <t>26328</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>96.8</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>97.6</t>
+          <t>97.7</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>96.9</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2251.93</t>
+          <t>1934.14</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>97.1</t>
+          <t>96.9</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-2.1</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>-36.48</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-12.91</t>
+          <t>-13.09</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,73 +7464,73 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>792</t>
+          <t>922</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>63.41</t>
+          <t>58.54</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>43.09</t>
+          <t>62.6</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-6.32</t>
+          <t>-5.36</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>95.86</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>102.32</v>
+        <v>101.64</v>
       </c>
       <c r="AN17" t="n">
-        <v>101.67</v>
+        <v>101.52</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>103.67</t>
+          <t>103.55</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-34.44</t>
+          <t>-22.57</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-110.58</t>
+          <t>-111.21</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>1662430966.46804</t>
+          <t>1660261273.210638</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>219814205.0</t>
+          <t>187058281.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>284371450.4</v>
+        <v>178982304.2</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>299063636.4</t>
+          <t>281758656.3</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>422852603.5</v>
+        <v>421804108.64</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-14692186</t>
+          <t>-102776352</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-52995379.27336744</t>
+          <t>-58111350.65553775</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-88345634.03296983</t>
+          <t>-86249193.25747448</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>219814205.0</t>
+          <t>187058281.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-4.33</t>
+          <t>-4.53</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7661,12 +7661,12 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>31.49</t>
+          <t>31.92</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>41.31</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>25973</t>
+          <t>26328</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
+          <t>97.5</t>
+        </is>
+      </c>
+      <c r="CE17" t="inlineStr">
+        <is>
           <t>97.6</t>
         </is>
       </c>
-      <c r="CE17" t="inlineStr">
-        <is>
-          <t>98.6</t>
-        </is>
-      </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>96.7</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>97.1</t>
+          <t>96.9</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1654.541</t>
+          <t>2251.93</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>97.2</t>
+          <t>97.1</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-12.83</t>
+          <t>-12.91</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,73 +7894,73 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>792</t>
+          <t>922</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>65.85</t>
+          <t>63.41</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>22.48</t>
+          <t>43.09</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-6.18</t>
+          <t>-6.32</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>96.16</t>
+          <t>95.86</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>102.5</v>
+        <v>102.32</v>
       </c>
       <c r="AN18" t="n">
-        <v>101.88</v>
+        <v>101.67</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>103.75</t>
+          <t>103.67</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-52.73</t>
+          <t>-34.44</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-109.67</t>
+          <t>-110.58</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1662430966.46804</t>
+          <t>1660261273.210638</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>159843579.0</t>
+          <t>219814205.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>323909709.6</v>
+        <v>284371450.4</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>303527778.0</t>
+          <t>299063636.4</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>427891465.06</v>
+        <v>422852603.5</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>20381931</t>
+          <t>-14692186</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-46568060.22616701</t>
+          <t>-52995379.27336744</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-91694911.4967857</t>
+          <t>-88345634.03296983</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>159843579.0</t>
+          <t>219814205.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-4.24</t>
+          <t>-4.33</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
@@ -8081,12 +8081,12 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>31.49</t>
+          <t>31.92</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>41.31</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>25973</t>
+          <t>26328</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>97.6</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>97.2</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>96.7</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>97.2</t>
+          <t>97.1</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,42 +8193,42 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
+          <t>2.83</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>1654.541</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>97.2</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
           <t>-0.83</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>1536.151</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>94.5</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>0.63</t>
-        </is>
-      </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>11.75</t>
+          <t>6.72</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-15.25</t>
+          <t>-12.83</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,73 +8324,73 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>792</t>
+          <t>922</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>65.85</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>22.48</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-6.60</t>
+          <t>-6.18</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>95.75999999999999</t>
+          <t>96.16</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>102.53</v>
+        <v>102.5</v>
       </c>
       <c r="AN19" t="n">
-        <v>102.08</v>
+        <v>101.88</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>103.82</t>
+          <t>103.75</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-82.43</t>
+          <t>-52.73</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-108.39</t>
+          <t>-109.67</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>1662430966.46804</t>
+          <t>1660261273.210638</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>145859250.0</t>
+          <t>159843579.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>348234730.2</v>
+        <v>323909709.6</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>311622176.9</t>
+          <t>303527778.0</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>429640696.94</v>
+        <v>427891465.06</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>36612553</t>
+          <t>20381931</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-38363178.1769636</t>
+          <t>-46568060.22616701</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-86779351.10592324</t>
+          <t>-91694911.4967857</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>145859250.0</t>
+          <t>159843579.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-6.90</t>
+          <t>-4.24</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
@@ -8511,22 +8511,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>31.49</t>
+          <t>31.92</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>41.31</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>25973</t>
+          <t>26328</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>97.2</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>97.2</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1914.684</t>
+          <t>1536.151</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>95.3</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>16.80</t>
+          <t>11.75</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-14.53</t>
+          <t>-15.25</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,73 +8754,73 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>792</t>
+          <t>922</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>13.41</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-6.38</t>
+          <t>-6.60</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>96.12</t>
+          <t>95.75999999999999</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>102.68</v>
+        <v>102.53</v>
       </c>
       <c r="AN20" t="n">
-        <v>102.33</v>
+        <v>102.08</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>103.93</t>
+          <t>103.82</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-109.29</t>
+          <t>-82.43</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-106.66</t>
+          <t>-108.39</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>1662430966.46804</t>
+          <t>1660261273.210638</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>182336206.0</t>
+          <t>145859250.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>376915742.6</v>
+        <v>348234730.2</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>322711393.4</t>
+          <t>311622176.9</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>429470961.98</v>
+        <v>429640696.94</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>54204349</t>
+          <t>36612553</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-29560237.64442549</t>
+          <t>-38363178.1769636</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-75159538.47233671</t>
+          <t>-86779351.10592324</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>182336206.0</t>
+          <t>145859250.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-6.11</t>
+          <t>-6.90</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
@@ -8941,22 +8941,22 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>31.49</t>
+          <t>31.92</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>41.31</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>25973</t>
+          <t>26328</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>95.8</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>96.3</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>95.3</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-3.53</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>7327.598</t>
+          <t>1914.684</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>95.3</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>14.67</t>
+          <t>16.80</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-14.62</t>
+          <t>-14.53</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12.09</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-4.94</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,73 +9184,73 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>792</t>
+          <t>922</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>12.88</t>
+          <t>13.41</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-6.09</t>
+          <t>-6.38</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>96.56</t>
+          <t>96.12</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>102.82</v>
+        <v>102.68</v>
       </c>
       <c r="AN21" t="n">
-        <v>102.56</v>
+        <v>102.33</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>104.04</t>
+          <t>103.93</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-159.05</t>
+          <t>-109.29</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-104.84</t>
+          <t>-106.66</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>1662430966.46804</t>
+          <t>1660261273.210638</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>714004012.0</t>
+          <t>182336206.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>384535008.4</v>
+        <v>376915742.6</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>335344540.6</t>
+          <t>322711393.4</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>431976435.3</v>
+        <v>429470961.98</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>49190467</t>
+          <t>54204349</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-21269455.67571436</t>
+          <t>-29560237.64442549</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-59783782.19320107</t>
+          <t>-75159538.47233671</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>714004012.0</t>
+          <t>182336206.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-6.21</t>
+          <t>-6.11</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9381,12 +9381,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>31.49</t>
+          <t>31.92</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>41.31</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>25973</t>
+          <t>26328</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>95.8</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>96.6</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>95.1</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>95.3</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>-3.53</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>4255.671</t>
+          <t>7327.598</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-3.68</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>14.67</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-11.57</t>
+          <t>-14.62</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>7.02</t>
+          <t>12.09</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>-4.94</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,17 +9614,17 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>792</t>
+          <t>922</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>38.64</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
@@ -9634,53 +9634,53 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-5.63</t>
+          <t>-6.09</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>97.24000000000001</t>
+          <t>96.56</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>103.04</v>
+        <v>102.82</v>
       </c>
       <c r="AN22" t="n">
-        <v>102.79</v>
+        <v>102.56</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>104.13</t>
+          <t>104.04</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-260.17</t>
+          <t>-159.05</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-102.92</t>
+          <t>-104.84</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>1662430966.46804</t>
+          <t>1660261273.210638</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>417505501.0</t>
+          <t>714004012.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>313755822.4</v>
+        <v>384535008.4</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>306400241.3</t>
+          <t>335344540.6</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>420660383.62</v>
+        <v>431976435.3</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>7355581</t>
+          <t>49190467</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-14266850.85435314</t>
+          <t>-21269455.67571436</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-92647688.78753585</t>
+          <t>-59783782.19320107</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>417505501.0</t>
+          <t>714004012.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-2.86</t>
+          <t>-6.21</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9781,7 +9781,7 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>31.49</t>
+          <t>31.92</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>41.31</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>25973</t>
+          <t>26328</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,7 +9866,7 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>98.4</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
@@ -9876,12 +9876,12 @@
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>95.1</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2950.547</t>
+          <t>4255.671</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-19.47</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-14.62</t>
+          <t>-11.57</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>7.02</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,73 +10044,73 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>792</t>
+          <t>922</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>38.64</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.88</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-5.20</t>
+          <t>-5.63</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>97.82</t>
+          <t>97.24000000000001</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>103.19</v>
+        <v>103.04</v>
       </c>
       <c r="AN23" t="n">
-        <v>102.95</v>
+        <v>102.79</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>104.19</t>
+          <t>104.13</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-887.49</t>
+          <t>-260.17</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-101.02</t>
+          <t>-102.92</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>1662430966.46804</t>
+          <t>1660261273.210638</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>281468682.0</t>
+          <t>417505501.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>283145846.4</v>
+        <v>313755822.4</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>351622846.6</t>
+          <t>306400241.3</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>414970230.06</v>
+        <v>420660383.62</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-68477000</t>
+          <t>7355581</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-15789.41195628047</t>
+          <t>-14266850.85435314</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-104519583.1441735</t>
+          <t>-92647688.78753585</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>281468682.0</t>
+          <t>417505501.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-6.21</t>
+          <t>-2.86</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10211,7 +10211,7 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>31.49</t>
+          <t>31.92</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>41.31</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>25973</t>
+          <t>26328</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>98.4</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>97.9</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>94.1</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/配電系統.xlsx
+++ b/Result/checksun_type/配電系統.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2409.738</t>
+          <t>1736.086</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>711.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-2.5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-32.61</t>
+          <t>-25.97</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>8.59</t>
+          <t>6.19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,176 +1014,168 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>71</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2410</t>
+          <t>1736</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
+          <t>72.92</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
           <t>62.5</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>43.94</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AH2" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>-2.08</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>9.23</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>706.2</t>
+        </is>
+      </c>
+      <c r="AM2" t="n">
+        <v>721.2</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>660.24</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>642.91</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>-39.98</t>
+        </is>
+      </c>
+      <c r="AQ2" t="n">
+        <v>7.82</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>13.02</v>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>80.75</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>-83.87</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>2025/10/16</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>4919856794.394476</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>1240653794.0</t>
+        </is>
+      </c>
+      <c r="AX2" t="n">
+        <v>1840994094</v>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>2486803181.6</t>
+        </is>
+      </c>
+      <c r="AZ2" t="n">
+        <v>2593471789.5</v>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>-645809087</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>-87575595.74692756</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>-295436683.9736991</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>1240653794.0</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>772.0</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>2025/11/04</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>-7.25</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>華城</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>華城</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>電機機械</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
         <is>
           <t>1.14</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>-2.73</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>9.89</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>2.38</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>703.0</t>
-        </is>
-      </c>
-      <c r="AM2" t="n">
-        <v>722.7</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>657.66</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>642.4</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>-45.49</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>7.81</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>14.33</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>80.75</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>-82.26</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>2025/10/16</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>4924195625.746809</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>1706016743.0</t>
-        </is>
-      </c>
-      <c r="AX2" t="n">
-        <v>2225561827.2</v>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>3302427213.3</t>
-        </is>
-      </c>
-      <c r="AZ2" t="n">
-        <v>2578743388.1</v>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>-1076865386</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>-49782670.61478729</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>-230075552.3796711</t>
-        </is>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>1706016743.0</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>772.0</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>2025/11/04</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>-7.90</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>華城</t>
-        </is>
-      </c>
-      <c r="BJ2" t="inlineStr">
-        <is>
-          <t>華城</t>
-        </is>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>電機機械</t>
-        </is>
-      </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>1.14</t>
-        </is>
-      </c>
       <c r="BN2" t="inlineStr">
         <is>
           <t>17.93840330060069</t>
@@ -1201,22 +1193,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>25.63</t>
+          <t>25.81</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>52.16</t>
+          <t>52.53</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>42.16</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>224591</t>
+          <t>226170</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>705.0</t>
+          <t>715.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>715.0</t>
+          <t>720.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>694.0</t>
+          <t>708.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>711.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1813.678</t>
+          <t>2409.738</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>711.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1343,12 +1335,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-2.5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-26.91</t>
+          <t>-32.61</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>6.47</t>
+          <t>8.59</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,74 +1436,66 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>71</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2410</t>
+          <t>1736</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>52.08</t>
+          <t>62.5</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>35.67</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>-0.08</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>-2.59</t>
-        </is>
+          <t>43.94</t>
+        </is>
+      </c>
+      <c r="AH3" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>-2.73</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>10.71</t>
+          <t>9.89</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>706.6</t>
+          <t>703.0</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>725.4</v>
+        <v>722.7</v>
       </c>
       <c r="AN3" t="n">
-        <v>655.24</v>
+        <v>657.66</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>641.96</t>
+          <t>642.4</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-48.64</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>8.19</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>15.96</t>
-        </is>
+          <t>-45.49</t>
+        </is>
+      </c>
+      <c r="AQ3" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>14.33</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1520,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-80.24</t>
+          <t>-82.26</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>4924195625.746809</t>
+          <t>4919856794.394476</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1267840540.0</t>
+          <t>1706016743.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>2709898314.4</v>
+        <v>2225561827.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>3707805926.5</t>
+          <t>3302427213.3</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>2561747225.36</v>
+        <v>2578743388.1</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-997907612</t>
+          <t>-1076865386</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-17002146.65753568</t>
+          <t>-49782670.61478729</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-178345839.1960711</t>
+          <t>-230075552.3796711</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>1267840540.0</t>
+          <t>1706016743.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-8.55</t>
+          <t>-7.90</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,22 +1615,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>25.63</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>52.16</t>
+          <t>52.53</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>42.16</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>224591</t>
+          <t>226170</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>703.0</t>
+          <t>705.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>715.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>692.0</t>
+          <t>694.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>711.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3516.568</t>
+          <t>1813.678</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>691.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-2.5</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-21.29</t>
+          <t>-26.91</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-6.37</t>
+          <t>-4.34</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12.54</t>
+          <t>6.47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,74 +1858,66 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>71</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2410</t>
+          <t>1736</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>17.24</t>
+          <t>52.08</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>27.49</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>-1.90</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>-3.42</t>
-        </is>
+          <t>35.67</t>
+        </is>
+      </c>
+      <c r="AH4" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>-2.59</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>11.69</t>
+          <t>10.71</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>704.4</t>
+          <t>706.6</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>729.35</v>
+        <v>725.4</v>
       </c>
       <c r="AN4" t="n">
-        <v>653</v>
+        <v>655.24</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>641.5</t>
+          <t>641.96</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-49.29</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>9.08</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>17.90</t>
-        </is>
+          <t>-48.64</t>
+        </is>
+      </c>
+      <c r="AQ4" t="n">
+        <v>8.19</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>15.96</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1950,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-77.84</t>
+          <t>-80.24</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>4924195625.746809</t>
+          <t>4919856794.394476</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>2463966639.0</t>
+          <t>1267840540.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>2885411570</v>
+        <v>2709898314.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>3665902553.6</t>
+          <t>3707805926.5</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>2552773254.62</v>
+        <v>2561747225.36</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-780490983</t>
+          <t>-997907612</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>12333070.16765259</t>
+          <t>-17002146.65753568</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-51129304.35535431</t>
+          <t>-178345839.1960711</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>2463966639.0</t>
+          <t>1267840540.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-10.49</t>
+          <t>-8.55</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,22 +2037,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>24.91</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>52.16</t>
+          <t>52.53</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>42.16</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>224591</t>
+          <t>226170</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>711.0</t>
+          <t>703.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>718.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>691.0</t>
+          <t>692.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>691.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3523.66</t>
+          <t>3516.568</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>691.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-2.5</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-14.40</t>
+          <t>-21.29</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-4.20</t>
+          <t>-6.37</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>12.54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,74 +2280,66 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>71</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2410</t>
+          <t>1736</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>37.68</t>
+          <t>17.24</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>44.93</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>0.65</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>-4.23</t>
-        </is>
+          <t>27.49</t>
+        </is>
+      </c>
+      <c r="AH5" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>-3.42</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>12.69</t>
+          <t>11.69</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>702.4</t>
+          <t>704.4</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>733.4</v>
+        <v>729.35</v>
       </c>
       <c r="AN5" t="n">
-        <v>650.8200000000001</v>
+        <v>653</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>641.01</t>
+          <t>641.5</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-42.31</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>11.60</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>20.10</t>
-        </is>
+          <t>-49.29</t>
+        </is>
+      </c>
+      <c r="AQ5" t="n">
+        <v>9.08</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>17.9</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2380,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-75.11</t>
+          <t>-77.84</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>4924195625.746809</t>
+          <t>4919856794.394476</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>2526492754.0</t>
+          <t>2463966639.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>2976124482.6</v>
+        <v>2885411570</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>3476901363.0</t>
+          <t>3665902553.6</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>2522196255.28</v>
+        <v>2552773254.62</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-500776880</t>
+          <t>-780490983</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>23871683.71729021</t>
+          <t>12333070.16765259</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>4278281.394074917</t>
+          <t>-51129304.35535431</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>2526492754.0</t>
+          <t>2463966639.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-8.42</t>
+          <t>-10.49</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,22 +2459,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>25.49</t>
+          <t>24.91</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>52.16</t>
+          <t>52.53</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>42.16</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>224591</t>
+          <t>226170</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>717.0</t>
+          <t>711.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>727.0</t>
+          <t>718.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>691.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>691.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4456.494</t>
+          <t>3523.66</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>700.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-2.5</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>-14.40</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-5.15</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15.89</t>
+          <t>12.57</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-5.14</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,74 +2702,66 @@
       <c r="AC6" t="inline